--- a/research/traditional_assets/database/data/israel/israel_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_construction_supplies.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="tase_ackr" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,40 +590,40 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.1410321921308125</v>
+        <v>0.1363850873053327</v>
       </c>
       <c r="H2">
-        <v>0.1410321921308125</v>
+        <v>0.1363850873053327</v>
       </c>
       <c r="I2">
-        <v>0.09248850281042413</v>
+        <v>0.08966493629070316</v>
       </c>
       <c r="J2">
-        <v>0.07133266811244916</v>
+        <v>0.0669271191131873</v>
       </c>
       <c r="K2">
-        <v>19.6</v>
+        <v>17.7</v>
       </c>
       <c r="L2">
-        <v>0.1001532958610118</v>
+        <v>0.08352996696554978</v>
       </c>
       <c r="M2">
-        <v>46.5</v>
+        <v>7.02</v>
       </c>
       <c r="N2">
-        <v>0.1238019169329073</v>
+        <v>0.02057444314185228</v>
       </c>
       <c r="O2">
-        <v>2.372448979591836</v>
+        <v>0.3966101694915254</v>
       </c>
       <c r="P2">
-        <v>46.5</v>
+        <v>7.02</v>
       </c>
       <c r="Q2">
-        <v>0.1238019169329073</v>
+        <v>0.02057444314185228</v>
       </c>
       <c r="R2">
-        <v>2.372448979591836</v>
+        <v>0.3966101694915254</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,55 +632,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>49.2</v>
+        <v>38.8</v>
       </c>
       <c r="V2">
-        <v>0.1309904153354633</v>
+        <v>0.1137162954279015</v>
+      </c>
+      <c r="W2">
+        <v>0.07088506207448939</v>
       </c>
       <c r="X2">
-        <v>0.07243803298263332</v>
+        <v>0.1180956343149011</v>
+      </c>
+      <c r="Y2">
+        <v>-0.04721057224041172</v>
+      </c>
+      <c r="Z2">
+        <v>0.7173324306025727</v>
+      </c>
+      <c r="AA2">
+        <v>0.04800899302669055</v>
       </c>
       <c r="AB2">
-        <v>0.06357339694229761</v>
+        <v>0.1049576115470164</v>
+      </c>
+      <c r="AC2">
+        <v>-0.05694861852032588</v>
       </c>
       <c r="AD2">
-        <v>94.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>94.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="AG2">
-        <v>45.7</v>
+        <v>41.3</v>
       </c>
       <c r="AH2">
-        <v>0.2017003188097768</v>
+        <v>0.1901258010918585</v>
       </c>
       <c r="AI2">
-        <v>0.27539175856065</v>
+        <v>0.2233063841650404</v>
       </c>
       <c r="AJ2">
-        <v>0.1084737716591503</v>
+        <v>0.1079738562091503</v>
       </c>
       <c r="AK2">
-        <v>0.1547054840893704</v>
+        <v>0.1291028446389496</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AM2">
-        <v>-3.55</v>
+        <v>0.9300000000000002</v>
       </c>
       <c r="AN2">
-        <v>3.425992779783394</v>
+        <v>2.8006993006993</v>
+      </c>
+      <c r="AO2">
+        <v>7.08955223880597</v>
       </c>
       <c r="AP2">
-        <v>1.649819494584838</v>
+        <v>1.444055944055944</v>
       </c>
       <c r="AQ2">
-        <v>-5.098591549295775</v>
+        <v>20.43010752688172</v>
       </c>
     </row>
     <row r="3">
@@ -698,40 +718,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.1410321921308125</v>
+        <v>0.1363850873053327</v>
       </c>
       <c r="H3">
-        <v>0.1410321921308125</v>
+        <v>0.1363850873053327</v>
       </c>
       <c r="I3">
-        <v>0.09248850281042413</v>
+        <v>0.08966493629070316</v>
       </c>
       <c r="J3">
-        <v>0.07133266811244916</v>
+        <v>0.0669271191131873</v>
       </c>
       <c r="K3">
-        <v>19.6</v>
+        <v>17.7</v>
       </c>
       <c r="L3">
-        <v>0.1001532958610118</v>
+        <v>0.08352996696554978</v>
       </c>
       <c r="M3">
-        <v>46.5</v>
+        <v>7.02</v>
       </c>
       <c r="N3">
-        <v>0.1238019169329073</v>
+        <v>0.02057444314185228</v>
       </c>
       <c r="O3">
-        <v>2.372448979591836</v>
+        <v>0.3966101694915254</v>
       </c>
       <c r="P3">
-        <v>46.5</v>
+        <v>7.02</v>
       </c>
       <c r="Q3">
-        <v>0.1238019169329073</v>
+        <v>0.02057444314185228</v>
       </c>
       <c r="R3">
-        <v>2.372448979591836</v>
+        <v>0.3966101694915254</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -740,55 +760,8785 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>49.2</v>
+        <v>38.8</v>
       </c>
       <c r="V3">
-        <v>0.1309904153354633</v>
+        <v>0.1137162954279015</v>
+      </c>
+      <c r="W3">
+        <v>0.07088506207448939</v>
       </c>
       <c r="X3">
-        <v>0.07243803298263332</v>
+        <v>0.1180956343149011</v>
+      </c>
+      <c r="Y3">
+        <v>-0.04721057224041172</v>
+      </c>
+      <c r="Z3">
+        <v>0.7173324306025727</v>
+      </c>
+      <c r="AA3">
+        <v>0.04800899302669055</v>
       </c>
       <c r="AB3">
-        <v>0.06357339694229761</v>
+        <v>0.1049576115470164</v>
+      </c>
+      <c r="AC3">
+        <v>-0.05694861852032588</v>
       </c>
       <c r="AD3">
-        <v>94.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>94.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="AG3">
-        <v>45.7</v>
+        <v>41.3</v>
       </c>
       <c r="AH3">
-        <v>0.2017003188097768</v>
+        <v>0.1901258010918585</v>
       </c>
       <c r="AI3">
-        <v>0.27539175856065</v>
+        <v>0.2233063841650404</v>
       </c>
       <c r="AJ3">
-        <v>0.1084737716591503</v>
+        <v>0.1079738562091503</v>
       </c>
       <c r="AK3">
-        <v>0.1547054840893704</v>
+        <v>0.1291028446389496</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AM3">
-        <v>-3.55</v>
+        <v>0.9300000000000002</v>
       </c>
       <c r="AN3">
-        <v>3.425992779783394</v>
+        <v>2.8006993006993</v>
+      </c>
+      <c r="AO3">
+        <v>7.08955223880597</v>
       </c>
       <c r="AP3">
-        <v>1.649819494584838</v>
+        <v>1.444055944055944</v>
       </c>
       <c r="AQ3">
-        <v>-5.098591549295775</v>
+        <v>20.43010752688172</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ackerstein Group Ltd (TASE:ACKR)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TASE:ACKR</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Construction Supplies</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.190125801091859</v>
+      </c>
+      <c r="F2">
+        <v>0.18</v>
+      </c>
+      <c r="G2">
+        <v>341.2</v>
+      </c>
+      <c r="H2">
+        <v>352.188933204695</v>
+      </c>
+      <c r="I2">
+        <v>382.5</v>
+      </c>
+      <c r="J2">
+        <v>389.222933204695</v>
+      </c>
+      <c r="K2">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="L2">
+        <v>75.834</v>
+      </c>
+      <c r="M2">
+        <v>0.104957611547016</v>
+      </c>
+      <c r="N2">
+        <v>0.103814890588231</v>
+      </c>
+      <c r="O2">
+        <v>0.0489938990825688</v>
+      </c>
+      <c r="P2">
+        <v>0.04235</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.118095634314901</v>
+      </c>
+      <c r="T2">
+        <v>0.117307183644185</v>
+      </c>
+      <c r="U2">
+        <v>1.11192406692622</v>
+      </c>
+      <c r="V2">
+        <v>1.10086800710744</v>
+      </c>
+      <c r="W2">
+        <v>4.555404507932398</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>341.2</v>
+      </c>
+      <c r="AB2">
+        <v>0.07131389334354851</v>
+      </c>
+      <c r="AC2">
+        <v>0.06362844036697247</v>
+      </c>
+      <c r="AD2">
+        <v>0.23</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>28.6</v>
+      </c>
+      <c r="AH2">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="AI2">
+        <v>22.272</v>
+      </c>
+      <c r="AJ2">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="AK2">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="AL2">
+        <v>2.68</v>
+      </c>
+      <c r="AM2">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="AN2">
+        <v>38.8</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1059561554227326</v>
+      </c>
+      <c r="C2">
+        <v>415.6126131914907</v>
+      </c>
+      <c r="D2">
+        <v>376.8126131914906</v>
+      </c>
+      <c r="E2">
+        <v>-80.09999999999999</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>38.8</v>
+      </c>
+      <c r="H2">
+        <v>341.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>28.6</v>
+      </c>
+      <c r="K2">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L2">
+        <v>19</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>19</v>
+      </c>
+      <c r="O2">
+        <v>4.369999999999999</v>
+      </c>
+      <c r="P2">
+        <v>14.63</v>
+      </c>
+      <c r="Q2">
+        <v>24.23</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1059561554227326</v>
+      </c>
+      <c r="T2">
+        <v>0.941698065750157</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.23</v>
+      </c>
+      <c r="W2">
+        <v>0.035189</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1057655862652604</v>
+      </c>
+      <c r="C3">
+        <v>412.471938041099</v>
+      </c>
+      <c r="D3">
+        <v>377.884938041099</v>
+      </c>
+      <c r="E3">
+        <v>-75.887</v>
+      </c>
+      <c r="F3">
+        <v>4.212999999999999</v>
+      </c>
+      <c r="G3">
+        <v>38.8</v>
+      </c>
+      <c r="H3">
+        <v>341.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>28.6</v>
+      </c>
+      <c r="K3">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L3">
+        <v>19</v>
+      </c>
+      <c r="M3">
+        <v>0.1925341</v>
+      </c>
+      <c r="N3">
+        <v>18.8074659</v>
+      </c>
+      <c r="O3">
+        <v>4.325717157</v>
+      </c>
+      <c r="P3">
+        <v>14.481748743</v>
+      </c>
+      <c r="Q3">
+        <v>24.081748743</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1064784810760206</v>
+      </c>
+      <c r="T3">
+        <v>0.949022384039325</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.23</v>
+      </c>
+      <c r="W3">
+        <v>0.035189</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>98.68381756790097</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1055750171077881</v>
+      </c>
+      <c r="C4">
+        <v>409.3373835044331</v>
+      </c>
+      <c r="D4">
+        <v>378.9633835044331</v>
+      </c>
+      <c r="E4">
+        <v>-71.67399999999999</v>
+      </c>
+      <c r="F4">
+        <v>8.425999999999998</v>
+      </c>
+      <c r="G4">
+        <v>38.8</v>
+      </c>
+      <c r="H4">
+        <v>341.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>28.6</v>
+      </c>
+      <c r="K4">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L4">
+        <v>19</v>
+      </c>
+      <c r="M4">
+        <v>0.3850682</v>
+      </c>
+      <c r="N4">
+        <v>18.6149318</v>
+      </c>
+      <c r="O4">
+        <v>4.281434314</v>
+      </c>
+      <c r="P4">
+        <v>14.333497486</v>
+      </c>
+      <c r="Q4">
+        <v>23.933497486</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1070114664365184</v>
+      </c>
+      <c r="T4">
+        <v>0.9564961782119453</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.23</v>
+      </c>
+      <c r="W4">
+        <v>0.035189</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>49.34190878395049</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1053844479503158</v>
+      </c>
+      <c r="C5">
+        <v>406.2090021343148</v>
+      </c>
+      <c r="D5">
+        <v>380.0480021343148</v>
+      </c>
+      <c r="E5">
+        <v>-67.461</v>
+      </c>
+      <c r="F5">
+        <v>12.639</v>
+      </c>
+      <c r="G5">
+        <v>38.8</v>
+      </c>
+      <c r="H5">
+        <v>341.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>28.6</v>
+      </c>
+      <c r="K5">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L5">
+        <v>19</v>
+      </c>
+      <c r="M5">
+        <v>0.5776022999999999</v>
+      </c>
+      <c r="N5">
+        <v>18.4223977</v>
+      </c>
+      <c r="O5">
+        <v>4.237151471</v>
+      </c>
+      <c r="P5">
+        <v>14.185246229</v>
+      </c>
+      <c r="Q5">
+        <v>23.785246229</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1075554411858926</v>
+      </c>
+      <c r="T5">
+        <v>0.9641240712334855</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.23</v>
+      </c>
+      <c r="W5">
+        <v>0.035189</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>32.89460585596699</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1051938787928435</v>
+      </c>
+      <c r="C6">
+        <v>403.0868470869307</v>
+      </c>
+      <c r="D6">
+        <v>381.1388470869306</v>
+      </c>
+      <c r="E6">
+        <v>-63.248</v>
+      </c>
+      <c r="F6">
+        <v>16.852</v>
+      </c>
+      <c r="G6">
+        <v>38.8</v>
+      </c>
+      <c r="H6">
+        <v>341.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>28.6</v>
+      </c>
+      <c r="K6">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L6">
+        <v>19</v>
+      </c>
+      <c r="M6">
+        <v>0.7701363999999999</v>
+      </c>
+      <c r="N6">
+        <v>18.2298636</v>
+      </c>
+      <c r="O6">
+        <v>4.192868628</v>
+      </c>
+      <c r="P6">
+        <v>14.036994972</v>
+      </c>
+      <c r="Q6">
+        <v>23.636994972</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1081107487425453</v>
+      </c>
+      <c r="T6">
+        <v>0.9719108786929744</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.23</v>
+      </c>
+      <c r="W6">
+        <v>0.035189</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>24.67095439197524</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1050033096353712</v>
+      </c>
+      <c r="C7">
+        <v>399.9709721305177</v>
+      </c>
+      <c r="D7">
+        <v>382.2359721305177</v>
+      </c>
+      <c r="E7">
+        <v>-59.035</v>
+      </c>
+      <c r="F7">
+        <v>21.065</v>
+      </c>
+      <c r="G7">
+        <v>38.8</v>
+      </c>
+      <c r="H7">
+        <v>341.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>28.6</v>
+      </c>
+      <c r="K7">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L7">
+        <v>19</v>
+      </c>
+      <c r="M7">
+        <v>0.9626705</v>
+      </c>
+      <c r="N7">
+        <v>18.0373295</v>
+      </c>
+      <c r="O7">
+        <v>4.148585784999999</v>
+      </c>
+      <c r="P7">
+        <v>13.888743715</v>
+      </c>
+      <c r="Q7">
+        <v>23.488743715</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1086777469846013</v>
+      </c>
+      <c r="T7">
+        <v>0.9798616189410845</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.23</v>
+      </c>
+      <c r="W7">
+        <v>0.035189</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>19.73676351358019</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1048127404778989</v>
+      </c>
+      <c r="C8">
+        <v>396.861431654197</v>
+      </c>
+      <c r="D8">
+        <v>383.339431654197</v>
+      </c>
+      <c r="E8">
+        <v>-54.822</v>
+      </c>
+      <c r="F8">
+        <v>25.278</v>
+      </c>
+      <c r="G8">
+        <v>38.8</v>
+      </c>
+      <c r="H8">
+        <v>341.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>28.6</v>
+      </c>
+      <c r="K8">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L8">
+        <v>19</v>
+      </c>
+      <c r="M8">
+        <v>1.1552046</v>
+      </c>
+      <c r="N8">
+        <v>17.8447954</v>
+      </c>
+      <c r="O8">
+        <v>4.104302941999999</v>
+      </c>
+      <c r="P8">
+        <v>13.740492458</v>
+      </c>
+      <c r="Q8">
+        <v>23.340492458</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1092568090190414</v>
+      </c>
+      <c r="T8">
+        <v>0.9879815238753242</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.23</v>
+      </c>
+      <c r="W8">
+        <v>0.035189</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>16.44730292798349</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1046221713204266</v>
+      </c>
+      <c r="C9">
+        <v>393.7582806769622</v>
+      </c>
+      <c r="D9">
+        <v>384.4492806769621</v>
+      </c>
+      <c r="E9">
+        <v>-50.60899999999999</v>
+      </c>
+      <c r="F9">
+        <v>29.491</v>
+      </c>
+      <c r="G9">
+        <v>38.8</v>
+      </c>
+      <c r="H9">
+        <v>341.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>28.6</v>
+      </c>
+      <c r="K9">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L9">
+        <v>19</v>
+      </c>
+      <c r="M9">
+        <v>1.3477387</v>
+      </c>
+      <c r="N9">
+        <v>17.6522613</v>
+      </c>
+      <c r="O9">
+        <v>4.060020099</v>
+      </c>
+      <c r="P9">
+        <v>13.592241201</v>
+      </c>
+      <c r="Q9">
+        <v>23.192241201</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1098483240004587</v>
+      </c>
+      <c r="T9">
+        <v>0.9962760504210532</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.23</v>
+      </c>
+      <c r="W9">
+        <v>0.035189</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>14.09768822398585</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1045301621629544</v>
+      </c>
+      <c r="C10">
+        <v>390.0834332273576</v>
+      </c>
+      <c r="D10">
+        <v>384.9874332273576</v>
+      </c>
+      <c r="E10">
+        <v>-46.396</v>
+      </c>
+      <c r="F10">
+        <v>33.70399999999999</v>
+      </c>
+      <c r="G10">
+        <v>38.8</v>
+      </c>
+      <c r="H10">
+        <v>341.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>28.6</v>
+      </c>
+      <c r="K10">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L10">
+        <v>19</v>
+      </c>
+      <c r="M10">
+        <v>1.5941992</v>
+      </c>
+      <c r="N10">
+        <v>17.4058008</v>
+      </c>
+      <c r="O10">
+        <v>4.003334184</v>
+      </c>
+      <c r="P10">
+        <v>13.402466616</v>
+      </c>
+      <c r="Q10">
+        <v>23.002466616</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1104526980032113</v>
+      </c>
+      <c r="T10">
+        <v>1.004750892761255</v>
+      </c>
+      <c r="U10">
+        <v>0.0473</v>
+      </c>
+      <c r="V10">
+        <v>0.23</v>
+      </c>
+      <c r="W10">
+        <v>0.036421</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>11.91820946842779</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1043519130054821</v>
+      </c>
+      <c r="C11">
+        <v>386.9172933793177</v>
+      </c>
+      <c r="D11">
+        <v>386.0342933793177</v>
+      </c>
+      <c r="E11">
+        <v>-42.183</v>
+      </c>
+      <c r="F11">
+        <v>37.91699999999999</v>
+      </c>
+      <c r="G11">
+        <v>38.8</v>
+      </c>
+      <c r="H11">
+        <v>341.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>28.6</v>
+      </c>
+      <c r="K11">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L11">
+        <v>19</v>
+      </c>
+      <c r="M11">
+        <v>1.7934741</v>
+      </c>
+      <c r="N11">
+        <v>17.2065259</v>
+      </c>
+      <c r="O11">
+        <v>3.957500956999999</v>
+      </c>
+      <c r="P11">
+        <v>13.249024943</v>
+      </c>
+      <c r="Q11">
+        <v>22.849024943</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1110703549510792</v>
+      </c>
+      <c r="T11">
+        <v>1.013411995372669</v>
+      </c>
+      <c r="U11">
+        <v>0.0473</v>
+      </c>
+      <c r="V11">
+        <v>0.23</v>
+      </c>
+      <c r="W11">
+        <v>0.036421</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>10.59396397193581</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1044662638480098</v>
+      </c>
+      <c r="C12">
+        <v>382.0320555496357</v>
+      </c>
+      <c r="D12">
+        <v>385.3620555496357</v>
+      </c>
+      <c r="E12">
+        <v>-37.97</v>
+      </c>
+      <c r="F12">
+        <v>42.13</v>
+      </c>
+      <c r="G12">
+        <v>38.8</v>
+      </c>
+      <c r="H12">
+        <v>341.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>28.6</v>
+      </c>
+      <c r="K12">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L12">
+        <v>19</v>
+      </c>
+      <c r="M12">
+        <v>2.152843</v>
+      </c>
+      <c r="N12">
+        <v>16.847157</v>
+      </c>
+      <c r="O12">
+        <v>3.87484611</v>
+      </c>
+      <c r="P12">
+        <v>12.97231089</v>
+      </c>
+      <c r="Q12">
+        <v>22.57231089</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1117017376088998</v>
+      </c>
+      <c r="T12">
+        <v>1.022265566931004</v>
+      </c>
+      <c r="U12">
+        <v>0.0511</v>
+      </c>
+      <c r="V12">
+        <v>0.23</v>
+      </c>
+      <c r="W12">
+        <v>0.039347</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>8.825539066248677</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1043172746905375</v>
+      </c>
+      <c r="C13">
+        <v>378.6953857732189</v>
+      </c>
+      <c r="D13">
+        <v>386.2383857732189</v>
+      </c>
+      <c r="E13">
+        <v>-33.757</v>
+      </c>
+      <c r="F13">
+        <v>46.343</v>
+      </c>
+      <c r="G13">
+        <v>38.8</v>
+      </c>
+      <c r="H13">
+        <v>341.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>28.6</v>
+      </c>
+      <c r="K13">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L13">
+        <v>19</v>
+      </c>
+      <c r="M13">
+        <v>2.3681273</v>
+      </c>
+      <c r="N13">
+        <v>16.6318727</v>
+      </c>
+      <c r="O13">
+        <v>3.825330720999999</v>
+      </c>
+      <c r="P13">
+        <v>12.806541979</v>
+      </c>
+      <c r="Q13">
+        <v>22.406541979</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1123473086410534</v>
+      </c>
+      <c r="T13">
+        <v>1.031318095153571</v>
+      </c>
+      <c r="U13">
+        <v>0.0511</v>
+      </c>
+      <c r="V13">
+        <v>0.23</v>
+      </c>
+      <c r="W13">
+        <v>0.039347</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>8.023217332953344</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1043438455330652</v>
+      </c>
+      <c r="C14">
+        <v>374.3258084585516</v>
+      </c>
+      <c r="D14">
+        <v>386.0818084585516</v>
+      </c>
+      <c r="E14">
+        <v>-29.544</v>
+      </c>
+      <c r="F14">
+        <v>50.55599999999999</v>
+      </c>
+      <c r="G14">
+        <v>38.8</v>
+      </c>
+      <c r="H14">
+        <v>341.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>28.6</v>
+      </c>
+      <c r="K14">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L14">
+        <v>19</v>
+      </c>
+      <c r="M14">
+        <v>2.679468</v>
+      </c>
+      <c r="N14">
+        <v>16.320532</v>
+      </c>
+      <c r="O14">
+        <v>3.75372236</v>
+      </c>
+      <c r="P14">
+        <v>12.56680964</v>
+      </c>
+      <c r="Q14">
+        <v>22.16680964</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1130075517421196</v>
+      </c>
+      <c r="T14">
+        <v>1.040576362653924</v>
+      </c>
+      <c r="U14">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V14">
+        <v>0.23</v>
+      </c>
+      <c r="W14">
+        <v>0.04081000000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>7.090959847253261</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1042094863755929</v>
+      </c>
+      <c r="C15">
+        <v>370.9058681410876</v>
+      </c>
+      <c r="D15">
+        <v>386.8748681410876</v>
+      </c>
+      <c r="E15">
+        <v>-25.331</v>
+      </c>
+      <c r="F15">
+        <v>54.769</v>
+      </c>
+      <c r="G15">
+        <v>38.8</v>
+      </c>
+      <c r="H15">
+        <v>341.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>28.6</v>
+      </c>
+      <c r="K15">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L15">
+        <v>19</v>
+      </c>
+      <c r="M15">
+        <v>2.902757</v>
+      </c>
+      <c r="N15">
+        <v>16.097243</v>
+      </c>
+      <c r="O15">
+        <v>3.702365889999999</v>
+      </c>
+      <c r="P15">
+        <v>12.39487711</v>
+      </c>
+      <c r="Q15">
+        <v>21.99487711</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1136829728455091</v>
+      </c>
+      <c r="T15">
+        <v>1.050047463889916</v>
+      </c>
+      <c r="U15">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V15">
+        <v>0.23</v>
+      </c>
+      <c r="W15">
+        <v>0.04081000000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>6.545501397464547</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1042907272181207</v>
+      </c>
+      <c r="C16">
+        <v>366.2129522571807</v>
+      </c>
+      <c r="D16">
+        <v>386.3949522571808</v>
+      </c>
+      <c r="E16">
+        <v>-21.11799999999999</v>
+      </c>
+      <c r="F16">
+        <v>58.982</v>
+      </c>
+      <c r="G16">
+        <v>38.8</v>
+      </c>
+      <c r="H16">
+        <v>341.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>28.6</v>
+      </c>
+      <c r="K16">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L16">
+        <v>19</v>
+      </c>
+      <c r="M16">
+        <v>3.24401</v>
+      </c>
+      <c r="N16">
+        <v>15.75599</v>
+      </c>
+      <c r="O16">
+        <v>3.6238777</v>
+      </c>
+      <c r="P16">
+        <v>12.1321123</v>
+      </c>
+      <c r="Q16">
+        <v>21.7321123</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1143741014164194</v>
+      </c>
+      <c r="T16">
+        <v>1.059738823294188</v>
+      </c>
+      <c r="U16">
+        <v>0.055</v>
+      </c>
+      <c r="V16">
+        <v>0.23</v>
+      </c>
+      <c r="W16">
+        <v>0.04235</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>5.85694865305594</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1041717680606484</v>
+      </c>
+      <c r="C17">
+        <v>362.7030878665683</v>
+      </c>
+      <c r="D17">
+        <v>387.0980878665683</v>
+      </c>
+      <c r="E17">
+        <v>-16.905</v>
+      </c>
+      <c r="F17">
+        <v>63.19499999999999</v>
+      </c>
+      <c r="G17">
+        <v>38.8</v>
+      </c>
+      <c r="H17">
+        <v>341.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>28.6</v>
+      </c>
+      <c r="K17">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L17">
+        <v>19</v>
+      </c>
+      <c r="M17">
+        <v>3.475725</v>
+      </c>
+      <c r="N17">
+        <v>15.524275</v>
+      </c>
+      <c r="O17">
+        <v>3.570583249999999</v>
+      </c>
+      <c r="P17">
+        <v>11.95369175</v>
+      </c>
+      <c r="Q17">
+        <v>21.55369175</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1150814918360569</v>
+      </c>
+      <c r="T17">
+        <v>1.069658214684443</v>
+      </c>
+      <c r="U17">
+        <v>0.055</v>
+      </c>
+      <c r="V17">
+        <v>0.23</v>
+      </c>
+      <c r="W17">
+        <v>0.04235</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>5.466485409518878</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1040528089031761</v>
+      </c>
+      <c r="C18">
+        <v>359.1957871792227</v>
+      </c>
+      <c r="D18">
+        <v>387.8037871792227</v>
+      </c>
+      <c r="E18">
+        <v>-12.69200000000001</v>
+      </c>
+      <c r="F18">
+        <v>67.40799999999999</v>
+      </c>
+      <c r="G18">
+        <v>38.8</v>
+      </c>
+      <c r="H18">
+        <v>341.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>28.6</v>
+      </c>
+      <c r="K18">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L18">
+        <v>19</v>
+      </c>
+      <c r="M18">
+        <v>3.707439999999999</v>
+      </c>
+      <c r="N18">
+        <v>15.29256</v>
+      </c>
+      <c r="O18">
+        <v>3.5172888</v>
+      </c>
+      <c r="P18">
+        <v>11.7752712</v>
+      </c>
+      <c r="Q18">
+        <v>21.3752712</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1158057248847334</v>
+      </c>
+      <c r="T18">
+        <v>1.07981378206018</v>
+      </c>
+      <c r="U18">
+        <v>0.055</v>
+      </c>
+      <c r="V18">
+        <v>0.23</v>
+      </c>
+      <c r="W18">
+        <v>0.04235</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>5.124830071423949</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1039338497457038</v>
+      </c>
+      <c r="C19">
+        <v>355.6910642420328</v>
+      </c>
+      <c r="D19">
+        <v>388.5120642420327</v>
+      </c>
+      <c r="E19">
+        <v>-8.478999999999999</v>
+      </c>
+      <c r="F19">
+        <v>71.621</v>
+      </c>
+      <c r="G19">
+        <v>38.8</v>
+      </c>
+      <c r="H19">
+        <v>341.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>28.6</v>
+      </c>
+      <c r="K19">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L19">
+        <v>19</v>
+      </c>
+      <c r="M19">
+        <v>3.939155</v>
+      </c>
+      <c r="N19">
+        <v>15.060845</v>
+      </c>
+      <c r="O19">
+        <v>3.46399435</v>
+      </c>
+      <c r="P19">
+        <v>11.59685065</v>
+      </c>
+      <c r="Q19">
+        <v>21.19685065</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1165474093321732</v>
+      </c>
+      <c r="T19">
+        <v>1.090214061902802</v>
+      </c>
+      <c r="U19">
+        <v>0.055</v>
+      </c>
+      <c r="V19">
+        <v>0.23</v>
+      </c>
+      <c r="W19">
+        <v>0.04235</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>4.823369478987245</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1038148905882315</v>
+      </c>
+      <c r="C20">
+        <v>352.188933204695</v>
+      </c>
+      <c r="D20">
+        <v>389.222933204695</v>
+      </c>
+      <c r="E20">
+        <v>-4.266000000000005</v>
+      </c>
+      <c r="F20">
+        <v>75.83399999999999</v>
+      </c>
+      <c r="G20">
+        <v>38.8</v>
+      </c>
+      <c r="H20">
+        <v>341.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>28.6</v>
+      </c>
+      <c r="K20">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L20">
+        <v>19</v>
+      </c>
+      <c r="M20">
+        <v>4.17087</v>
+      </c>
+      <c r="N20">
+        <v>14.82913</v>
+      </c>
+      <c r="O20">
+        <v>3.4106999</v>
+      </c>
+      <c r="P20">
+        <v>11.4184301</v>
+      </c>
+      <c r="Q20">
+        <v>21.0184301</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1173071836441847</v>
+      </c>
+      <c r="T20">
+        <v>1.100868007107439</v>
+      </c>
+      <c r="U20">
+        <v>0.055</v>
+      </c>
+      <c r="V20">
+        <v>0.23</v>
+      </c>
+      <c r="W20">
+        <v>0.04235</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>4.555404507932398</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1042518714307592</v>
+      </c>
+      <c r="C21">
+        <v>345.3773372965118</v>
+      </c>
+      <c r="D21">
+        <v>386.6243372965118</v>
+      </c>
+      <c r="E21">
+        <v>-0.05299999999999727</v>
+      </c>
+      <c r="F21">
+        <v>80.047</v>
+      </c>
+      <c r="G21">
+        <v>38.8</v>
+      </c>
+      <c r="H21">
+        <v>341.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>28.6</v>
+      </c>
+      <c r="K21">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L21">
+        <v>19</v>
+      </c>
+      <c r="M21">
+        <v>4.7067636</v>
+      </c>
+      <c r="N21">
+        <v>14.2932364</v>
+      </c>
+      <c r="O21">
+        <v>3.287444372</v>
+      </c>
+      <c r="P21">
+        <v>11.005792028</v>
+      </c>
+      <c r="Q21">
+        <v>20.605792028</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1180857178157521</v>
+      </c>
+      <c r="T21">
+        <v>1.1117850126875</v>
+      </c>
+      <c r="U21">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V21">
+        <v>0.23</v>
+      </c>
+      <c r="W21">
+        <v>0.045276</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>4.036744059123768</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1048089722732869</v>
+      </c>
+      <c r="C22">
+        <v>337.9013150643543</v>
+      </c>
+      <c r="D22">
+        <v>383.3613150643542</v>
+      </c>
+      <c r="E22">
+        <v>4.159999999999997</v>
+      </c>
+      <c r="F22">
+        <v>84.25999999999999</v>
+      </c>
+      <c r="G22">
+        <v>38.8</v>
+      </c>
+      <c r="H22">
+        <v>341.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>28.6</v>
+      </c>
+      <c r="K22">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L22">
+        <v>19</v>
+      </c>
+      <c r="M22">
+        <v>5.30838</v>
+      </c>
+      <c r="N22">
+        <v>13.69162</v>
+      </c>
+      <c r="O22">
+        <v>3.1490726</v>
+      </c>
+      <c r="P22">
+        <v>10.5425474</v>
+      </c>
+      <c r="Q22">
+        <v>20.1425474</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1188837153416087</v>
+      </c>
+      <c r="T22">
+        <v>1.122974943407062</v>
+      </c>
+      <c r="U22">
+        <v>0.063</v>
+      </c>
+      <c r="V22">
+        <v>0.23</v>
+      </c>
+      <c r="W22">
+        <v>0.04851</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>3.579246399089741</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1058996831158147</v>
+      </c>
+      <c r="C23">
+        <v>327.4567455020261</v>
+      </c>
+      <c r="D23">
+        <v>377.1297455020261</v>
+      </c>
+      <c r="E23">
+        <v>8.37299999999999</v>
+      </c>
+      <c r="F23">
+        <v>88.47299999999998</v>
+      </c>
+      <c r="G23">
+        <v>38.8</v>
+      </c>
+      <c r="H23">
+        <v>341.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>28.6</v>
+      </c>
+      <c r="K23">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L23">
+        <v>19</v>
+      </c>
+      <c r="M23">
+        <v>6.201957299999998</v>
+      </c>
+      <c r="N23">
+        <v>12.7980427</v>
+      </c>
+      <c r="O23">
+        <v>2.943549821</v>
+      </c>
+      <c r="P23">
+        <v>9.854492879000002</v>
+      </c>
+      <c r="Q23">
+        <v>19.454492879</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1197019153364742</v>
+      </c>
+      <c r="T23">
+        <v>1.13444816351193</v>
+      </c>
+      <c r="U23">
+        <v>0.0701</v>
+      </c>
+      <c r="V23">
+        <v>0.23</v>
+      </c>
+      <c r="W23">
+        <v>0.053977</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>3.06354898638209</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1095052139583424</v>
+      </c>
+      <c r="C24">
+        <v>304.0124490683103</v>
+      </c>
+      <c r="D24">
+        <v>357.8984490683103</v>
+      </c>
+      <c r="E24">
+        <v>12.586</v>
+      </c>
+      <c r="F24">
+        <v>92.68599999999999</v>
+      </c>
+      <c r="G24">
+        <v>38.8</v>
+      </c>
+      <c r="H24">
+        <v>341.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>28.6</v>
+      </c>
+      <c r="K24">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L24">
+        <v>19</v>
+      </c>
+      <c r="M24">
+        <v>8.4715004</v>
+      </c>
+      <c r="N24">
+        <v>10.5284996</v>
+      </c>
+      <c r="O24">
+        <v>2.421554908</v>
+      </c>
+      <c r="P24">
+        <v>8.106944692000001</v>
+      </c>
+      <c r="Q24">
+        <v>17.706944692</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1205410948183877</v>
+      </c>
+      <c r="T24">
+        <v>1.146215568747691</v>
+      </c>
+      <c r="U24">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V24">
+        <v>0.23</v>
+      </c>
+      <c r="W24">
+        <v>0.07037800000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>2.242814035634113</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1096665348008701</v>
+      </c>
+      <c r="C25">
+        <v>298.9847277120976</v>
+      </c>
+      <c r="D25">
+        <v>357.0837277120976</v>
+      </c>
+      <c r="E25">
+        <v>16.79899999999999</v>
+      </c>
+      <c r="F25">
+        <v>96.89899999999999</v>
+      </c>
+      <c r="G25">
+        <v>38.8</v>
+      </c>
+      <c r="H25">
+        <v>341.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>28.6</v>
+      </c>
+      <c r="K25">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L25">
+        <v>19</v>
+      </c>
+      <c r="M25">
+        <v>8.856568599999999</v>
+      </c>
+      <c r="N25">
+        <v>10.1434314</v>
+      </c>
+      <c r="O25">
+        <v>2.332989222</v>
+      </c>
+      <c r="P25">
+        <v>7.810442178000001</v>
+      </c>
+      <c r="Q25">
+        <v>17.410442178</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1214020711699611</v>
+      </c>
+      <c r="T25">
+        <v>1.158288620872693</v>
+      </c>
+      <c r="U25">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V25">
+        <v>0.23</v>
+      </c>
+      <c r="W25">
+        <v>0.07037800000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>2.145300381910891</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1098278556433978</v>
+      </c>
+      <c r="C26">
+        <v>293.960707200699</v>
+      </c>
+      <c r="D26">
+        <v>356.272707200699</v>
+      </c>
+      <c r="E26">
+        <v>21.01199999999999</v>
+      </c>
+      <c r="F26">
+        <v>101.112</v>
+      </c>
+      <c r="G26">
+        <v>38.8</v>
+      </c>
+      <c r="H26">
+        <v>341.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>28.6</v>
+      </c>
+      <c r="K26">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L26">
+        <v>19</v>
+      </c>
+      <c r="M26">
+        <v>9.241636799999998</v>
+      </c>
+      <c r="N26">
+        <v>9.758363200000002</v>
+      </c>
+      <c r="O26">
+        <v>2.244423536</v>
+      </c>
+      <c r="P26">
+        <v>7.513939664000001</v>
+      </c>
+      <c r="Q26">
+        <v>17.113939664</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1222857047939445</v>
+      </c>
+      <c r="T26">
+        <v>1.170679384895722</v>
+      </c>
+      <c r="U26">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V26">
+        <v>0.23</v>
+      </c>
+      <c r="W26">
+        <v>0.07037800000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>2.055912865997937</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1140509264859255</v>
+      </c>
+      <c r="C27">
+        <v>269.7537356706729</v>
+      </c>
+      <c r="D27">
+        <v>336.2787356706729</v>
+      </c>
+      <c r="E27">
+        <v>25.22499999999999</v>
+      </c>
+      <c r="F27">
+        <v>105.325</v>
+      </c>
+      <c r="G27">
+        <v>38.8</v>
+      </c>
+      <c r="H27">
+        <v>341.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>28.6</v>
+      </c>
+      <c r="K27">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L27">
+        <v>19</v>
+      </c>
+      <c r="M27">
+        <v>11.8490625</v>
+      </c>
+      <c r="N27">
+        <v>7.150937500000001</v>
+      </c>
+      <c r="O27">
+        <v>1.644715625</v>
+      </c>
+      <c r="P27">
+        <v>5.506221875000001</v>
+      </c>
+      <c r="Q27">
+        <v>15.106221875</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.123192901981234</v>
+      </c>
+      <c r="T27">
+        <v>1.183400569292697</v>
+      </c>
+      <c r="U27">
+        <v>0.1125</v>
+      </c>
+      <c r="V27">
+        <v>0.23</v>
+      </c>
+      <c r="W27">
+        <v>0.08662500000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>1.603502386792204</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1143747173284532</v>
+      </c>
+      <c r="C28">
+        <v>264.0999896249583</v>
+      </c>
+      <c r="D28">
+        <v>334.8379896249583</v>
+      </c>
+      <c r="E28">
+        <v>29.438</v>
+      </c>
+      <c r="F28">
+        <v>109.538</v>
+      </c>
+      <c r="G28">
+        <v>38.8</v>
+      </c>
+      <c r="H28">
+        <v>341.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>28.6</v>
+      </c>
+      <c r="K28">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L28">
+        <v>19</v>
+      </c>
+      <c r="M28">
+        <v>12.323025</v>
+      </c>
+      <c r="N28">
+        <v>6.676975000000001</v>
+      </c>
+      <c r="O28">
+        <v>1.53570425</v>
+      </c>
+      <c r="P28">
+        <v>5.14127075</v>
+      </c>
+      <c r="Q28">
+        <v>14.74127075</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1241246180114233</v>
+      </c>
+      <c r="T28">
+        <v>1.196465569484186</v>
+      </c>
+      <c r="U28">
+        <v>0.1125</v>
+      </c>
+      <c r="V28">
+        <v>0.23</v>
+      </c>
+      <c r="W28">
+        <v>0.08662500000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>1.541829218069427</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1346463269125028</v>
+      </c>
+      <c r="C29">
+        <v>189.0683654978008</v>
+      </c>
+      <c r="D29">
+        <v>264.0193654978008</v>
+      </c>
+      <c r="E29">
+        <v>33.651</v>
+      </c>
+      <c r="F29">
+        <v>113.751</v>
+      </c>
+      <c r="G29">
+        <v>38.8</v>
+      </c>
+      <c r="H29">
+        <v>341.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>28.6</v>
+      </c>
+      <c r="K29">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L29">
+        <v>19</v>
+      </c>
+      <c r="M29">
+        <v>22.3634466</v>
+      </c>
+      <c r="N29">
+        <v>-3.363446599999996</v>
+      </c>
+      <c r="O29">
+        <v>-0.7735927179999991</v>
+      </c>
+      <c r="P29">
+        <v>-2.589853881999997</v>
+      </c>
+      <c r="Q29">
+        <v>7.010146118000004</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1259410725713218</v>
+      </c>
+      <c r="T29">
+        <v>1.221936827253662</v>
+      </c>
+      <c r="U29">
+        <v>0.1966</v>
+      </c>
+      <c r="V29">
+        <v>0.1954081621747875</v>
+      </c>
+      <c r="W29">
+        <v>0.1581827553164368</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.8496007051077719</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1362243269125028</v>
+      </c>
+      <c r="C30">
+        <v>180.5789945752724</v>
+      </c>
+      <c r="D30">
+        <v>259.7429945752723</v>
+      </c>
+      <c r="E30">
+        <v>37.864</v>
+      </c>
+      <c r="F30">
+        <v>117.964</v>
+      </c>
+      <c r="G30">
+        <v>38.8</v>
+      </c>
+      <c r="H30">
+        <v>341.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>28.6</v>
+      </c>
+      <c r="K30">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L30">
+        <v>19</v>
+      </c>
+      <c r="M30">
+        <v>23.1917224</v>
+      </c>
+      <c r="N30">
+        <v>-4.1917224</v>
+      </c>
+      <c r="O30">
+        <v>-0.9640961519999999</v>
+      </c>
+      <c r="P30">
+        <v>-3.227626248</v>
+      </c>
+      <c r="Q30">
+        <v>6.372373752000001</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1271513652459234</v>
+      </c>
+      <c r="T30">
+        <v>1.23890817207663</v>
+      </c>
+      <c r="U30">
+        <v>0.1966</v>
+      </c>
+      <c r="V30">
+        <v>0.1884292992399736</v>
+      </c>
+      <c r="W30">
+        <v>0.1595547997694212</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.8192578227824941</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1430753716555593</v>
+      </c>
+      <c r="C31">
+        <v>159.3004991540839</v>
+      </c>
+      <c r="D31">
+        <v>242.6774991540838</v>
+      </c>
+      <c r="E31">
+        <v>42.07699999999998</v>
+      </c>
+      <c r="F31">
+        <v>122.177</v>
+      </c>
+      <c r="G31">
+        <v>38.8</v>
+      </c>
+      <c r="H31">
+        <v>341.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>28.6</v>
+      </c>
+      <c r="K31">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L31">
+        <v>19</v>
+      </c>
+      <c r="M31">
+        <v>26.12144259999999</v>
+      </c>
+      <c r="N31">
+        <v>-7.121442599999995</v>
+      </c>
+      <c r="O31">
+        <v>-1.637931797999999</v>
+      </c>
+      <c r="P31">
+        <v>-5.483510801999996</v>
+      </c>
+      <c r="Q31">
+        <v>4.116489198000005</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1287972221410161</v>
+      </c>
+      <c r="T31">
+        <v>1.261987221865202</v>
+      </c>
+      <c r="U31">
+        <v>0.2138</v>
+      </c>
+      <c r="V31">
+        <v>0.1672955076378516</v>
+      </c>
+      <c r="W31">
+        <v>0.1780322204670274</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.7273717723384849</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1448253716555593</v>
+      </c>
+      <c r="C32">
+        <v>151.081989747342</v>
+      </c>
+      <c r="D32">
+        <v>238.671989747342</v>
+      </c>
+      <c r="E32">
+        <v>46.28999999999999</v>
+      </c>
+      <c r="F32">
+        <v>126.39</v>
+      </c>
+      <c r="G32">
+        <v>38.8</v>
+      </c>
+      <c r="H32">
+        <v>341.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>28.6</v>
+      </c>
+      <c r="K32">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L32">
+        <v>19</v>
+      </c>
+      <c r="M32">
+        <v>27.022182</v>
+      </c>
+      <c r="N32">
+        <v>-8.022181999999997</v>
+      </c>
+      <c r="O32">
+        <v>-1.845101859999999</v>
+      </c>
+      <c r="P32">
+        <v>-6.177080139999997</v>
+      </c>
+      <c r="Q32">
+        <v>3.422919860000004</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1300828967430306</v>
+      </c>
+      <c r="T32">
+        <v>1.28001561074899</v>
+      </c>
+      <c r="U32">
+        <v>0.2138</v>
+      </c>
+      <c r="V32">
+        <v>0.1617189907165898</v>
+      </c>
+      <c r="W32">
+        <v>0.1792244797847931</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.7031260465938688</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1465753716555593</v>
+      </c>
+      <c r="C33">
+        <v>142.993559065528</v>
+      </c>
+      <c r="D33">
+        <v>234.796559065528</v>
+      </c>
+      <c r="E33">
+        <v>50.50299999999999</v>
+      </c>
+      <c r="F33">
+        <v>130.603</v>
+      </c>
+      <c r="G33">
+        <v>38.8</v>
+      </c>
+      <c r="H33">
+        <v>341.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>28.6</v>
+      </c>
+      <c r="K33">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L33">
+        <v>19</v>
+      </c>
+      <c r="M33">
+        <v>27.92292139999999</v>
+      </c>
+      <c r="N33">
+        <v>-8.922921399999993</v>
+      </c>
+      <c r="O33">
+        <v>-2.052271921999998</v>
+      </c>
+      <c r="P33">
+        <v>-6.870649477999994</v>
+      </c>
+      <c r="Q33">
+        <v>2.729350522000007</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1314058372755383</v>
+      </c>
+      <c r="T33">
+        <v>1.29856656162941</v>
+      </c>
+      <c r="U33">
+        <v>0.2138</v>
+      </c>
+      <c r="V33">
+        <v>0.1565022490805708</v>
+      </c>
+      <c r="W33">
+        <v>0.180339819146574</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.6804445612198731</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1483253716555593</v>
+      </c>
+      <c r="C34">
+        <v>135.0289719021732</v>
+      </c>
+      <c r="D34">
+        <v>231.0449719021732</v>
+      </c>
+      <c r="E34">
+        <v>54.71599999999998</v>
+      </c>
+      <c r="F34">
+        <v>134.816</v>
+      </c>
+      <c r="G34">
+        <v>38.8</v>
+      </c>
+      <c r="H34">
+        <v>341.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>28.6</v>
+      </c>
+      <c r="K34">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L34">
+        <v>19</v>
+      </c>
+      <c r="M34">
+        <v>28.82366079999999</v>
+      </c>
+      <c r="N34">
+        <v>-9.823660799999992</v>
+      </c>
+      <c r="O34">
+        <v>-2.259441983999998</v>
+      </c>
+      <c r="P34">
+        <v>-7.564218815999994</v>
+      </c>
+      <c r="Q34">
+        <v>2.035781184000007</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.132767687823708</v>
+      </c>
+      <c r="T34">
+        <v>1.317663128712195</v>
+      </c>
+      <c r="U34">
+        <v>0.2138</v>
+      </c>
+      <c r="V34">
+        <v>0.151611553796803</v>
+      </c>
+      <c r="W34">
+        <v>0.1813854497982435</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.6591806686817521</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1500753716555593</v>
+      </c>
+      <c r="C35">
+        <v>127.1823852889524</v>
+      </c>
+      <c r="D35">
+        <v>227.4113852889525</v>
+      </c>
+      <c r="E35">
+        <v>58.929</v>
+      </c>
+      <c r="F35">
+        <v>139.029</v>
+      </c>
+      <c r="G35">
+        <v>38.8</v>
+      </c>
+      <c r="H35">
+        <v>341.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>28.6</v>
+      </c>
+      <c r="K35">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L35">
+        <v>19</v>
+      </c>
+      <c r="M35">
+        <v>29.7244002</v>
+      </c>
+      <c r="N35">
+        <v>-10.7244002</v>
+      </c>
+      <c r="O35">
+        <v>-2.466612045999999</v>
+      </c>
+      <c r="P35">
+        <v>-8.257788153999998</v>
+      </c>
+      <c r="Q35">
+        <v>1.342211846000003</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1341701906270469</v>
+      </c>
+      <c r="T35">
+        <v>1.337329742573572</v>
+      </c>
+      <c r="U35">
+        <v>0.2138</v>
+      </c>
+      <c r="V35">
+        <v>0.1470172642878089</v>
+      </c>
+      <c r="W35">
+        <v>0.1823677088952664</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.639205496903517</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1518253716555593</v>
+      </c>
+      <c r="C36">
+        <v>119.4483181300807</v>
+      </c>
+      <c r="D36">
+        <v>223.8903181300807</v>
+      </c>
+      <c r="E36">
+        <v>63.142</v>
+      </c>
+      <c r="F36">
+        <v>143.242</v>
+      </c>
+      <c r="G36">
+        <v>38.8</v>
+      </c>
+      <c r="H36">
+        <v>341.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>28.6</v>
+      </c>
+      <c r="K36">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L36">
+        <v>19</v>
+      </c>
+      <c r="M36">
+        <v>30.6251396</v>
+      </c>
+      <c r="N36">
+        <v>-11.6251396</v>
+      </c>
+      <c r="O36">
+        <v>-2.673782107999999</v>
+      </c>
+      <c r="P36">
+        <v>-8.951357491999998</v>
+      </c>
+      <c r="Q36">
+        <v>0.6486425080000036</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1356151935153355</v>
+      </c>
+      <c r="T36">
+        <v>1.357592314430747</v>
+      </c>
+      <c r="U36">
+        <v>0.2138</v>
+      </c>
+      <c r="V36">
+        <v>0.1426932271028734</v>
+      </c>
+      <c r="W36">
+        <v>0.1832921880454057</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.6204053352298842</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1535753716555593</v>
+      </c>
+      <c r="C37">
+        <v>111.8216236146453</v>
+      </c>
+      <c r="D37">
+        <v>220.4766236146453</v>
+      </c>
+      <c r="E37">
+        <v>67.35499999999999</v>
+      </c>
+      <c r="F37">
+        <v>147.455</v>
+      </c>
+      <c r="G37">
+        <v>38.8</v>
+      </c>
+      <c r="H37">
+        <v>341.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>28.6</v>
+      </c>
+      <c r="K37">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L37">
+        <v>19</v>
+      </c>
+      <c r="M37">
+        <v>31.525879</v>
+      </c>
+      <c r="N37">
+        <v>-12.525879</v>
+      </c>
+      <c r="O37">
+        <v>-2.880952169999999</v>
+      </c>
+      <c r="P37">
+        <v>-9.644926829999998</v>
+      </c>
+      <c r="Q37">
+        <v>-0.04492682999999609</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.137104658030956</v>
+      </c>
+      <c r="T37">
+        <v>1.378478350037374</v>
+      </c>
+      <c r="U37">
+        <v>0.2138</v>
+      </c>
+      <c r="V37">
+        <v>0.138616277757077</v>
+      </c>
+      <c r="W37">
+        <v>0.1841638398155369</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.6026794685090304</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1553253716555593</v>
+      </c>
+      <c r="C38">
+        <v>104.2974641148402</v>
+      </c>
+      <c r="D38">
+        <v>217.1654641148401</v>
+      </c>
+      <c r="E38">
+        <v>71.56799999999998</v>
+      </c>
+      <c r="F38">
+        <v>151.668</v>
+      </c>
+      <c r="G38">
+        <v>38.8</v>
+      </c>
+      <c r="H38">
+        <v>341.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>28.6</v>
+      </c>
+      <c r="K38">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L38">
+        <v>19</v>
+      </c>
+      <c r="M38">
+        <v>32.4266184</v>
+      </c>
+      <c r="N38">
+        <v>-13.4266184</v>
+      </c>
+      <c r="O38">
+        <v>-3.088122231999999</v>
+      </c>
+      <c r="P38">
+        <v>-10.338496168</v>
+      </c>
+      <c r="Q38">
+        <v>-0.7384961679999957</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1386406683126897</v>
+      </c>
+      <c r="T38">
+        <v>1.400017074256708</v>
+      </c>
+      <c r="U38">
+        <v>0.2138</v>
+      </c>
+      <c r="V38">
+        <v>0.1347658255971582</v>
+      </c>
+      <c r="W38">
+        <v>0.1849870664873276</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.5859383721615573</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1570753716555593</v>
+      </c>
+      <c r="C39">
+        <v>96.87128831263072</v>
+      </c>
+      <c r="D39">
+        <v>213.9522883126307</v>
+      </c>
+      <c r="E39">
+        <v>75.78099999999998</v>
+      </c>
+      <c r="F39">
+        <v>155.881</v>
+      </c>
+      <c r="G39">
+        <v>38.8</v>
+      </c>
+      <c r="H39">
+        <v>341.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>28.6</v>
+      </c>
+      <c r="K39">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L39">
+        <v>19</v>
+      </c>
+      <c r="M39">
+        <v>33.32735779999999</v>
+      </c>
+      <c r="N39">
+        <v>-14.32735779999999</v>
+      </c>
+      <c r="O39">
+        <v>-3.295292293999998</v>
+      </c>
+      <c r="P39">
+        <v>-11.032065506</v>
+      </c>
+      <c r="Q39">
+        <v>-1.432065505999994</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1402254408255895</v>
+      </c>
+      <c r="T39">
+        <v>1.422239567498878</v>
+      </c>
+      <c r="U39">
+        <v>0.2138</v>
+      </c>
+      <c r="V39">
+        <v>0.1311235059864242</v>
+      </c>
+      <c r="W39">
+        <v>0.1857657944201025</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.5701021999409748</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1588253716555593</v>
+      </c>
+      <c r="C40">
+        <v>89.53881032741293</v>
+      </c>
+      <c r="D40">
+        <v>210.8328103274129</v>
+      </c>
+      <c r="E40">
+        <v>79.994</v>
+      </c>
+      <c r="F40">
+        <v>160.094</v>
+      </c>
+      <c r="G40">
+        <v>38.8</v>
+      </c>
+      <c r="H40">
+        <v>341.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>28.6</v>
+      </c>
+      <c r="K40">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L40">
+        <v>19</v>
+      </c>
+      <c r="M40">
+        <v>34.2280972</v>
+      </c>
+      <c r="N40">
+        <v>-15.2280972</v>
+      </c>
+      <c r="O40">
+        <v>-3.502462356</v>
+      </c>
+      <c r="P40">
+        <v>-11.725634844</v>
+      </c>
+      <c r="Q40">
+        <v>-2.125634844</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1418613350324539</v>
+      </c>
+      <c r="T40">
+        <v>1.445178915361763</v>
+      </c>
+      <c r="U40">
+        <v>0.2138</v>
+      </c>
+      <c r="V40">
+        <v>0.127672887407834</v>
+      </c>
+      <c r="W40">
+        <v>0.1865035366722051</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.5550995104688436</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1605753716555594</v>
+      </c>
+      <c r="C41">
+        <v>82.29599064337557</v>
+      </c>
+      <c r="D41">
+        <v>207.8029906433756</v>
+      </c>
+      <c r="E41">
+        <v>84.20699999999999</v>
+      </c>
+      <c r="F41">
+        <v>164.307</v>
+      </c>
+      <c r="G41">
+        <v>38.8</v>
+      </c>
+      <c r="H41">
+        <v>341.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>28.6</v>
+      </c>
+      <c r="K41">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L41">
+        <v>19</v>
+      </c>
+      <c r="M41">
+        <v>35.12883659999999</v>
+      </c>
+      <c r="N41">
+        <v>-16.12883659999999</v>
+      </c>
+      <c r="O41">
+        <v>-3.709632417999998</v>
+      </c>
+      <c r="P41">
+        <v>-12.41920418199999</v>
+      </c>
+      <c r="Q41">
+        <v>-2.819204181999993</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1435508651149531</v>
+      </c>
+      <c r="T41">
+        <v>1.468870372990644</v>
+      </c>
+      <c r="U41">
+        <v>0.2138</v>
+      </c>
+      <c r="V41">
+        <v>0.124399223628146</v>
+      </c>
+      <c r="W41">
+        <v>0.1872034459883024</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.5408661896875915</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1623253716555593</v>
+      </c>
+      <c r="C42">
+        <v>75.13901865809038</v>
+      </c>
+      <c r="D42">
+        <v>204.8590186580904</v>
+      </c>
+      <c r="E42">
+        <v>88.41999999999999</v>
+      </c>
+      <c r="F42">
+        <v>168.52</v>
+      </c>
+      <c r="G42">
+        <v>38.8</v>
+      </c>
+      <c r="H42">
+        <v>341.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>28.6</v>
+      </c>
+      <c r="K42">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L42">
+        <v>19</v>
+      </c>
+      <c r="M42">
+        <v>36.02957599999999</v>
+      </c>
+      <c r="N42">
+        <v>-17.02957599999999</v>
+      </c>
+      <c r="O42">
+        <v>-3.916802479999998</v>
+      </c>
+      <c r="P42">
+        <v>-13.11277351999999</v>
+      </c>
+      <c r="Q42">
+        <v>-3.512773519999993</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.145296712866869</v>
+      </c>
+      <c r="T42">
+        <v>1.493351545873822</v>
+      </c>
+      <c r="U42">
+        <v>0.2138</v>
+      </c>
+      <c r="V42">
+        <v>0.1212892430374424</v>
+      </c>
+      <c r="W42">
+        <v>0.1878683598385948</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.5273445349454016</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1640753716555594</v>
+      </c>
+      <c r="C43">
+        <v>68.06429669379759</v>
+      </c>
+      <c r="D43">
+        <v>201.9972966937976</v>
+      </c>
+      <c r="E43">
+        <v>92.63300000000001</v>
+      </c>
+      <c r="F43">
+        <v>172.733</v>
+      </c>
+      <c r="G43">
+        <v>38.8</v>
+      </c>
+      <c r="H43">
+        <v>341.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>28.6</v>
+      </c>
+      <c r="K43">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L43">
+        <v>19</v>
+      </c>
+      <c r="M43">
+        <v>36.9303154</v>
+      </c>
+      <c r="N43">
+        <v>-17.9303154</v>
+      </c>
+      <c r="O43">
+        <v>-4.123972541999999</v>
+      </c>
+      <c r="P43">
+        <v>-13.806342858</v>
+      </c>
+      <c r="Q43">
+        <v>-4.206342857999998</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1471017418985109</v>
+      </c>
+      <c r="T43">
+        <v>1.518662589024226</v>
+      </c>
+      <c r="U43">
+        <v>0.2138</v>
+      </c>
+      <c r="V43">
+        <v>0.1183309688170169</v>
+      </c>
+      <c r="W43">
+        <v>0.1885008388669218</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.5144824731174649</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1658253716555593</v>
+      </c>
+      <c r="C44">
+        <v>61.06842533032955</v>
+      </c>
+      <c r="D44">
+        <v>199.2144253303295</v>
+      </c>
+      <c r="E44">
+        <v>96.84599999999998</v>
+      </c>
+      <c r="F44">
+        <v>176.946</v>
+      </c>
+      <c r="G44">
+        <v>38.8</v>
+      </c>
+      <c r="H44">
+        <v>341.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>28.6</v>
+      </c>
+      <c r="K44">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L44">
+        <v>19</v>
+      </c>
+      <c r="M44">
+        <v>37.83105479999999</v>
+      </c>
+      <c r="N44">
+        <v>-18.83105479999999</v>
+      </c>
+      <c r="O44">
+        <v>-4.331142603999997</v>
+      </c>
+      <c r="P44">
+        <v>-14.49991219599999</v>
+      </c>
+      <c r="Q44">
+        <v>-4.899912195999992</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1489690133105541</v>
+      </c>
+      <c r="T44">
+        <v>1.544846426766022</v>
+      </c>
+      <c r="U44">
+        <v>0.2138</v>
+      </c>
+      <c r="V44">
+        <v>0.1155135647975642</v>
+      </c>
+      <c r="W44">
+        <v>0.1891031998462808</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.5022328904241921</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1786664654267707</v>
+      </c>
+      <c r="C45">
+        <v>38.5656150570864</v>
+      </c>
+      <c r="D45">
+        <v>180.9246150570864</v>
+      </c>
+      <c r="E45">
+        <v>101.059</v>
+      </c>
+      <c r="F45">
+        <v>181.159</v>
+      </c>
+      <c r="G45">
+        <v>38.8</v>
+      </c>
+      <c r="H45">
+        <v>341.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>28.6</v>
+      </c>
+      <c r="K45">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L45">
+        <v>19</v>
+      </c>
+      <c r="M45">
+        <v>43.2607692</v>
+      </c>
+      <c r="N45">
+        <v>-24.2607692</v>
+      </c>
+      <c r="O45">
+        <v>-5.579976916</v>
+      </c>
+      <c r="P45">
+        <v>-18.680792284</v>
+      </c>
+      <c r="Q45">
+        <v>-9.080792283999997</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1515002131426891</v>
+      </c>
+      <c r="T45">
+        <v>1.580340209442297</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.101015309732403</v>
+      </c>
+      <c r="W45">
+        <v>0.2146775440359022</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.4391969988365348</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1806664654267707</v>
+      </c>
+      <c r="C46">
+        <v>31.80198246730814</v>
+      </c>
+      <c r="D46">
+        <v>178.3739824673081</v>
+      </c>
+      <c r="E46">
+        <v>105.272</v>
+      </c>
+      <c r="F46">
+        <v>185.372</v>
+      </c>
+      <c r="G46">
+        <v>38.8</v>
+      </c>
+      <c r="H46">
+        <v>341.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>28.6</v>
+      </c>
+      <c r="K46">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L46">
+        <v>19</v>
+      </c>
+      <c r="M46">
+        <v>44.2668336</v>
+      </c>
+      <c r="N46">
+        <v>-25.2668336</v>
+      </c>
+      <c r="O46">
+        <v>-5.811371727999999</v>
+      </c>
+      <c r="P46">
+        <v>-19.455461872</v>
+      </c>
+      <c r="Q46">
+        <v>-9.855461871999999</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1535127169488086</v>
+      </c>
+      <c r="T46">
+        <v>1.608560570325196</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.09871950723848474</v>
+      </c>
+      <c r="W46">
+        <v>0.2152257816714498</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.4292152488629772</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1826664654267707</v>
+      </c>
+      <c r="C47">
+        <v>25.10926654548894</v>
+      </c>
+      <c r="D47">
+        <v>175.8942665454889</v>
+      </c>
+      <c r="E47">
+        <v>109.485</v>
+      </c>
+      <c r="F47">
+        <v>189.585</v>
+      </c>
+      <c r="G47">
+        <v>38.8</v>
+      </c>
+      <c r="H47">
+        <v>341.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>28.6</v>
+      </c>
+      <c r="K47">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L47">
+        <v>19</v>
+      </c>
+      <c r="M47">
+        <v>45.272898</v>
+      </c>
+      <c r="N47">
+        <v>-26.272898</v>
+      </c>
+      <c r="O47">
+        <v>-6.042766539999999</v>
+      </c>
+      <c r="P47">
+        <v>-20.23013146</v>
+      </c>
+      <c r="Q47">
+        <v>-10.63013146</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1555984027115142</v>
+      </c>
+      <c r="T47">
+        <v>1.63780712614929</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.09652574041096286</v>
+      </c>
+      <c r="W47">
+        <v>0.2157496531898621</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.4196771322215777</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1846664654267707</v>
+      </c>
+      <c r="C48">
+        <v>18.48455024001922</v>
+      </c>
+      <c r="D48">
+        <v>173.4825502400192</v>
+      </c>
+      <c r="E48">
+        <v>113.698</v>
+      </c>
+      <c r="F48">
+        <v>193.798</v>
+      </c>
+      <c r="G48">
+        <v>38.8</v>
+      </c>
+      <c r="H48">
+        <v>341.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>28.6</v>
+      </c>
+      <c r="K48">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L48">
+        <v>19</v>
+      </c>
+      <c r="M48">
+        <v>46.2789624</v>
+      </c>
+      <c r="N48">
+        <v>-27.2789624</v>
+      </c>
+      <c r="O48">
+        <v>-6.274161351999999</v>
+      </c>
+      <c r="P48">
+        <v>-21.004801048</v>
+      </c>
+      <c r="Q48">
+        <v>-11.404801048</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1577613360950607</v>
+      </c>
+      <c r="T48">
+        <v>1.668136887744647</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.09442735474985497</v>
+      </c>
+      <c r="W48">
+        <v>0.2162507476857347</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.4105537163037173</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1866664654267707</v>
+      </c>
+      <c r="C49">
+        <v>11.92507432015034</v>
+      </c>
+      <c r="D49">
+        <v>171.1360743201504</v>
+      </c>
+      <c r="E49">
+        <v>117.911</v>
+      </c>
+      <c r="F49">
+        <v>198.011</v>
+      </c>
+      <c r="G49">
+        <v>38.8</v>
+      </c>
+      <c r="H49">
+        <v>341.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>28.6</v>
+      </c>
+      <c r="K49">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L49">
+        <v>19</v>
+      </c>
+      <c r="M49">
+        <v>47.2850268</v>
+      </c>
+      <c r="N49">
+        <v>-28.2850268</v>
+      </c>
+      <c r="O49">
+        <v>-6.505556164000001</v>
+      </c>
+      <c r="P49">
+        <v>-21.779470636</v>
+      </c>
+      <c r="Q49">
+        <v>-12.179470636</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1600058896062883</v>
+      </c>
+      <c r="T49">
+        <v>1.69961116864549</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.09241826209560272</v>
+      </c>
+      <c r="W49">
+        <v>0.2167305190115701</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.4018185308504467</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1886664654267707</v>
+      </c>
+      <c r="C50">
+        <v>5.428226845229148</v>
+      </c>
+      <c r="D50">
+        <v>168.8522268452291</v>
+      </c>
+      <c r="E50">
+        <v>122.124</v>
+      </c>
+      <c r="F50">
+        <v>202.224</v>
+      </c>
+      <c r="G50">
+        <v>38.8</v>
+      </c>
+      <c r="H50">
+        <v>341.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>28.6</v>
+      </c>
+      <c r="K50">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L50">
+        <v>19</v>
+      </c>
+      <c r="M50">
+        <v>48.29109119999999</v>
+      </c>
+      <c r="N50">
+        <v>-29.29109119999999</v>
+      </c>
+      <c r="O50">
+        <v>-6.736950975999997</v>
+      </c>
+      <c r="P50">
+        <v>-22.55414022399999</v>
+      </c>
+      <c r="Q50">
+        <v>-12.95414022399999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1623367720987169</v>
+      </c>
+      <c r="T50">
+        <v>1.732295998811749</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.0904928816352777</v>
+      </c>
+      <c r="W50">
+        <v>0.2171902998654957</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.3934473114577292</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1906664654267707</v>
+      </c>
+      <c r="C51">
+        <v>-1.008466533960615</v>
+      </c>
+      <c r="D51">
+        <v>166.6285334660394</v>
+      </c>
+      <c r="E51">
+        <v>126.337</v>
+      </c>
+      <c r="F51">
+        <v>206.437</v>
+      </c>
+      <c r="G51">
+        <v>38.8</v>
+      </c>
+      <c r="H51">
+        <v>341.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>28.6</v>
+      </c>
+      <c r="K51">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L51">
+        <v>19</v>
+      </c>
+      <c r="M51">
+        <v>49.2971556</v>
+      </c>
+      <c r="N51">
+        <v>-30.2971556</v>
+      </c>
+      <c r="O51">
+        <v>-6.968345787999999</v>
+      </c>
+      <c r="P51">
+        <v>-23.328809812</v>
+      </c>
+      <c r="Q51">
+        <v>-13.72880981199999</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1647590617477113</v>
+      </c>
+      <c r="T51">
+        <v>1.766262587023744</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.08864608813251691</v>
+      </c>
+      <c r="W51">
+        <v>0.217631314153955</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.385417774489204</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1926664654267707</v>
+      </c>
+      <c r="C52">
+        <v>-7.387351517460729</v>
+      </c>
+      <c r="D52">
+        <v>164.4626484825393</v>
+      </c>
+      <c r="E52">
+        <v>130.55</v>
+      </c>
+      <c r="F52">
+        <v>210.65</v>
+      </c>
+      <c r="G52">
+        <v>38.8</v>
+      </c>
+      <c r="H52">
+        <v>341.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>28.6</v>
+      </c>
+      <c r="K52">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L52">
+        <v>19</v>
+      </c>
+      <c r="M52">
+        <v>50.30322</v>
+      </c>
+      <c r="N52">
+        <v>-31.30322</v>
+      </c>
+      <c r="O52">
+        <v>-7.199740599999998</v>
+      </c>
+      <c r="P52">
+        <v>-24.1034794</v>
+      </c>
+      <c r="Q52">
+        <v>-14.5034794</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1672782429826656</v>
+      </c>
+      <c r="T52">
+        <v>1.801587838764219</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.08687316636986658</v>
+      </c>
+      <c r="W52">
+        <v>0.2180546878708759</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.3777094189994199</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1946664654267707</v>
+      </c>
+      <c r="C53">
+        <v>-13.71065340994582</v>
+      </c>
+      <c r="D53">
+        <v>162.3523465900542</v>
+      </c>
+      <c r="E53">
+        <v>134.763</v>
+      </c>
+      <c r="F53">
+        <v>214.863</v>
+      </c>
+      <c r="G53">
+        <v>38.8</v>
+      </c>
+      <c r="H53">
+        <v>341.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>28.6</v>
+      </c>
+      <c r="K53">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L53">
+        <v>19</v>
+      </c>
+      <c r="M53">
+        <v>51.3092844</v>
+      </c>
+      <c r="N53">
+        <v>-32.3092844</v>
+      </c>
+      <c r="O53">
+        <v>-7.431135411999999</v>
+      </c>
+      <c r="P53">
+        <v>-24.878148988</v>
+      </c>
+      <c r="Q53">
+        <v>-15.27814898799999</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1699002479414955</v>
+      </c>
+      <c r="T53">
+        <v>1.838354937514509</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.08516977095084959</v>
+      </c>
+      <c r="W53">
+        <v>0.2184614586969371</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.3703033519602157</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1966664654267707</v>
+      </c>
+      <c r="C54">
+        <v>-19.98048474712888</v>
+      </c>
+      <c r="D54">
+        <v>160.2955152528711</v>
+      </c>
+      <c r="E54">
+        <v>138.976</v>
+      </c>
+      <c r="F54">
+        <v>219.076</v>
+      </c>
+      <c r="G54">
+        <v>38.8</v>
+      </c>
+      <c r="H54">
+        <v>341.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>28.6</v>
+      </c>
+      <c r="K54">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L54">
+        <v>19</v>
+      </c>
+      <c r="M54">
+        <v>52.3153488</v>
+      </c>
+      <c r="N54">
+        <v>-33.3153488</v>
+      </c>
+      <c r="O54">
+        <v>-7.662530224</v>
+      </c>
+      <c r="P54">
+        <v>-25.652818576</v>
+      </c>
+      <c r="Q54">
+        <v>-16.052818576</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1726315031069433</v>
+      </c>
+      <c r="T54">
+        <v>1.876653998712728</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.08353189074025633</v>
+      </c>
+      <c r="W54">
+        <v>0.2188525844912268</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.3631821336532883</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1986664654267707</v>
+      </c>
+      <c r="C55">
+        <v>-26.19885234970837</v>
+      </c>
+      <c r="D55">
+        <v>158.2901476502916</v>
+      </c>
+      <c r="E55">
+        <v>143.189</v>
+      </c>
+      <c r="F55">
+        <v>223.289</v>
+      </c>
+      <c r="G55">
+        <v>38.8</v>
+      </c>
+      <c r="H55">
+        <v>341.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>28.6</v>
+      </c>
+      <c r="K55">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L55">
+        <v>19</v>
+      </c>
+      <c r="M55">
+        <v>53.3214132</v>
+      </c>
+      <c r="N55">
+        <v>-34.3214132</v>
+      </c>
+      <c r="O55">
+        <v>-7.893925036</v>
+      </c>
+      <c r="P55">
+        <v>-26.427488164</v>
+      </c>
+      <c r="Q55">
+        <v>-16.827488164</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1754789818964528</v>
+      </c>
+      <c r="T55">
+        <v>1.916582807195978</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.08195581733006281</v>
+      </c>
+      <c r="W55">
+        <v>0.219228950821581</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.3563296405654904</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2006664654267707</v>
+      </c>
+      <c r="C56">
+        <v>-32.36766385436997</v>
+      </c>
+      <c r="D56">
+        <v>156.33433614563</v>
+      </c>
+      <c r="E56">
+        <v>147.402</v>
+      </c>
+      <c r="F56">
+        <v>227.502</v>
+      </c>
+      <c r="G56">
+        <v>38.8</v>
+      </c>
+      <c r="H56">
+        <v>341.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>28.6</v>
+      </c>
+      <c r="K56">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L56">
+        <v>19</v>
+      </c>
+      <c r="M56">
+        <v>54.3274776</v>
+      </c>
+      <c r="N56">
+        <v>-35.3274776</v>
+      </c>
+      <c r="O56">
+        <v>-8.125319848</v>
+      </c>
+      <c r="P56">
+        <v>-27.202157752</v>
+      </c>
+      <c r="Q56">
+        <v>-17.602157752</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.178450264111593</v>
+      </c>
+      <c r="T56">
+        <v>1.958247650830673</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.08043811700913571</v>
+      </c>
+      <c r="W56">
+        <v>0.2195913776582184</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.3497309435179814</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2026664654267707</v>
+      </c>
+      <c r="C57">
+        <v>-38.48873376652043</v>
+      </c>
+      <c r="D57">
+        <v>154.4262662334796</v>
+      </c>
+      <c r="E57">
+        <v>151.615</v>
+      </c>
+      <c r="F57">
+        <v>231.715</v>
+      </c>
+      <c r="G57">
+        <v>38.8</v>
+      </c>
+      <c r="H57">
+        <v>341.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>28.6</v>
+      </c>
+      <c r="K57">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L57">
+        <v>19</v>
+      </c>
+      <c r="M57">
+        <v>55.333542</v>
+      </c>
+      <c r="N57">
+        <v>-36.333542</v>
+      </c>
+      <c r="O57">
+        <v>-8.35671466</v>
+      </c>
+      <c r="P57">
+        <v>-27.97682734</v>
+      </c>
+      <c r="Q57">
+        <v>-18.37682734</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1815536033140729</v>
+      </c>
+      <c r="T57">
+        <v>2.001764265293577</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.0789756057907878</v>
+      </c>
+      <c r="W57">
+        <v>0.2199406253371599</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.3433721990903817</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2046664654267707</v>
+      </c>
+      <c r="C58">
+        <v>-44.56378907512237</v>
+      </c>
+      <c r="D58">
+        <v>152.5642109248776</v>
+      </c>
+      <c r="E58">
+        <v>155.828</v>
+      </c>
+      <c r="F58">
+        <v>235.928</v>
+      </c>
+      <c r="G58">
+        <v>38.8</v>
+      </c>
+      <c r="H58">
+        <v>341.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>28.6</v>
+      </c>
+      <c r="K58">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L58">
+        <v>19</v>
+      </c>
+      <c r="M58">
+        <v>56.3396064</v>
+      </c>
+      <c r="N58">
+        <v>-37.3396064</v>
+      </c>
+      <c r="O58">
+        <v>-8.588109471999999</v>
+      </c>
+      <c r="P58">
+        <v>-28.751496928</v>
+      </c>
+      <c r="Q58">
+        <v>-19.151496928</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1847980033893927</v>
+      </c>
+      <c r="T58">
+        <v>2.047258907686613</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.07756532711595229</v>
+      </c>
+      <c r="W58">
+        <v>0.2202773998847106</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.3372405526780535</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2066664654267708</v>
+      </c>
+      <c r="C59">
+        <v>-50.59447446615039</v>
+      </c>
+      <c r="D59">
+        <v>150.7465255338496</v>
+      </c>
+      <c r="E59">
+        <v>160.041</v>
+      </c>
+      <c r="F59">
+        <v>240.141</v>
+      </c>
+      <c r="G59">
+        <v>38.8</v>
+      </c>
+      <c r="H59">
+        <v>341.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>28.6</v>
+      </c>
+      <c r="K59">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L59">
+        <v>19</v>
+      </c>
+      <c r="M59">
+        <v>57.3456708</v>
+      </c>
+      <c r="N59">
+        <v>-38.3456708</v>
+      </c>
+      <c r="O59">
+        <v>-8.819504283999999</v>
+      </c>
+      <c r="P59">
+        <v>-29.526166516</v>
+      </c>
+      <c r="Q59">
+        <v>-19.926166516</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1881933057937972</v>
+      </c>
+      <c r="T59">
+        <v>2.094869579958395</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.07620453190339173</v>
+      </c>
+      <c r="W59">
+        <v>0.2206023577814701</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.3313240517538771</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2086664654267708</v>
+      </c>
+      <c r="C60">
+        <v>-56.58235716774911</v>
+      </c>
+      <c r="D60">
+        <v>148.9716428322508</v>
+      </c>
+      <c r="E60">
+        <v>164.254</v>
+      </c>
+      <c r="F60">
+        <v>244.354</v>
+      </c>
+      <c r="G60">
+        <v>38.8</v>
+      </c>
+      <c r="H60">
+        <v>341.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>28.6</v>
+      </c>
+      <c r="K60">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L60">
+        <v>19</v>
+      </c>
+      <c r="M60">
+        <v>58.35173519999999</v>
+      </c>
+      <c r="N60">
+        <v>-39.35173519999999</v>
+      </c>
+      <c r="O60">
+        <v>-9.050899095999998</v>
+      </c>
+      <c r="P60">
+        <v>-30.30083610399999</v>
+      </c>
+      <c r="Q60">
+        <v>-20.70083610399999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1917502892650781</v>
+      </c>
+      <c r="T60">
+        <v>2.144747427100261</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.07489066066367808</v>
+      </c>
+      <c r="W60">
+        <v>0.2209161102335137</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.3256115681029482</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2106664654267707</v>
+      </c>
+      <c r="C61">
+        <v>-62.52893145709436</v>
+      </c>
+      <c r="D61">
+        <v>147.2380685429056</v>
+      </c>
+      <c r="E61">
+        <v>168.467</v>
+      </c>
+      <c r="F61">
+        <v>248.567</v>
+      </c>
+      <c r="G61">
+        <v>38.8</v>
+      </c>
+      <c r="H61">
+        <v>341.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>28.6</v>
+      </c>
+      <c r="K61">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L61">
+        <v>19</v>
+      </c>
+      <c r="M61">
+        <v>59.35779959999999</v>
+      </c>
+      <c r="N61">
+        <v>-40.35779959999999</v>
+      </c>
+      <c r="O61">
+        <v>-9.282293907999998</v>
+      </c>
+      <c r="P61">
+        <v>-31.07550569199999</v>
+      </c>
+      <c r="Q61">
+        <v>-21.47550569199999</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1954807841252019</v>
+      </c>
+      <c r="T61">
+        <v>2.197058339956365</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.07362132743209032</v>
+      </c>
+      <c r="W61">
+        <v>0.2212192270092169</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.3200927279656102</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2126664654267707</v>
+      </c>
+      <c r="C62">
+        <v>-68.43562285619771</v>
+      </c>
+      <c r="D62">
+        <v>145.5443771438023</v>
+      </c>
+      <c r="E62">
+        <v>172.68</v>
+      </c>
+      <c r="F62">
+        <v>252.78</v>
+      </c>
+      <c r="G62">
+        <v>38.8</v>
+      </c>
+      <c r="H62">
+        <v>341.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>28.6</v>
+      </c>
+      <c r="K62">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L62">
+        <v>19</v>
+      </c>
+      <c r="M62">
+        <v>60.363864</v>
+      </c>
+      <c r="N62">
+        <v>-41.363864</v>
+      </c>
+      <c r="O62">
+        <v>-9.513688719999999</v>
+      </c>
+      <c r="P62">
+        <v>-31.85017528</v>
+      </c>
+      <c r="Q62">
+        <v>-22.25017528</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.199397803728332</v>
+      </c>
+      <c r="T62">
+        <v>2.251984798455274</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.07239430530822215</v>
+      </c>
+      <c r="W62">
+        <v>0.2215122398923966</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.3147578491661832</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2146664654267708</v>
+      </c>
+      <c r="C63">
+        <v>-74.30379204141576</v>
+      </c>
+      <c r="D63">
+        <v>143.8892079585842</v>
+      </c>
+      <c r="E63">
+        <v>176.893</v>
+      </c>
+      <c r="F63">
+        <v>256.993</v>
+      </c>
+      <c r="G63">
+        <v>38.8</v>
+      </c>
+      <c r="H63">
+        <v>341.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>28.6</v>
+      </c>
+      <c r="K63">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L63">
+        <v>19</v>
+      </c>
+      <c r="M63">
+        <v>61.3699284</v>
+      </c>
+      <c r="N63">
+        <v>-42.3699284</v>
+      </c>
+      <c r="O63">
+        <v>-9.745083531999999</v>
+      </c>
+      <c r="P63">
+        <v>-32.624844868</v>
+      </c>
+      <c r="Q63">
+        <v>-23.024844868</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2035156961316226</v>
+      </c>
+      <c r="T63">
+        <v>2.309727998415666</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.07120751341792342</v>
+      </c>
+      <c r="W63">
+        <v>0.2217956457957999</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.3095978844257541</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2166664654267707</v>
+      </c>
+      <c r="C64">
+        <v>-80.13473848919989</v>
+      </c>
+      <c r="D64">
+        <v>142.2712615108001</v>
+      </c>
+      <c r="E64">
+        <v>181.106</v>
+      </c>
+      <c r="F64">
+        <v>261.206</v>
+      </c>
+      <c r="G64">
+        <v>38.8</v>
+      </c>
+      <c r="H64">
+        <v>341.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>28.6</v>
+      </c>
+      <c r="K64">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L64">
+        <v>19</v>
+      </c>
+      <c r="M64">
+        <v>62.37599279999999</v>
+      </c>
+      <c r="N64">
+        <v>-43.37599279999999</v>
+      </c>
+      <c r="O64">
+        <v>-9.976478343999997</v>
+      </c>
+      <c r="P64">
+        <v>-33.39951445599999</v>
+      </c>
+      <c r="Q64">
+        <v>-23.79951445599999</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2078503197140337</v>
+      </c>
+      <c r="T64">
+        <v>2.370510314163446</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.07005900513698918</v>
+      </c>
+      <c r="W64">
+        <v>0.222069909573287</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.3046043701608225</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2186664654267707</v>
+      </c>
+      <c r="C65">
+        <v>-85.92970387861516</v>
+      </c>
+      <c r="D65">
+        <v>140.6892961213848</v>
+      </c>
+      <c r="E65">
+        <v>185.319</v>
+      </c>
+      <c r="F65">
+        <v>265.419</v>
+      </c>
+      <c r="G65">
+        <v>38.8</v>
+      </c>
+      <c r="H65">
+        <v>341.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>28.6</v>
+      </c>
+      <c r="K65">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L65">
+        <v>19</v>
+      </c>
+      <c r="M65">
+        <v>63.3820572</v>
+      </c>
+      <c r="N65">
+        <v>-44.3820572</v>
+      </c>
+      <c r="O65">
+        <v>-10.207873156</v>
+      </c>
+      <c r="P65">
+        <v>-34.174184044</v>
+      </c>
+      <c r="Q65">
+        <v>-24.574184044</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2124192472738724</v>
+      </c>
+      <c r="T65">
+        <v>2.434578160492188</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.06894695743640204</v>
+      </c>
+      <c r="W65">
+        <v>0.2223354665641872</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2997693801582698</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2206664654267708</v>
+      </c>
+      <c r="C66">
+        <v>-91.68987526935217</v>
+      </c>
+      <c r="D66">
+        <v>139.1421247306478</v>
+      </c>
+      <c r="E66">
+        <v>189.532</v>
+      </c>
+      <c r="F66">
+        <v>269.6319999999999</v>
+      </c>
+      <c r="G66">
+        <v>38.8</v>
+      </c>
+      <c r="H66">
+        <v>341.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>28.6</v>
+      </c>
+      <c r="K66">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L66">
+        <v>19</v>
+      </c>
+      <c r="M66">
+        <v>64.38812159999999</v>
+      </c>
+      <c r="N66">
+        <v>-45.38812159999999</v>
+      </c>
+      <c r="O66">
+        <v>-10.439267968</v>
+      </c>
+      <c r="P66">
+        <v>-34.948853632</v>
+      </c>
+      <c r="Q66">
+        <v>-25.34885363199999</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2172420041425911</v>
+      </c>
+      <c r="T66">
+        <v>2.502205331616971</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.06786966122645827</v>
+      </c>
+      <c r="W66">
+        <v>0.2225927248991218</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2950854835932969</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2226664654267708</v>
+      </c>
+      <c r="C67">
+        <v>-97.41638807232783</v>
+      </c>
+      <c r="D67">
+        <v>137.6286119276721</v>
+      </c>
+      <c r="E67">
+        <v>193.745</v>
+      </c>
+      <c r="F67">
+        <v>273.845</v>
+      </c>
+      <c r="G67">
+        <v>38.8</v>
+      </c>
+      <c r="H67">
+        <v>341.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>28.6</v>
+      </c>
+      <c r="K67">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L67">
+        <v>19</v>
+      </c>
+      <c r="M67">
+        <v>65.39418599999999</v>
+      </c>
+      <c r="N67">
+        <v>-46.39418599999999</v>
+      </c>
+      <c r="O67">
+        <v>-10.67066278</v>
+      </c>
+      <c r="P67">
+        <v>-35.72352321999999</v>
+      </c>
+      <c r="Q67">
+        <v>-26.12352321999999</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2223403471180938</v>
+      </c>
+      <c r="T67">
+        <v>2.573696912520314</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.06682551259220507</v>
+      </c>
+      <c r="W67">
+        <v>0.2228420675929814</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2905457069226307</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2246664654267708</v>
+      </c>
+      <c r="C68">
+        <v>-103.1103288284956</v>
+      </c>
+      <c r="D68">
+        <v>136.1476711715044</v>
+      </c>
+      <c r="E68">
+        <v>197.958</v>
+      </c>
+      <c r="F68">
+        <v>278.058</v>
+      </c>
+      <c r="G68">
+        <v>38.8</v>
+      </c>
+      <c r="H68">
+        <v>341.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>28.6</v>
+      </c>
+      <c r="K68">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L68">
+        <v>19</v>
+      </c>
+      <c r="M68">
+        <v>66.4002504</v>
+      </c>
+      <c r="N68">
+        <v>-47.4002504</v>
+      </c>
+      <c r="O68">
+        <v>-10.902057592</v>
+      </c>
+      <c r="P68">
+        <v>-36.49819280800001</v>
+      </c>
+      <c r="Q68">
+        <v>-26.898192808</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.227738592621567</v>
+      </c>
+      <c r="T68">
+        <v>2.649393880535616</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.0658130048256565</v>
+      </c>
+      <c r="W68">
+        <v>0.2230838544476333</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2861434992419848</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2266664654267707</v>
+      </c>
+      <c r="C69">
+        <v>-108.7727378101594</v>
+      </c>
+      <c r="D69">
+        <v>134.6982621898406</v>
+      </c>
+      <c r="E69">
+        <v>202.171</v>
+      </c>
+      <c r="F69">
+        <v>282.271</v>
+      </c>
+      <c r="G69">
+        <v>38.8</v>
+      </c>
+      <c r="H69">
+        <v>341.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>28.6</v>
+      </c>
+      <c r="K69">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L69">
+        <v>19</v>
+      </c>
+      <c r="M69">
+        <v>67.40631479999999</v>
+      </c>
+      <c r="N69">
+        <v>-48.40631479999999</v>
+      </c>
+      <c r="O69">
+        <v>-11.133452404</v>
+      </c>
+      <c r="P69">
+        <v>-37.27286239599999</v>
+      </c>
+      <c r="Q69">
+        <v>-27.67286239599999</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2334640045191903</v>
+      </c>
+      <c r="T69">
+        <v>2.729678543582151</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.06483072117154223</v>
+      </c>
+      <c r="W69">
+        <v>0.2233184237842357</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.2818727007458358</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2286664654267707</v>
+      </c>
+      <c r="C70">
+        <v>-114.4046114578789</v>
+      </c>
+      <c r="D70">
+        <v>133.2793885421211</v>
+      </c>
+      <c r="E70">
+        <v>206.384</v>
+      </c>
+      <c r="F70">
+        <v>286.484</v>
+      </c>
+      <c r="G70">
+        <v>38.8</v>
+      </c>
+      <c r="H70">
+        <v>341.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>28.6</v>
+      </c>
+      <c r="K70">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L70">
+        <v>19</v>
+      </c>
+      <c r="M70">
+        <v>68.4123792</v>
+      </c>
+      <c r="N70">
+        <v>-49.4123792</v>
+      </c>
+      <c r="O70">
+        <v>-11.364847216</v>
+      </c>
+      <c r="P70">
+        <v>-38.047531984</v>
+      </c>
+      <c r="Q70">
+        <v>-28.447531984</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.239547254660415</v>
+      </c>
+      <c r="T70">
+        <v>2.814980998069093</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.06387732821313719</v>
+      </c>
+      <c r="W70">
+        <v>0.2235460940227028</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.2777275139701617</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2306664654267707</v>
+      </c>
+      <c r="C71">
+        <v>-120.0069046649609</v>
+      </c>
+      <c r="D71">
+        <v>131.8900953350391</v>
+      </c>
+      <c r="E71">
+        <v>210.597</v>
+      </c>
+      <c r="F71">
+        <v>290.697</v>
+      </c>
+      <c r="G71">
+        <v>38.8</v>
+      </c>
+      <c r="H71">
+        <v>341.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>28.6</v>
+      </c>
+      <c r="K71">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L71">
+        <v>19</v>
+      </c>
+      <c r="M71">
+        <v>69.4184436</v>
+      </c>
+      <c r="N71">
+        <v>-50.4184436</v>
+      </c>
+      <c r="O71">
+        <v>-11.596242028</v>
+      </c>
+      <c r="P71">
+        <v>-38.822201572</v>
+      </c>
+      <c r="Q71">
+        <v>-29.222201572</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2460229725526865</v>
+      </c>
+      <c r="T71">
+        <v>2.905786836716483</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.06295156983323665</v>
+      </c>
+      <c r="W71">
+        <v>0.2237671651238231</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2737024775358116</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2326664654267708</v>
+      </c>
+      <c r="C72">
+        <v>-125.580532920546</v>
+      </c>
+      <c r="D72">
+        <v>130.529467079454</v>
+      </c>
+      <c r="E72">
+        <v>214.81</v>
+      </c>
+      <c r="F72">
+        <v>294.91</v>
+      </c>
+      <c r="G72">
+        <v>38.8</v>
+      </c>
+      <c r="H72">
+        <v>341.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>28.6</v>
+      </c>
+      <c r="K72">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L72">
+        <v>19</v>
+      </c>
+      <c r="M72">
+        <v>70.424508</v>
+      </c>
+      <c r="N72">
+        <v>-51.424508</v>
+      </c>
+      <c r="O72">
+        <v>-11.82763684</v>
+      </c>
+      <c r="P72">
+        <v>-39.59687116000001</v>
+      </c>
+      <c r="Q72">
+        <v>-29.99687116</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2529304049711094</v>
+      </c>
+      <c r="T72">
+        <v>3.002646397940366</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.06205226169276184</v>
+      </c>
+      <c r="W72">
+        <v>0.2239819199077685</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2697924421424428</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2346664654267707</v>
+      </c>
+      <c r="C73">
+        <v>-131.1263743213956</v>
+      </c>
+      <c r="D73">
+        <v>129.1966256786043</v>
+      </c>
+      <c r="E73">
+        <v>219.0229999999999</v>
+      </c>
+      <c r="F73">
+        <v>299.1229999999999</v>
+      </c>
+      <c r="G73">
+        <v>38.8</v>
+      </c>
+      <c r="H73">
+        <v>341.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>28.6</v>
+      </c>
+      <c r="K73">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L73">
+        <v>19</v>
+      </c>
+      <c r="M73">
+        <v>71.43057239999999</v>
+      </c>
+      <c r="N73">
+        <v>-52.43057239999999</v>
+      </c>
+      <c r="O73">
+        <v>-12.059031652</v>
+      </c>
+      <c r="P73">
+        <v>-40.37154074799999</v>
+      </c>
+      <c r="Q73">
+        <v>-30.77154074799999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2603142120390786</v>
+      </c>
+      <c r="T73">
+        <v>3.106185928903826</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.06117828617596239</v>
+      </c>
+      <c r="W73">
+        <v>0.2241906252611802</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2659925485911409</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2366664654267707</v>
+      </c>
+      <c r="C74">
+        <v>-136.645271461671</v>
+      </c>
+      <c r="D74">
+        <v>127.8907285383289</v>
+      </c>
+      <c r="E74">
+        <v>223.236</v>
+      </c>
+      <c r="F74">
+        <v>303.336</v>
+      </c>
+      <c r="G74">
+        <v>38.8</v>
+      </c>
+      <c r="H74">
+        <v>341.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>28.6</v>
+      </c>
+      <c r="K74">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L74">
+        <v>19</v>
+      </c>
+      <c r="M74">
+        <v>72.43663679999999</v>
+      </c>
+      <c r="N74">
+        <v>-53.43663679999999</v>
+      </c>
+      <c r="O74">
+        <v>-12.290426464</v>
+      </c>
+      <c r="P74">
+        <v>-41.146210336</v>
+      </c>
+      <c r="Q74">
+        <v>-31.54621033599999</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2682254338976171</v>
+      </c>
+      <c r="T74">
+        <v>3.217121140650391</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.0603285877568518</v>
+      </c>
+      <c r="W74">
+        <v>0.2243935332436638</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2622982076384861</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2386664654267707</v>
+      </c>
+      <c r="C75">
+        <v>-142.1380332092483</v>
+      </c>
+      <c r="D75">
+        <v>126.6109667907517</v>
+      </c>
+      <c r="E75">
+        <v>227.449</v>
+      </c>
+      <c r="F75">
+        <v>307.549</v>
+      </c>
+      <c r="G75">
+        <v>38.8</v>
+      </c>
+      <c r="H75">
+        <v>341.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>28.6</v>
+      </c>
+      <c r="K75">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L75">
+        <v>19</v>
+      </c>
+      <c r="M75">
+        <v>73.4427012</v>
+      </c>
+      <c r="N75">
+        <v>-54.4427012</v>
+      </c>
+      <c r="O75">
+        <v>-12.521821276</v>
+      </c>
+      <c r="P75">
+        <v>-41.920879924</v>
+      </c>
+      <c r="Q75">
+        <v>-32.320879924</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2767226721901215</v>
+      </c>
+      <c r="T75">
+        <v>3.336273775489294</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.05950216874648395</v>
+      </c>
+      <c r="W75">
+        <v>0.2245908821033396</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.258705081506452</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2406664654267707</v>
+      </c>
+      <c r="C76">
+        <v>-147.6054363764418</v>
+      </c>
+      <c r="D76">
+        <v>125.3565636235581</v>
+      </c>
+      <c r="E76">
+        <v>231.6619999999999</v>
+      </c>
+      <c r="F76">
+        <v>311.7619999999999</v>
+      </c>
+      <c r="G76">
+        <v>38.8</v>
+      </c>
+      <c r="H76">
+        <v>341.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>28.6</v>
+      </c>
+      <c r="K76">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L76">
+        <v>19</v>
+      </c>
+      <c r="M76">
+        <v>74.44876559999999</v>
+      </c>
+      <c r="N76">
+        <v>-55.44876559999999</v>
+      </c>
+      <c r="O76">
+        <v>-12.753216088</v>
+      </c>
+      <c r="P76">
+        <v>-42.69554951199999</v>
+      </c>
+      <c r="Q76">
+        <v>-33.09554951199999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2858735441974338</v>
+      </c>
+      <c r="T76">
+        <v>3.464591997623498</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.05869808538504499</v>
+      </c>
+      <c r="W76">
+        <v>0.2247828972100513</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2552090668915</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2426664654267707</v>
+      </c>
+      <c r="C77">
+        <v>-153.0482272923842</v>
+      </c>
+      <c r="D77">
+        <v>124.1267727076158</v>
+      </c>
+      <c r="E77">
+        <v>235.875</v>
+      </c>
+      <c r="F77">
+        <v>315.975</v>
+      </c>
+      <c r="G77">
+        <v>38.8</v>
+      </c>
+      <c r="H77">
+        <v>341.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>28.6</v>
+      </c>
+      <c r="K77">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L77">
+        <v>19</v>
+      </c>
+      <c r="M77">
+        <v>75.45483</v>
+      </c>
+      <c r="N77">
+        <v>-56.45483</v>
+      </c>
+      <c r="O77">
+        <v>-12.9846109</v>
+      </c>
+      <c r="P77">
+        <v>-43.4702191</v>
+      </c>
+      <c r="Q77">
+        <v>-33.8702191</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2957564859653312</v>
+      </c>
+      <c r="T77">
+        <v>3.603175677528438</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.05791544424657771</v>
+      </c>
+      <c r="W77">
+        <v>0.2249697919139172</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2518062793329466</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2446664654267707</v>
+      </c>
+      <c r="C78">
+        <v>-158.4671232837521</v>
+      </c>
+      <c r="D78">
+        <v>122.9208767162479</v>
+      </c>
+      <c r="E78">
+        <v>240.088</v>
+      </c>
+      <c r="F78">
+        <v>320.188</v>
+      </c>
+      <c r="G78">
+        <v>38.8</v>
+      </c>
+      <c r="H78">
+        <v>341.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>28.6</v>
+      </c>
+      <c r="K78">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L78">
+        <v>19</v>
+      </c>
+      <c r="M78">
+        <v>76.4608944</v>
+      </c>
+      <c r="N78">
+        <v>-57.4608944</v>
+      </c>
+      <c r="O78">
+        <v>-13.216005712</v>
+      </c>
+      <c r="P78">
+        <v>-44.244888688</v>
+      </c>
+      <c r="Q78">
+        <v>-34.644888688</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3064630062138867</v>
+      </c>
+      <c r="T78">
+        <v>3.753307997425457</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.0571533989275438</v>
+      </c>
+      <c r="W78">
+        <v>0.2251517683361026</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2484930388154079</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2466664654267707</v>
+      </c>
+      <c r="C79">
+        <v>-163.8628140700112</v>
+      </c>
+      <c r="D79">
+        <v>121.7381859299887</v>
+      </c>
+      <c r="E79">
+        <v>244.301</v>
+      </c>
+      <c r="F79">
+        <v>324.401</v>
+      </c>
+      <c r="G79">
+        <v>38.8</v>
+      </c>
+      <c r="H79">
+        <v>341.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>28.6</v>
+      </c>
+      <c r="K79">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L79">
+        <v>19</v>
+      </c>
+      <c r="M79">
+        <v>77.46695879999999</v>
+      </c>
+      <c r="N79">
+        <v>-58.46695879999999</v>
+      </c>
+      <c r="O79">
+        <v>-13.447400524</v>
+      </c>
+      <c r="P79">
+        <v>-45.01955827599999</v>
+      </c>
+      <c r="Q79">
+        <v>-35.41955827599999</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3181005282231861</v>
+      </c>
+      <c r="T79">
+        <v>3.916495301661346</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.05641114699341986</v>
+      </c>
+      <c r="W79">
+        <v>0.2253290180979713</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2452658564931298</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2486664654267707</v>
+      </c>
+      <c r="C80">
+        <v>-169.2359630788816</v>
+      </c>
+      <c r="D80">
+        <v>120.5780369211184</v>
+      </c>
+      <c r="E80">
+        <v>248.514</v>
+      </c>
+      <c r="F80">
+        <v>328.614</v>
+      </c>
+      <c r="G80">
+        <v>38.8</v>
+      </c>
+      <c r="H80">
+        <v>341.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>28.6</v>
+      </c>
+      <c r="K80">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L80">
+        <v>19</v>
+      </c>
+      <c r="M80">
+        <v>78.4730232</v>
+      </c>
+      <c r="N80">
+        <v>-59.4730232</v>
+      </c>
+      <c r="O80">
+        <v>-13.678795336</v>
+      </c>
+      <c r="P80">
+        <v>-45.794227864</v>
+      </c>
+      <c r="Q80">
+        <v>-36.194227864</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3307960067787855</v>
+      </c>
+      <c r="T80">
+        <v>4.094517815373226</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.05568792716017088</v>
+      </c>
+      <c r="W80">
+        <v>0.2255017229941512</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2421214224355256</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2506664654267707</v>
+      </c>
+      <c r="C81">
+        <v>-174.5872086872957</v>
+      </c>
+      <c r="D81">
+        <v>119.4397913127043</v>
+      </c>
+      <c r="E81">
+        <v>252.727</v>
+      </c>
+      <c r="F81">
+        <v>332.827</v>
+      </c>
+      <c r="G81">
+        <v>38.8</v>
+      </c>
+      <c r="H81">
+        <v>341.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>28.6</v>
+      </c>
+      <c r="K81">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L81">
+        <v>19</v>
+      </c>
+      <c r="M81">
+        <v>79.4790876</v>
+      </c>
+      <c r="N81">
+        <v>-60.4790876</v>
+      </c>
+      <c r="O81">
+        <v>-13.910190148</v>
+      </c>
+      <c r="P81">
+        <v>-46.568897452</v>
+      </c>
+      <c r="Q81">
+        <v>-36.968897452</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3447005785301563</v>
+      </c>
+      <c r="T81">
+        <v>4.289494854200523</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.05498301668978897</v>
+      </c>
+      <c r="W81">
+        <v>0.2256700556144784</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2390565943034303</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2526664654267707</v>
+      </c>
+      <c r="C82">
+        <v>-179.9171653927273</v>
+      </c>
+      <c r="D82">
+        <v>118.3228346072726</v>
+      </c>
+      <c r="E82">
+        <v>256.9399999999999</v>
+      </c>
+      <c r="F82">
+        <v>337.04</v>
+      </c>
+      <c r="G82">
+        <v>38.8</v>
+      </c>
+      <c r="H82">
+        <v>341.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>28.6</v>
+      </c>
+      <c r="K82">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L82">
+        <v>19</v>
+      </c>
+      <c r="M82">
+        <v>80.485152</v>
+      </c>
+      <c r="N82">
+        <v>-61.485152</v>
+      </c>
+      <c r="O82">
+        <v>-14.14158496</v>
+      </c>
+      <c r="P82">
+        <v>-47.34356704</v>
+      </c>
+      <c r="Q82">
+        <v>-37.74356703999999</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3599956074566641</v>
+      </c>
+      <c r="T82">
+        <v>4.503969596910549</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.05429572898116661</v>
+      </c>
+      <c r="W82">
+        <v>0.2258341799192974</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2360683868746375</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2546664654267707</v>
+      </c>
+      <c r="C83">
+        <v>-185.226424919406</v>
+      </c>
+      <c r="D83">
+        <v>117.226575080594</v>
+      </c>
+      <c r="E83">
+        <v>261.153</v>
+      </c>
+      <c r="F83">
+        <v>341.253</v>
+      </c>
+      <c r="G83">
+        <v>38.8</v>
+      </c>
+      <c r="H83">
+        <v>341.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>28.6</v>
+      </c>
+      <c r="K83">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L83">
+        <v>19</v>
+      </c>
+      <c r="M83">
+        <v>81.4912164</v>
+      </c>
+      <c r="N83">
+        <v>-62.4912164</v>
+      </c>
+      <c r="O83">
+        <v>-14.372979772</v>
+      </c>
+      <c r="P83">
+        <v>-48.118236628</v>
+      </c>
+      <c r="Q83">
+        <v>-38.518236628</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3769006394280675</v>
+      </c>
+      <c r="T83">
+        <v>4.741020628326894</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.05362541133942381</v>
+      </c>
+      <c r="W83">
+        <v>0.2259942517721456</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.2331539623453209</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2566664654267707</v>
+      </c>
+      <c r="C84">
+        <v>-190.515557263601</v>
+      </c>
+      <c r="D84">
+        <v>116.150442736399</v>
+      </c>
+      <c r="E84">
+        <v>265.366</v>
+      </c>
+      <c r="F84">
+        <v>345.466</v>
+      </c>
+      <c r="G84">
+        <v>38.8</v>
+      </c>
+      <c r="H84">
+        <v>341.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>28.6</v>
+      </c>
+      <c r="K84">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L84">
+        <v>19</v>
+      </c>
+      <c r="M84">
+        <v>82.49728080000001</v>
+      </c>
+      <c r="N84">
+        <v>-63.49728080000001</v>
+      </c>
+      <c r="O84">
+        <v>-14.604374584</v>
+      </c>
+      <c r="P84">
+        <v>-48.89290621600001</v>
+      </c>
+      <c r="Q84">
+        <v>-39.29290621600001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3956840082851823</v>
+      </c>
+      <c r="T84">
+        <v>5.004410663233943</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.05297144290845522</v>
+      </c>
+      <c r="W84">
+        <v>0.2261504194334609</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2303106213411097</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2586664654267707</v>
+      </c>
+      <c r="C85">
+        <v>-195.7851116818561</v>
+      </c>
+      <c r="D85">
+        <v>115.0938883181438</v>
+      </c>
+      <c r="E85">
+        <v>269.579</v>
+      </c>
+      <c r="F85">
+        <v>349.679</v>
+      </c>
+      <c r="G85">
+        <v>38.8</v>
+      </c>
+      <c r="H85">
+        <v>341.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>28.6</v>
+      </c>
+      <c r="K85">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L85">
+        <v>19</v>
+      </c>
+      <c r="M85">
+        <v>83.5033452</v>
+      </c>
+      <c r="N85">
+        <v>-64.5033452</v>
+      </c>
+      <c r="O85">
+        <v>-14.835769396</v>
+      </c>
+      <c r="P85">
+        <v>-49.667575804</v>
+      </c>
+      <c r="Q85">
+        <v>-40.067575804</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4166771852431342</v>
+      </c>
+      <c r="T85">
+        <v>5.298787761071234</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.05233323275293167</v>
+      </c>
+      <c r="W85">
+        <v>0.2263028240185999</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2275357945779638</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2606664654267707</v>
+      </c>
+      <c r="C86">
+        <v>-201.0356176257738</v>
+      </c>
+      <c r="D86">
+        <v>114.0563823742261</v>
+      </c>
+      <c r="E86">
+        <v>273.7919999999999</v>
+      </c>
+      <c r="F86">
+        <v>353.8919999999999</v>
+      </c>
+      <c r="G86">
+        <v>38.8</v>
+      </c>
+      <c r="H86">
+        <v>341.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>28.6</v>
+      </c>
+      <c r="K86">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L86">
+        <v>19</v>
+      </c>
+      <c r="M86">
+        <v>84.50940959999998</v>
+      </c>
+      <c r="N86">
+        <v>-65.50940959999998</v>
+      </c>
+      <c r="O86">
+        <v>-15.067164208</v>
+      </c>
+      <c r="P86">
+        <v>-50.44224539199999</v>
+      </c>
+      <c r="Q86">
+        <v>-40.84224539199999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.44029450932083</v>
+      </c>
+      <c r="T86">
+        <v>5.629961996138184</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.05171021807730154</v>
+      </c>
+      <c r="W86">
+        <v>0.2264515999231404</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2248270351187024</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2626664654267707</v>
+      </c>
+      <c r="C87">
+        <v>-206.2675856266916</v>
+      </c>
+      <c r="D87">
+        <v>113.0374143733083</v>
+      </c>
+      <c r="E87">
+        <v>278.005</v>
+      </c>
+      <c r="F87">
+        <v>358.105</v>
+      </c>
+      <c r="G87">
+        <v>38.8</v>
+      </c>
+      <c r="H87">
+        <v>341.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>28.6</v>
+      </c>
+      <c r="K87">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L87">
+        <v>19</v>
+      </c>
+      <c r="M87">
+        <v>85.515474</v>
+      </c>
+      <c r="N87">
+        <v>-66.515474</v>
+      </c>
+      <c r="O87">
+        <v>-15.29855902</v>
+      </c>
+      <c r="P87">
+        <v>-51.21691498</v>
+      </c>
+      <c r="Q87">
+        <v>-41.61691498</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4670608099422187</v>
+      </c>
+      <c r="T87">
+        <v>6.00529279588073</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.05110186257050976</v>
+      </c>
+      <c r="W87">
+        <v>0.2265968752181623</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2221820111761293</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2646664654267707</v>
+      </c>
+      <c r="C88">
+        <v>-211.4815081333571</v>
+      </c>
+      <c r="D88">
+        <v>112.0364918666429</v>
+      </c>
+      <c r="E88">
+        <v>282.218</v>
+      </c>
+      <c r="F88">
+        <v>362.318</v>
+      </c>
+      <c r="G88">
+        <v>38.8</v>
+      </c>
+      <c r="H88">
+        <v>341.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>28.6</v>
+      </c>
+      <c r="K88">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L88">
+        <v>19</v>
+      </c>
+      <c r="M88">
+        <v>86.5215384</v>
+      </c>
+      <c r="N88">
+        <v>-67.5215384</v>
+      </c>
+      <c r="O88">
+        <v>-15.529953832</v>
+      </c>
+      <c r="P88">
+        <v>-51.991584568</v>
+      </c>
+      <c r="Q88">
+        <v>-42.391584568</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4976508677952342</v>
+      </c>
+      <c r="T88">
+        <v>6.434242281300782</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.0505076548662015</v>
+      </c>
+      <c r="W88">
+        <v>0.2267387720179511</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2195984994182674</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2666664654267707</v>
+      </c>
+      <c r="C89">
+        <v>-216.6778603054883</v>
+      </c>
+      <c r="D89">
+        <v>111.0531396945117</v>
+      </c>
+      <c r="E89">
+        <v>286.4309999999999</v>
+      </c>
+      <c r="F89">
+        <v>366.5309999999999</v>
+      </c>
+      <c r="G89">
+        <v>38.8</v>
+      </c>
+      <c r="H89">
+        <v>341.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>28.6</v>
+      </c>
+      <c r="K89">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L89">
+        <v>19</v>
+      </c>
+      <c r="M89">
+        <v>87.5276028</v>
+      </c>
+      <c r="N89">
+        <v>-68.5276028</v>
+      </c>
+      <c r="O89">
+        <v>-15.761348644</v>
+      </c>
+      <c r="P89">
+        <v>-52.766254156</v>
+      </c>
+      <c r="Q89">
+        <v>-43.166254156</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5329470883948677</v>
+      </c>
+      <c r="T89">
+        <v>6.929183995246996</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.04992710710911872</v>
+      </c>
+      <c r="W89">
+        <v>0.2268774068223424</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2170743787352988</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2686664654267708</v>
+      </c>
+      <c r="C90">
+        <v>-221.8571007659081</v>
+      </c>
+      <c r="D90">
+        <v>110.0868992340919</v>
+      </c>
+      <c r="E90">
+        <v>290.644</v>
+      </c>
+      <c r="F90">
+        <v>370.744</v>
+      </c>
+      <c r="G90">
+        <v>38.8</v>
+      </c>
+      <c r="H90">
+        <v>341.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>28.6</v>
+      </c>
+      <c r="K90">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L90">
+        <v>19</v>
+      </c>
+      <c r="M90">
+        <v>88.5336672</v>
+      </c>
+      <c r="N90">
+        <v>-69.5336672</v>
+      </c>
+      <c r="O90">
+        <v>-15.992743456</v>
+      </c>
+      <c r="P90">
+        <v>-53.540923744</v>
+      </c>
+      <c r="Q90">
+        <v>-43.940923744</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5741260124277734</v>
+      </c>
+      <c r="T90">
+        <v>7.506615994850914</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.04935975361924237</v>
+      </c>
+      <c r="W90">
+        <v>0.2270128908357249</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2146076244314886</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2706664654267708</v>
+      </c>
+      <c r="C91">
+        <v>-227.019672313751</v>
+      </c>
+      <c r="D91">
+        <v>109.1373276862489</v>
+      </c>
+      <c r="E91">
+        <v>294.857</v>
+      </c>
+      <c r="F91">
+        <v>374.9569999999999</v>
+      </c>
+      <c r="G91">
+        <v>38.8</v>
+      </c>
+      <c r="H91">
+        <v>341.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>28.6</v>
+      </c>
+      <c r="K91">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L91">
+        <v>19</v>
+      </c>
+      <c r="M91">
+        <v>89.5397316</v>
+      </c>
+      <c r="N91">
+        <v>-70.5397316</v>
+      </c>
+      <c r="O91">
+        <v>-16.224138268</v>
+      </c>
+      <c r="P91">
+        <v>-54.315593332</v>
+      </c>
+      <c r="Q91">
+        <v>-44.715593332</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6227920135575709</v>
+      </c>
+      <c r="T91">
+        <v>8.189035630746451</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.04880514964599246</v>
+      </c>
+      <c r="W91">
+        <v>0.227145330264537</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2121963028086629</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2726664654267708</v>
+      </c>
+      <c r="C92">
+        <v>-232.1660026010763</v>
+      </c>
+      <c r="D92">
+        <v>108.2039973989237</v>
+      </c>
+      <c r="E92">
+        <v>299.0699999999999</v>
+      </c>
+      <c r="F92">
+        <v>379.17</v>
+      </c>
+      <c r="G92">
+        <v>38.8</v>
+      </c>
+      <c r="H92">
+        <v>341.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>28.6</v>
+      </c>
+      <c r="K92">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L92">
+        <v>19</v>
+      </c>
+      <c r="M92">
+        <v>90.545796</v>
+      </c>
+      <c r="N92">
+        <v>-71.545796</v>
+      </c>
+      <c r="O92">
+        <v>-16.45553308</v>
+      </c>
+      <c r="P92">
+        <v>-55.09026292</v>
+      </c>
+      <c r="Q92">
+        <v>-45.49026292</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6811912149133281</v>
+      </c>
+      <c r="T92">
+        <v>9.007939193821096</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.04826287020548143</v>
+      </c>
+      <c r="W92">
+        <v>0.227274826594931</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2098385661107889</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2746664654267708</v>
+      </c>
+      <c r="C93">
+        <v>-237.2965047750554</v>
+      </c>
+      <c r="D93">
+        <v>107.2864952249445</v>
+      </c>
+      <c r="E93">
+        <v>303.283</v>
+      </c>
+      <c r="F93">
+        <v>383.383</v>
+      </c>
+      <c r="G93">
+        <v>38.8</v>
+      </c>
+      <c r="H93">
+        <v>341.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>28.6</v>
+      </c>
+      <c r="K93">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L93">
+        <v>19</v>
+      </c>
+      <c r="M93">
+        <v>91.5518604</v>
+      </c>
+      <c r="N93">
+        <v>-72.5518604</v>
+      </c>
+      <c r="O93">
+        <v>-16.686927892</v>
+      </c>
+      <c r="P93">
+        <v>-55.864932508</v>
+      </c>
+      <c r="Q93">
+        <v>-46.26493250799999</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7525680165703645</v>
+      </c>
+      <c r="T93">
+        <v>10.00882132646789</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.04773250899443218</v>
+      </c>
+      <c r="W93">
+        <v>0.2274014768521296</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2075326478018791</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2766664654267708</v>
+      </c>
+      <c r="C94">
+        <v>-242.4115780877644</v>
+      </c>
+      <c r="D94">
+        <v>106.3844219122356</v>
+      </c>
+      <c r="E94">
+        <v>307.496</v>
+      </c>
+      <c r="F94">
+        <v>387.5959999999999</v>
+      </c>
+      <c r="G94">
+        <v>38.8</v>
+      </c>
+      <c r="H94">
+        <v>341.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>28.6</v>
+      </c>
+      <c r="K94">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L94">
+        <v>19</v>
+      </c>
+      <c r="M94">
+        <v>92.5579248</v>
+      </c>
+      <c r="N94">
+        <v>-73.5579248</v>
+      </c>
+      <c r="O94">
+        <v>-16.918322704</v>
+      </c>
+      <c r="P94">
+        <v>-56.639602096</v>
+      </c>
+      <c r="Q94">
+        <v>-47.039602096</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8417890186416606</v>
+      </c>
+      <c r="T94">
+        <v>11.25992399227638</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.04721367737492749</v>
+      </c>
+      <c r="W94">
+        <v>0.2275253738428673</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2052768581518587</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2786664654267708</v>
+      </c>
+      <c r="C95">
+        <v>-247.5116084754674</v>
+      </c>
+      <c r="D95">
+        <v>105.4973915245325</v>
+      </c>
+      <c r="E95">
+        <v>311.7089999999999</v>
+      </c>
+      <c r="F95">
+        <v>391.809</v>
+      </c>
+      <c r="G95">
+        <v>38.8</v>
+      </c>
+      <c r="H95">
+        <v>341.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>28.6</v>
+      </c>
+      <c r="K95">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L95">
+        <v>19</v>
+      </c>
+      <c r="M95">
+        <v>93.56398919999999</v>
+      </c>
+      <c r="N95">
+        <v>-74.56398919999999</v>
+      </c>
+      <c r="O95">
+        <v>-17.149717516</v>
+      </c>
+      <c r="P95">
+        <v>-57.414271684</v>
+      </c>
+      <c r="Q95">
+        <v>-47.814271684</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.956501735590469</v>
+      </c>
+      <c r="T95">
+        <v>12.86848456260157</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.04670600342465945</v>
+      </c>
+      <c r="W95">
+        <v>0.2276466063821913</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.203069580107215</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2806664654267708</v>
+      </c>
+      <c r="C96">
+        <v>-252.5969691091616</v>
+      </c>
+      <c r="D96">
+        <v>104.6250308908384</v>
+      </c>
+      <c r="E96">
+        <v>315.922</v>
+      </c>
+      <c r="F96">
+        <v>396.022</v>
+      </c>
+      <c r="G96">
+        <v>38.8</v>
+      </c>
+      <c r="H96">
+        <v>341.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>28.6</v>
+      </c>
+      <c r="K96">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L96">
+        <v>19</v>
+      </c>
+      <c r="M96">
+        <v>94.57005360000001</v>
+      </c>
+      <c r="N96">
+        <v>-75.57005360000001</v>
+      </c>
+      <c r="O96">
+        <v>-17.381112328</v>
+      </c>
+      <c r="P96">
+        <v>-58.18894127200001</v>
+      </c>
+      <c r="Q96">
+        <v>-48.58894127200001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.109452024855548</v>
+      </c>
+      <c r="T96">
+        <v>15.01323198970184</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.04620913104780136</v>
+      </c>
+      <c r="W96">
+        <v>0.2277652595057851</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2009092654252234</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2826664654267708</v>
+      </c>
+      <c r="C97">
+        <v>-257.6680209180295</v>
+      </c>
+      <c r="D97">
+        <v>103.7669790819704</v>
+      </c>
+      <c r="E97">
+        <v>320.135</v>
+      </c>
+      <c r="F97">
+        <v>400.235</v>
+      </c>
+      <c r="G97">
+        <v>38.8</v>
+      </c>
+      <c r="H97">
+        <v>341.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>28.6</v>
+      </c>
+      <c r="K97">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L97">
+        <v>19</v>
+      </c>
+      <c r="M97">
+        <v>95.57611799999999</v>
+      </c>
+      <c r="N97">
+        <v>-76.57611799999999</v>
+      </c>
+      <c r="O97">
+        <v>-17.61250714</v>
+      </c>
+      <c r="P97">
+        <v>-58.96361086</v>
+      </c>
+      <c r="Q97">
+        <v>-49.36361085999999</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.323582429826658</v>
+      </c>
+      <c r="T97">
+        <v>18.01587838764221</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.04572271914203504</v>
+      </c>
+      <c r="W97">
+        <v>0.227881414668882</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1987944310523263</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2846664654267708</v>
+      </c>
+      <c r="C98">
+        <v>-262.7251130873447</v>
+      </c>
+      <c r="D98">
+        <v>102.9228869126552</v>
+      </c>
+      <c r="E98">
+        <v>324.348</v>
+      </c>
+      <c r="F98">
+        <v>404.4479999999999</v>
+      </c>
+      <c r="G98">
+        <v>38.8</v>
+      </c>
+      <c r="H98">
+        <v>341.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>28.6</v>
+      </c>
+      <c r="K98">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L98">
+        <v>19</v>
+      </c>
+      <c r="M98">
+        <v>96.58218239999998</v>
+      </c>
+      <c r="N98">
+        <v>-77.58218239999998</v>
+      </c>
+      <c r="O98">
+        <v>-17.84390195199999</v>
+      </c>
+      <c r="P98">
+        <v>-59.73828044799998</v>
+      </c>
+      <c r="Q98">
+        <v>-50.13828044799998</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.644778037283319</v>
+      </c>
+      <c r="T98">
+        <v>22.51984798455272</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.04524644081763885</v>
+      </c>
+      <c r="W98">
+        <v>0.2279951499327479</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1967236557288646</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2866664654267708</v>
+      </c>
+      <c r="C99">
+        <v>-267.7685835322711</v>
+      </c>
+      <c r="D99">
+        <v>102.0924164677288</v>
+      </c>
+      <c r="E99">
+        <v>328.5609999999999</v>
+      </c>
+      <c r="F99">
+        <v>408.6609999999999</v>
+      </c>
+      <c r="G99">
+        <v>38.8</v>
+      </c>
+      <c r="H99">
+        <v>341.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>28.6</v>
+      </c>
+      <c r="K99">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L99">
+        <v>19</v>
+      </c>
+      <c r="M99">
+        <v>97.58824679999999</v>
+      </c>
+      <c r="N99">
+        <v>-78.58824679999999</v>
+      </c>
+      <c r="O99">
+        <v>-18.075296764</v>
+      </c>
+      <c r="P99">
+        <v>-60.51295003599999</v>
+      </c>
+      <c r="Q99">
+        <v>-50.91295003599999</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.180104049711092</v>
+      </c>
+      <c r="T99">
+        <v>30.02646397940363</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.04477998266487968</v>
+      </c>
+      <c r="W99">
+        <v>0.2281065401396268</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1946955768038248</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2886664654267708</v>
+      </c>
+      <c r="C100">
+        <v>-272.7987593489087</v>
+      </c>
+      <c r="D100">
+        <v>101.2752406510913</v>
+      </c>
+      <c r="E100">
+        <v>332.774</v>
+      </c>
+      <c r="F100">
+        <v>412.874</v>
+      </c>
+      <c r="G100">
+        <v>38.8</v>
+      </c>
+      <c r="H100">
+        <v>341.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>28.6</v>
+      </c>
+      <c r="K100">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L100">
+        <v>19</v>
+      </c>
+      <c r="M100">
+        <v>98.59431119999999</v>
+      </c>
+      <c r="N100">
+        <v>-79.59431119999999</v>
+      </c>
+      <c r="O100">
+        <v>-18.306691576</v>
+      </c>
+      <c r="P100">
+        <v>-61.28761962399999</v>
+      </c>
+      <c r="Q100">
+        <v>-51.68761962399999</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.250756074566637</v>
+      </c>
+      <c r="T100">
+        <v>45.03969596910544</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.04432304406625846</v>
+      </c>
+      <c r="W100">
+        <v>0.2282156570769775</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.192708887244602</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2906664654267708</v>
+      </c>
+      <c r="C101">
+        <v>-277.8159572438486</v>
+      </c>
+      <c r="D101">
+        <v>100.4710427561513</v>
+      </c>
+      <c r="E101">
+        <v>336.987</v>
+      </c>
+      <c r="F101">
+        <v>417.0869999999999</v>
+      </c>
+      <c r="G101">
+        <v>38.8</v>
+      </c>
+      <c r="H101">
+        <v>341.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>28.6</v>
+      </c>
+      <c r="K101">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="L101">
+        <v>19</v>
+      </c>
+      <c r="M101">
+        <v>99.60037559999999</v>
+      </c>
+      <c r="N101">
+        <v>-80.60037559999999</v>
+      </c>
+      <c r="O101">
+        <v>-18.538086388</v>
+      </c>
+      <c r="P101">
+        <v>-62.062289212</v>
+      </c>
+      <c r="Q101">
+        <v>-52.46228921199999</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.462712149133274</v>
+      </c>
+      <c r="T101">
+        <v>90.07939193821088</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.04387533655043767</v>
+      </c>
+      <c r="W101">
+        <v>0.2283225696317555</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1907623328279898</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/israel/israel_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_construction_supplies.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09205096276314527</v>
+        <v>0.09187389554879004</v>
       </c>
       <c r="C2">
-        <v>722.3037337108051</v>
+        <v>717.8214134415275</v>
       </c>
       <c r="D2">
-        <v>717.3037337108051</v>
+        <v>720.0604134415275</v>
       </c>
       <c r="E2">
-        <v>-44.6</v>
+        <v>-37.361</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7.239</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -1439,28 +1439,28 @@
         <v>30.7</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3641217</v>
       </c>
       <c r="N2">
-        <v>30.7</v>
+        <v>30.3358783</v>
       </c>
       <c r="O2">
-        <v>7.061</v>
+        <v>6.977252009000001</v>
       </c>
       <c r="P2">
-        <v>23.639</v>
+        <v>23.358626291</v>
       </c>
       <c r="Q2">
-        <v>33.439</v>
+        <v>33.158626291</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09205096276314527</v>
+        <v>0.09241069247352529</v>
       </c>
       <c r="T2">
-        <v>0.715487684377053</v>
+        <v>0.7210525885888747</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>84.31247025376406</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09187389554879004</v>
+        <v>0.09169682833443479</v>
       </c>
       <c r="C3">
-        <v>717.8214134415275</v>
+        <v>713.3603633827859</v>
       </c>
       <c r="D3">
-        <v>720.0604134415275</v>
+        <v>722.8383633827858</v>
       </c>
       <c r="E3">
-        <v>-37.361</v>
+        <v>-30.122</v>
       </c>
       <c r="F3">
-        <v>7.239</v>
+        <v>14.478</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -1521,28 +1521,28 @@
         <v>30.7</v>
       </c>
       <c r="M3">
-        <v>0.3641217</v>
+        <v>0.7282434</v>
       </c>
       <c r="N3">
-        <v>30.3358783</v>
+        <v>29.9717566</v>
       </c>
       <c r="O3">
-        <v>6.977252009000001</v>
+        <v>6.893504018</v>
       </c>
       <c r="P3">
-        <v>23.358626291</v>
+        <v>23.078252582</v>
       </c>
       <c r="Q3">
-        <v>33.158626291</v>
+        <v>32.878252582</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09241069247352529</v>
+        <v>0.09277776360656612</v>
       </c>
       <c r="T3">
-        <v>0.7210525885888747</v>
+        <v>0.7267310622744068</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>84.31247025376406</v>
+        <v>42.15623512688203</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09169682833443479</v>
+        <v>0.09151976112007958</v>
       </c>
       <c r="C4">
-        <v>713.3603633827859</v>
+        <v>708.9208306655897</v>
       </c>
       <c r="D4">
-        <v>722.8383633827858</v>
+        <v>725.6378306655897</v>
       </c>
       <c r="E4">
-        <v>-30.122</v>
+        <v>-22.883</v>
       </c>
       <c r="F4">
-        <v>14.478</v>
+        <v>21.717</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -1603,28 +1603,28 @@
         <v>30.7</v>
       </c>
       <c r="M4">
-        <v>0.7282434</v>
+        <v>1.0923651</v>
       </c>
       <c r="N4">
-        <v>29.9717566</v>
+        <v>29.6076349</v>
       </c>
       <c r="O4">
-        <v>6.893504018</v>
+        <v>6.809756027000001</v>
       </c>
       <c r="P4">
-        <v>23.078252582</v>
+        <v>22.797878873</v>
       </c>
       <c r="Q4">
-        <v>32.878252582</v>
+        <v>32.597878873</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09277776360656612</v>
+        <v>0.09315240321657688</v>
       </c>
       <c r="T4">
-        <v>0.7267310622744068</v>
+        <v>0.7325266178915993</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>42.15623512688203</v>
+        <v>28.10415675125469</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09151976112007958</v>
+        <v>0.09134269390572432</v>
       </c>
       <c r="C5">
-        <v>708.9208306655897</v>
+        <v>704.5030662642727</v>
       </c>
       <c r="D5">
-        <v>725.6378306655897</v>
+        <v>728.4590662642727</v>
       </c>
       <c r="E5">
-        <v>-22.883</v>
+        <v>-15.644</v>
       </c>
       <c r="F5">
-        <v>21.717</v>
+        <v>28.956</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -1685,28 +1685,28 @@
         <v>30.7</v>
       </c>
       <c r="M5">
-        <v>1.0923651</v>
+        <v>1.4564868</v>
       </c>
       <c r="N5">
-        <v>29.6076349</v>
+        <v>29.2435132</v>
       </c>
       <c r="O5">
-        <v>6.809756027000001</v>
+        <v>6.726008036</v>
       </c>
       <c r="P5">
-        <v>22.797878873</v>
+        <v>22.517505164</v>
       </c>
       <c r="Q5">
-        <v>32.597878873</v>
+        <v>32.317505164</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09315240321657688</v>
+        <v>0.09353484781846284</v>
       </c>
       <c r="T5">
-        <v>0.7325266178915993</v>
+        <v>0.7384429142508168</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>28.10415675125469</v>
+        <v>21.07811756344102</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09134269390572432</v>
+        <v>0.09116562669136909</v>
       </c>
       <c r="C6">
-        <v>704.5030662642727</v>
+        <v>700.1073250714912</v>
       </c>
       <c r="D6">
-        <v>728.4590662642727</v>
+        <v>731.3023250714913</v>
       </c>
       <c r="E6">
-        <v>-15.644</v>
+        <v>-8.405000000000001</v>
       </c>
       <c r="F6">
-        <v>28.956</v>
+        <v>36.195</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -1767,28 +1767,28 @@
         <v>30.7</v>
       </c>
       <c r="M6">
-        <v>1.4564868</v>
+        <v>1.8206085</v>
       </c>
       <c r="N6">
-        <v>29.2435132</v>
+        <v>28.8793915</v>
       </c>
       <c r="O6">
-        <v>6.726008036</v>
+        <v>6.642260045</v>
       </c>
       <c r="P6">
-        <v>22.517505164</v>
+        <v>22.237131455</v>
       </c>
       <c r="Q6">
-        <v>32.317505164</v>
+        <v>32.037131455</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09353484781846284</v>
+        <v>0.09392534388565169</v>
       </c>
       <c r="T6">
-        <v>0.7384429142508168</v>
+        <v>0.7444837642175968</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>21.07811756344102</v>
+        <v>16.86249405075282</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09116562669136909</v>
+        <v>0.09098855947701387</v>
       </c>
       <c r="C7">
-        <v>700.1073250714912</v>
+        <v>695.7338659749973</v>
       </c>
       <c r="D7">
-        <v>731.3023250714913</v>
+        <v>734.1678659749973</v>
       </c>
       <c r="E7">
-        <v>-8.405000000000001</v>
+        <v>-1.165999999999997</v>
       </c>
       <c r="F7">
-        <v>36.195</v>
+        <v>43.434</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -1849,28 +1849,28 @@
         <v>30.7</v>
       </c>
       <c r="M7">
-        <v>1.8206085</v>
+        <v>2.1847302</v>
       </c>
       <c r="N7">
-        <v>28.8793915</v>
+        <v>28.5152698</v>
       </c>
       <c r="O7">
-        <v>6.642260045</v>
+        <v>6.558512054</v>
       </c>
       <c r="P7">
-        <v>22.237131455</v>
+        <v>21.956757746</v>
       </c>
       <c r="Q7">
-        <v>32.037131455</v>
+        <v>31.756757746</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09392534388565169</v>
+        <v>0.09432414837980199</v>
       </c>
       <c r="T7">
-        <v>0.7444837642175968</v>
+        <v>0.7506531429070742</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>16.86249405075282</v>
+        <v>14.05207837562734</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09098855947701386</v>
+        <v>0.09089234226265865</v>
       </c>
       <c r="C8">
-        <v>695.7338659749976</v>
+        <v>690.0614199260376</v>
       </c>
       <c r="D8">
-        <v>734.1678659749975</v>
+        <v>735.7344199260376</v>
       </c>
       <c r="E8">
-        <v>-1.166000000000004</v>
+        <v>6.072999999999993</v>
       </c>
       <c r="F8">
-        <v>43.434</v>
+        <v>50.67299999999999</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -1931,45 +1931,45 @@
         <v>30.7</v>
       </c>
       <c r="M8">
-        <v>2.1847302</v>
+        <v>2.624861399999999</v>
       </c>
       <c r="N8">
-        <v>28.5152698</v>
+        <v>28.0751386</v>
       </c>
       <c r="O8">
-        <v>6.558512054</v>
+        <v>6.457281878</v>
       </c>
       <c r="P8">
-        <v>21.956757746</v>
+        <v>21.617856722</v>
       </c>
       <c r="Q8">
-        <v>31.756757746</v>
+        <v>31.417856722</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09432414837980198</v>
+        <v>0.0947315293146867</v>
       </c>
       <c r="T8">
-        <v>0.7506531429070741</v>
+        <v>0.7569551964070779</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.23</v>
       </c>
       <c r="W8">
-        <v>0.038731</v>
+        <v>0.039886</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>14.05207837562734</v>
+        <v>11.6958556364157</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09089234226265863</v>
+        <v>0.0907268250483034</v>
       </c>
       <c r="C9">
-        <v>690.061419926038</v>
+        <v>685.5329767383765</v>
       </c>
       <c r="D9">
-        <v>735.734419926038</v>
+        <v>738.4449767383766</v>
       </c>
       <c r="E9">
-        <v>6.073</v>
+        <v>13.312</v>
       </c>
       <c r="F9">
-        <v>50.673</v>
+        <v>57.912</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -2013,28 +2013,28 @@
         <v>30.7</v>
       </c>
       <c r="M9">
-        <v>2.6248614</v>
+        <v>2.9998416</v>
       </c>
       <c r="N9">
-        <v>28.0751386</v>
+        <v>27.7001584</v>
       </c>
       <c r="O9">
-        <v>6.457281878</v>
+        <v>6.371036432</v>
       </c>
       <c r="P9">
-        <v>21.617856722</v>
+        <v>21.329121968</v>
       </c>
       <c r="Q9">
-        <v>31.417856722</v>
+        <v>31.129121968</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0947315293146867</v>
+        <v>0.09514776635685152</v>
       </c>
       <c r="T9">
-        <v>0.7569551964070779</v>
+        <v>0.7633942510701252</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.6958556364157</v>
+        <v>10.23387368186374</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0907268250483034</v>
+        <v>0.09067911783394818</v>
       </c>
       <c r="C10">
-        <v>685.5329767383765</v>
+        <v>679.0789554655687</v>
       </c>
       <c r="D10">
-        <v>738.4449767383766</v>
+        <v>739.2299554655687</v>
       </c>
       <c r="E10">
-        <v>13.312</v>
+        <v>20.55099999999999</v>
       </c>
       <c r="F10">
-        <v>57.912</v>
+        <v>65.151</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -2095,45 +2095,45 @@
         <v>30.7</v>
       </c>
       <c r="M10">
-        <v>2.9998416</v>
+        <v>3.4855785</v>
       </c>
       <c r="N10">
-        <v>27.7001584</v>
+        <v>27.2144215</v>
       </c>
       <c r="O10">
-        <v>6.371036432</v>
+        <v>6.259316945</v>
       </c>
       <c r="P10">
-        <v>21.329121968</v>
+        <v>20.955104555</v>
       </c>
       <c r="Q10">
-        <v>31.129121968</v>
+        <v>30.755104555</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09514776635685152</v>
+        <v>0.09557315146587711</v>
       </c>
       <c r="T10">
-        <v>0.7633942510701252</v>
+        <v>0.7699748234180748</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.23</v>
       </c>
       <c r="W10">
-        <v>0.039886</v>
+        <v>0.041195</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.23387368186374</v>
+        <v>8.807720153196952</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09067911783394818</v>
+        <v>0.09052669061959294</v>
       </c>
       <c r="C11">
-        <v>679.0789554655687</v>
+        <v>674.3592288863972</v>
       </c>
       <c r="D11">
-        <v>739.2299554655687</v>
+        <v>741.7492288863972</v>
       </c>
       <c r="E11">
-        <v>20.55099999999999</v>
+        <v>27.78999999999998</v>
       </c>
       <c r="F11">
-        <v>65.151</v>
+        <v>72.38999999999999</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -2177,28 +2177,28 @@
         <v>30.7</v>
       </c>
       <c r="M11">
-        <v>3.4855785</v>
+        <v>3.872864999999999</v>
       </c>
       <c r="N11">
-        <v>27.2144215</v>
+        <v>26.827135</v>
       </c>
       <c r="O11">
-        <v>6.259316945</v>
+        <v>6.17024105</v>
       </c>
       <c r="P11">
-        <v>20.955104555</v>
+        <v>20.65689395</v>
       </c>
       <c r="Q11">
-        <v>30.755104555</v>
+        <v>30.45689395</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09557315146587711</v>
+        <v>0.09600798957732548</v>
       </c>
       <c r="T11">
-        <v>0.7699748234180748</v>
+        <v>0.7767016307070898</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.807720153196952</v>
+        <v>7.926948137877257</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09052669061959294</v>
+        <v>0.09044202340523771</v>
       </c>
       <c r="C12">
-        <v>674.3592288863972</v>
+        <v>668.5270163966733</v>
       </c>
       <c r="D12">
-        <v>741.7492288863972</v>
+        <v>743.1560163966733</v>
       </c>
       <c r="E12">
-        <v>27.79</v>
+        <v>35.029</v>
       </c>
       <c r="F12">
-        <v>72.39</v>
+        <v>79.629</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -2259,45 +2259,45 @@
         <v>30.7</v>
       </c>
       <c r="M12">
-        <v>3.872865</v>
+        <v>4.3238547</v>
       </c>
       <c r="N12">
-        <v>26.827135</v>
+        <v>26.3761453</v>
       </c>
       <c r="O12">
-        <v>6.17024105</v>
+        <v>6.066513419</v>
       </c>
       <c r="P12">
-        <v>20.65689395</v>
+        <v>20.309631881</v>
       </c>
       <c r="Q12">
-        <v>30.45689395</v>
+        <v>30.109631881</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09600798957732548</v>
+        <v>0.09645259933172776</v>
       </c>
       <c r="T12">
-        <v>0.7767016307070898</v>
+        <v>0.7835796022048468</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.23</v>
       </c>
       <c r="W12">
-        <v>0.041195</v>
+        <v>0.041811</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>7.926948137877256</v>
+        <v>7.100146080301911</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09044202340523771</v>
+        <v>0.09029575619088247</v>
       </c>
       <c r="C13">
-        <v>668.5270163966733</v>
+        <v>663.7309316239903</v>
       </c>
       <c r="D13">
-        <v>743.1560163966733</v>
+        <v>745.5989316239902</v>
       </c>
       <c r="E13">
-        <v>35.029</v>
+        <v>42.26799999999999</v>
       </c>
       <c r="F13">
-        <v>79.629</v>
+        <v>86.86799999999999</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -2341,28 +2341,28 @@
         <v>30.7</v>
       </c>
       <c r="M13">
-        <v>4.3238547</v>
+        <v>4.7169324</v>
       </c>
       <c r="N13">
-        <v>26.3761453</v>
+        <v>25.9830676</v>
       </c>
       <c r="O13">
-        <v>6.066513419</v>
+        <v>5.976105548</v>
       </c>
       <c r="P13">
-        <v>20.309631881</v>
+        <v>20.006962052</v>
       </c>
       <c r="Q13">
-        <v>30.109631881</v>
+        <v>29.806962052</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09645259933172776</v>
+        <v>0.09690731385327553</v>
       </c>
       <c r="T13">
-        <v>0.7835796022048468</v>
+        <v>0.7906138912366436</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.100146080301911</v>
+        <v>6.508467240276752</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09029575619088247</v>
+        <v>0.09024958897652723</v>
       </c>
       <c r="C14">
-        <v>663.7309316239903</v>
+        <v>657.2663420626897</v>
       </c>
       <c r="D14">
-        <v>745.5989316239902</v>
+        <v>746.3733420626896</v>
       </c>
       <c r="E14">
-        <v>42.26799999999999</v>
+        <v>49.507</v>
       </c>
       <c r="F14">
-        <v>86.86799999999999</v>
+        <v>94.107</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -2423,45 +2423,45 @@
         <v>30.7</v>
       </c>
       <c r="M14">
-        <v>4.7169324</v>
+        <v>5.2041171</v>
       </c>
       <c r="N14">
-        <v>25.9830676</v>
+        <v>25.4958829</v>
       </c>
       <c r="O14">
-        <v>5.976105548</v>
+        <v>5.864053067</v>
       </c>
       <c r="P14">
-        <v>20.006962052</v>
+        <v>19.631829833</v>
       </c>
       <c r="Q14">
-        <v>29.806962052</v>
+        <v>29.431829833</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09690731385327553</v>
+        <v>0.0973724815822152</v>
       </c>
       <c r="T14">
-        <v>0.7906138912366436</v>
+        <v>0.7978098880622748</v>
       </c>
       <c r="U14">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V14">
         <v>0.23</v>
       </c>
       <c r="W14">
-        <v>0.041811</v>
+        <v>0.042581</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.508467240276752</v>
+        <v>5.89917548165855</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09024958897652723</v>
+        <v>0.09011102176217199</v>
       </c>
       <c r="C15">
-        <v>657.2663420626897</v>
+        <v>652.3613635039854</v>
       </c>
       <c r="D15">
-        <v>746.3733420626896</v>
+        <v>748.7073635039854</v>
       </c>
       <c r="E15">
-        <v>49.507</v>
+        <v>56.746</v>
       </c>
       <c r="F15">
-        <v>94.107</v>
+        <v>101.346</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -2505,28 +2505,28 @@
         <v>30.7</v>
       </c>
       <c r="M15">
-        <v>5.2041171</v>
+        <v>5.604433800000001</v>
       </c>
       <c r="N15">
-        <v>25.4958829</v>
+        <v>25.0955662</v>
       </c>
       <c r="O15">
-        <v>5.864053067</v>
+        <v>5.771980226</v>
       </c>
       <c r="P15">
-        <v>19.631829833</v>
+        <v>19.323585974</v>
       </c>
       <c r="Q15">
-        <v>29.431829833</v>
+        <v>29.123585974</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0973724815822152</v>
+        <v>0.09784846716531627</v>
       </c>
       <c r="T15">
-        <v>0.7978098880622748</v>
+        <v>0.8051732336512929</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.89917548165855</v>
+        <v>5.477805804397225</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09011102176217199</v>
+        <v>0.08997245454781674</v>
       </c>
       <c r="C16">
-        <v>652.3613635039854</v>
+        <v>647.4710284081668</v>
       </c>
       <c r="D16">
-        <v>748.7073635039854</v>
+        <v>751.0560284081669</v>
       </c>
       <c r="E16">
-        <v>56.746</v>
+        <v>63.98500000000001</v>
       </c>
       <c r="F16">
-        <v>101.346</v>
+        <v>108.585</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -2587,28 +2587,28 @@
         <v>30.7</v>
       </c>
       <c r="M16">
-        <v>5.604433800000001</v>
+        <v>6.004750500000001</v>
       </c>
       <c r="N16">
-        <v>25.0955662</v>
+        <v>24.6952495</v>
       </c>
       <c r="O16">
-        <v>5.771980226</v>
+        <v>5.679907385</v>
       </c>
       <c r="P16">
-        <v>19.323585974</v>
+        <v>19.015342115</v>
       </c>
       <c r="Q16">
-        <v>29.123585974</v>
+        <v>28.815342115</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09784846716531627</v>
+        <v>0.09833565240919619</v>
       </c>
       <c r="T16">
-        <v>0.8051732336512929</v>
+        <v>0.8127098344306408</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.477805804397225</v>
+        <v>5.112618750770743</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08997245454781674</v>
+        <v>0.08983388733346151</v>
       </c>
       <c r="C17">
-        <v>647.4710284081668</v>
+        <v>642.5954750167551</v>
       </c>
       <c r="D17">
-        <v>751.0560284081669</v>
+        <v>753.4194750167551</v>
       </c>
       <c r="E17">
-        <v>63.98499999999999</v>
+        <v>71.22399999999999</v>
       </c>
       <c r="F17">
-        <v>108.585</v>
+        <v>115.824</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -2669,28 +2669,28 @@
         <v>30.7</v>
       </c>
       <c r="M17">
-        <v>6.0047505</v>
+        <v>6.4050672</v>
       </c>
       <c r="N17">
-        <v>24.6952495</v>
+        <v>24.2949328</v>
       </c>
       <c r="O17">
-        <v>5.679907385</v>
+        <v>5.587834544</v>
       </c>
       <c r="P17">
-        <v>19.015342115</v>
+        <v>18.707098256</v>
       </c>
       <c r="Q17">
-        <v>28.815342115</v>
+        <v>28.507098256</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09833565240919619</v>
+        <v>0.09883443730173991</v>
       </c>
       <c r="T17">
-        <v>0.8127098344306408</v>
+        <v>0.8204258780856875</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.112618750770744</v>
+        <v>4.793080078847572</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08983388733346151</v>
+        <v>0.08969532011910629</v>
       </c>
       <c r="C18">
-        <v>642.5954750167551</v>
+        <v>637.7348433168555</v>
       </c>
       <c r="D18">
-        <v>753.4194750167551</v>
+        <v>755.7978433168555</v>
       </c>
       <c r="E18">
-        <v>71.22399999999999</v>
+        <v>78.46299999999999</v>
       </c>
       <c r="F18">
-        <v>115.824</v>
+        <v>123.063</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -2751,28 +2751,28 @@
         <v>30.7</v>
       </c>
       <c r="M18">
-        <v>6.4050672</v>
+        <v>6.805383900000001</v>
       </c>
       <c r="N18">
-        <v>24.2949328</v>
+        <v>23.8946161</v>
       </c>
       <c r="O18">
-        <v>5.587834544</v>
+        <v>5.495761703</v>
       </c>
       <c r="P18">
-        <v>18.707098256</v>
+        <v>18.398854397</v>
       </c>
       <c r="Q18">
-        <v>28.507098256</v>
+        <v>28.198854397</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09883443730173991</v>
+        <v>0.09934524110735697</v>
       </c>
       <c r="T18">
-        <v>0.8204258780856875</v>
+        <v>0.8283278505035063</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.793080078847572</v>
+        <v>4.511134191856538</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08969532011910629</v>
+        <v>0.08990325290475105</v>
       </c>
       <c r="C19">
-        <v>637.7348433168555</v>
+        <v>626.9324972914595</v>
       </c>
       <c r="D19">
-        <v>755.7978433168555</v>
+        <v>752.2344972914595</v>
       </c>
       <c r="E19">
-        <v>78.46299999999999</v>
+        <v>85.70200000000003</v>
       </c>
       <c r="F19">
-        <v>123.063</v>
+        <v>130.302</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -2833,45 +2833,45 @@
         <v>30.7</v>
       </c>
       <c r="M19">
-        <v>6.805383900000001</v>
+        <v>7.531455600000002</v>
       </c>
       <c r="N19">
-        <v>23.8946161</v>
+        <v>23.1685444</v>
       </c>
       <c r="O19">
-        <v>5.495761703</v>
+        <v>5.328765212</v>
       </c>
       <c r="P19">
-        <v>18.398854397</v>
+        <v>17.839779188</v>
       </c>
       <c r="Q19">
-        <v>28.198854397</v>
+        <v>27.639779188</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09934524110735697</v>
+        <v>0.09986850354237933</v>
       </c>
       <c r="T19">
-        <v>0.8283278505035063</v>
+        <v>0.836422553955906</v>
       </c>
       <c r="U19">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V19">
         <v>0.23</v>
       </c>
       <c r="W19">
-        <v>0.042581</v>
+        <v>0.044506</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.511134191856538</v>
+        <v>4.076237268131806</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08990325290475107</v>
+        <v>0.09029598569039582</v>
       </c>
       <c r="C20">
-        <v>626.9324972914594</v>
+        <v>613.0540860053504</v>
       </c>
       <c r="D20">
-        <v>752.2344972914594</v>
+        <v>745.5950860053505</v>
       </c>
       <c r="E20">
-        <v>85.702</v>
+        <v>92.941</v>
       </c>
       <c r="F20">
-        <v>130.302</v>
+        <v>137.541</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -2915,45 +2915,45 @@
         <v>30.7</v>
       </c>
       <c r="M20">
-        <v>7.5314556</v>
+        <v>8.431263299999999</v>
       </c>
       <c r="N20">
-        <v>23.1685444</v>
+        <v>22.2687367</v>
       </c>
       <c r="O20">
-        <v>5.328765212</v>
+        <v>5.121809441</v>
       </c>
       <c r="P20">
-        <v>17.839779188</v>
+        <v>17.146927259</v>
       </c>
       <c r="Q20">
-        <v>27.639779188</v>
+        <v>26.946927259</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09986850354237933</v>
+        <v>0.1004046860375257</v>
       </c>
       <c r="T20">
-        <v>0.836422553955906</v>
+        <v>0.8447171266293528</v>
       </c>
       <c r="U20">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V20">
         <v>0.23</v>
       </c>
       <c r="W20">
-        <v>0.044506</v>
+        <v>0.047201</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.076237268131807</v>
+        <v>3.641209971464181</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09029598569039582</v>
+        <v>0.09063481847604059</v>
       </c>
       <c r="C21">
-        <v>613.0540860053504</v>
+        <v>600.1803568251877</v>
       </c>
       <c r="D21">
-        <v>745.5950860053505</v>
+        <v>739.9603568251877</v>
       </c>
       <c r="E21">
-        <v>92.941</v>
+        <v>100.18</v>
       </c>
       <c r="F21">
-        <v>137.541</v>
+        <v>144.78</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -2997,45 +2997,45 @@
         <v>30.7</v>
       </c>
       <c r="M21">
-        <v>8.431263299999999</v>
+        <v>9.280398</v>
       </c>
       <c r="N21">
-        <v>22.2687367</v>
+        <v>21.419602</v>
       </c>
       <c r="O21">
-        <v>5.121809441</v>
+        <v>4.92650846</v>
       </c>
       <c r="P21">
-        <v>17.146927259</v>
+        <v>16.49309354</v>
       </c>
       <c r="Q21">
-        <v>26.946927259</v>
+        <v>26.29309354</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1004046860375257</v>
+        <v>0.1009542730950507</v>
       </c>
       <c r="T21">
-        <v>0.8447171266293528</v>
+        <v>0.8532190636196356</v>
       </c>
       <c r="U21">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V21">
         <v>0.23</v>
       </c>
       <c r="W21">
-        <v>0.047201</v>
+        <v>0.04935700000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>3.641209971464181</v>
+        <v>3.308047779847373</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09063481847604059</v>
+        <v>0.09056401126168537</v>
       </c>
       <c r="C22">
-        <v>600.1803568251877</v>
+        <v>594.1118178746633</v>
       </c>
       <c r="D22">
-        <v>739.9603568251877</v>
+        <v>741.1308178746633</v>
       </c>
       <c r="E22">
-        <v>100.18</v>
+        <v>107.419</v>
       </c>
       <c r="F22">
-        <v>144.78</v>
+        <v>152.019</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -3079,28 +3079,28 @@
         <v>30.7</v>
       </c>
       <c r="M22">
-        <v>9.280398</v>
+        <v>9.7444179</v>
       </c>
       <c r="N22">
-        <v>21.419602</v>
+        <v>20.9555821</v>
       </c>
       <c r="O22">
-        <v>4.92650846</v>
+        <v>4.819783883</v>
       </c>
       <c r="P22">
-        <v>16.49309354</v>
+        <v>16.135798217</v>
       </c>
       <c r="Q22">
-        <v>26.29309354</v>
+        <v>25.935798217</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1009542730950507</v>
+        <v>0.1015177737489688</v>
       </c>
       <c r="T22">
-        <v>0.8532190636196356</v>
+        <v>0.861936239521065</v>
       </c>
       <c r="U22">
         <v>0.0641</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.308047779847373</v>
+        <v>3.150521695092736</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09056401126168537</v>
+        <v>0.09049320404733012</v>
       </c>
       <c r="C23">
-        <v>594.1118178746633</v>
+        <v>588.0469876350356</v>
       </c>
       <c r="D23">
-        <v>741.1308178746633</v>
+        <v>742.3049876350357</v>
       </c>
       <c r="E23">
-        <v>107.419</v>
+        <v>114.658</v>
       </c>
       <c r="F23">
-        <v>152.019</v>
+        <v>159.258</v>
       </c>
       <c r="G23">
         <v>5</v>
@@ -3161,28 +3161,28 @@
         <v>30.7</v>
       </c>
       <c r="M23">
-        <v>9.744417899999998</v>
+        <v>10.2084378</v>
       </c>
       <c r="N23">
-        <v>20.9555821</v>
+        <v>20.4915622</v>
       </c>
       <c r="O23">
-        <v>4.819783883</v>
+        <v>4.713059306</v>
       </c>
       <c r="P23">
-        <v>16.135798217</v>
+        <v>15.778502894</v>
       </c>
       <c r="Q23">
-        <v>25.935798217</v>
+        <v>25.578502894</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1015177737489688</v>
+        <v>0.1020957231376027</v>
       </c>
       <c r="T23">
-        <v>0.861936239521065</v>
+        <v>0.8708769327533001</v>
       </c>
       <c r="U23">
         <v>0.0641</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.150521695092737</v>
+        <v>3.007316163497611</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09049320404733012</v>
+        <v>0.09180377683297487</v>
       </c>
       <c r="C24">
-        <v>588.0469876350356</v>
+        <v>559.6609257541181</v>
       </c>
       <c r="D24">
-        <v>742.3049876350357</v>
+        <v>721.1579257541182</v>
       </c>
       <c r="E24">
-        <v>114.658</v>
+        <v>121.897</v>
       </c>
       <c r="F24">
-        <v>159.258</v>
+        <v>166.497</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -3243,45 +3243,45 @@
         <v>30.7</v>
       </c>
       <c r="M24">
-        <v>10.2084378</v>
+        <v>11.9711343</v>
       </c>
       <c r="N24">
-        <v>20.4915622</v>
+        <v>18.7288657</v>
       </c>
       <c r="O24">
-        <v>4.713059306</v>
+        <v>4.307639110999999</v>
       </c>
       <c r="P24">
-        <v>15.778502894</v>
+        <v>14.421226589</v>
       </c>
       <c r="Q24">
-        <v>25.578502894</v>
+        <v>24.221226589</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1020957231376027</v>
+        <v>0.1026886841986687</v>
       </c>
       <c r="T24">
-        <v>0.8708769327533001</v>
+        <v>0.8800498517837751</v>
       </c>
       <c r="U24">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V24">
         <v>0.23</v>
       </c>
       <c r="W24">
-        <v>0.04935700000000001</v>
+        <v>0.055363</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.007316163497611</v>
+        <v>2.564502179212875</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09180377683297487</v>
+        <v>0.09251374961861966</v>
       </c>
       <c r="C25">
-        <v>559.6609257541181</v>
+        <v>541.4615017757915</v>
       </c>
       <c r="D25">
-        <v>721.1579257541182</v>
+        <v>710.1975017757915</v>
       </c>
       <c r="E25">
-        <v>121.897</v>
+        <v>129.136</v>
       </c>
       <c r="F25">
-        <v>166.497</v>
+        <v>173.736</v>
       </c>
       <c r="G25">
         <v>5</v>
@@ -3325,45 +3325,45 @@
         <v>30.7</v>
       </c>
       <c r="M25">
-        <v>11.9711343</v>
+        <v>13.1691888</v>
       </c>
       <c r="N25">
-        <v>18.7288657</v>
+        <v>17.5308112</v>
       </c>
       <c r="O25">
-        <v>4.307639110999999</v>
+        <v>4.032086575999999</v>
       </c>
       <c r="P25">
-        <v>14.421226589</v>
+        <v>13.498724624</v>
       </c>
       <c r="Q25">
-        <v>24.221226589</v>
+        <v>23.29872462399999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1026886841986687</v>
+        <v>0.1032972494981838</v>
       </c>
       <c r="T25">
-        <v>0.8800498517837751</v>
+        <v>0.8894641634203153</v>
       </c>
       <c r="U25">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V25">
         <v>0.23</v>
       </c>
       <c r="W25">
-        <v>0.055363</v>
+        <v>0.05836600000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.564502179212875</v>
+        <v>2.331199018120235</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09251374961861966</v>
+        <v>0.09253303240426441</v>
       </c>
       <c r="C26">
-        <v>541.4615017757915</v>
+        <v>533.9294630944211</v>
       </c>
       <c r="D26">
-        <v>710.1975017757915</v>
+        <v>709.9044630944211</v>
       </c>
       <c r="E26">
-        <v>129.136</v>
+        <v>136.375</v>
       </c>
       <c r="F26">
-        <v>173.736</v>
+        <v>180.975</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -3407,28 +3407,28 @@
         <v>30.7</v>
       </c>
       <c r="M26">
-        <v>13.1691888</v>
+        <v>13.717905</v>
       </c>
       <c r="N26">
-        <v>17.5308112</v>
+        <v>16.982095</v>
       </c>
       <c r="O26">
-        <v>4.032086576</v>
+        <v>3.905881850000001</v>
       </c>
       <c r="P26">
-        <v>13.498724624</v>
+        <v>13.07621315</v>
       </c>
       <c r="Q26">
-        <v>23.298724624</v>
+        <v>22.87621315</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1032972494981838</v>
+        <v>0.1039220432056859</v>
       </c>
       <c r="T26">
-        <v>0.8894641634203153</v>
+        <v>0.8991295233671632</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.331199018120235</v>
+        <v>2.237951057395426</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09253303240426441</v>
+        <v>0.09255231518990918</v>
       </c>
       <c r="C27">
-        <v>533.9294630944211</v>
+        <v>526.3976661380671</v>
       </c>
       <c r="D27">
-        <v>709.9044630944211</v>
+        <v>709.611666138067</v>
       </c>
       <c r="E27">
-        <v>136.375</v>
+        <v>143.614</v>
       </c>
       <c r="F27">
-        <v>180.975</v>
+        <v>188.214</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -3489,28 +3489,28 @@
         <v>30.7</v>
       </c>
       <c r="M27">
-        <v>13.717905</v>
+        <v>14.2666212</v>
       </c>
       <c r="N27">
-        <v>16.982095</v>
+        <v>16.4333788</v>
       </c>
       <c r="O27">
-        <v>3.905881850000001</v>
+        <v>3.779677124</v>
       </c>
       <c r="P27">
-        <v>13.07621315</v>
+        <v>12.653701676</v>
       </c>
       <c r="Q27">
-        <v>22.87621315</v>
+        <v>22.453701676</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1039220432056859</v>
+        <v>0.104563723229607</v>
       </c>
       <c r="T27">
-        <v>0.8991295233671632</v>
+        <v>0.9090561092585207</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.237951057395426</v>
+        <v>2.151876016726371</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09255231518990918</v>
+        <v>0.09257159797555395</v>
       </c>
       <c r="C28">
-        <v>526.3976661380671</v>
+        <v>518.8661106077575</v>
       </c>
       <c r="D28">
-        <v>709.611666138067</v>
+        <v>709.3191106077575</v>
       </c>
       <c r="E28">
-        <v>143.614</v>
+        <v>150.853</v>
       </c>
       <c r="F28">
-        <v>188.214</v>
+        <v>195.453</v>
       </c>
       <c r="G28">
         <v>5</v>
@@ -3571,28 +3571,28 @@
         <v>30.7</v>
       </c>
       <c r="M28">
-        <v>14.2666212</v>
+        <v>14.8153374</v>
       </c>
       <c r="N28">
-        <v>16.4333788</v>
+        <v>15.8846626</v>
       </c>
       <c r="O28">
-        <v>3.779677124</v>
+        <v>3.653472398</v>
       </c>
       <c r="P28">
-        <v>12.653701676</v>
+        <v>12.231190202</v>
       </c>
       <c r="Q28">
-        <v>22.453701676</v>
+        <v>22.031190202</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.104563723229607</v>
+        <v>0.1052229835281561</v>
       </c>
       <c r="T28">
-        <v>0.9090561092585207</v>
+        <v>0.9192546564071754</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.151876016726371</v>
+        <v>2.072176904995764</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09257159797555395</v>
+        <v>0.09565240076119873</v>
       </c>
       <c r="C29">
-        <v>518.8661106077575</v>
+        <v>467.7922649733562</v>
       </c>
       <c r="D29">
-        <v>709.3191106077575</v>
+        <v>665.4842649733562</v>
       </c>
       <c r="E29">
-        <v>150.853</v>
+        <v>158.092</v>
       </c>
       <c r="F29">
-        <v>195.453</v>
+        <v>202.692</v>
       </c>
       <c r="G29">
         <v>5</v>
@@ -3653,45 +3653,45 @@
         <v>30.7</v>
       </c>
       <c r="M29">
-        <v>14.8153374</v>
+        <v>18.24228</v>
       </c>
       <c r="N29">
-        <v>15.8846626</v>
+        <v>12.45772</v>
       </c>
       <c r="O29">
-        <v>3.653472398</v>
+        <v>2.8652756</v>
       </c>
       <c r="P29">
-        <v>12.231190202</v>
+        <v>9.592444399999998</v>
       </c>
       <c r="Q29">
-        <v>22.031190202</v>
+        <v>19.3924444</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1052229835281561</v>
+        <v>0.105900556612776</v>
       </c>
       <c r="T29">
-        <v>0.9192546564071754</v>
+        <v>0.9297364965321818</v>
       </c>
       <c r="U29">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V29">
         <v>0.23</v>
       </c>
       <c r="W29">
-        <v>0.05836600000000001</v>
+        <v>0.0693</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.072176904995764</v>
+        <v>1.682903672128703</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09565240076119873</v>
+        <v>0.09578102354684348</v>
       </c>
       <c r="C30">
-        <v>467.7922649733562</v>
+        <v>458.8406862006665</v>
       </c>
       <c r="D30">
-        <v>665.4842649733562</v>
+        <v>663.7716862006665</v>
       </c>
       <c r="E30">
-        <v>158.092</v>
+        <v>165.331</v>
       </c>
       <c r="F30">
-        <v>202.692</v>
+        <v>209.931</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -3735,28 +3735,28 @@
         <v>30.7</v>
       </c>
       <c r="M30">
-        <v>18.24228</v>
+        <v>18.89379</v>
       </c>
       <c r="N30">
-        <v>12.45772</v>
+        <v>11.80621</v>
       </c>
       <c r="O30">
-        <v>2.8652756</v>
+        <v>2.7154283</v>
       </c>
       <c r="P30">
-        <v>9.592444399999998</v>
+        <v>9.090781700000001</v>
       </c>
       <c r="Q30">
-        <v>19.3924444</v>
+        <v>18.8907817</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.105900556612776</v>
+        <v>0.1065972162631598</v>
       </c>
       <c r="T30">
-        <v>0.9297364965321818</v>
+        <v>0.9405135997593008</v>
       </c>
       <c r="U30">
         <v>0.09</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.682903672128703</v>
+        <v>1.624872511020817</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09578102354684348</v>
+        <v>0.09590964633248825</v>
       </c>
       <c r="C31">
-        <v>458.8406862006665</v>
+        <v>449.8978992143293</v>
       </c>
       <c r="D31">
-        <v>663.7716862006665</v>
+        <v>662.0678992143293</v>
       </c>
       <c r="E31">
-        <v>165.331</v>
+        <v>172.57</v>
       </c>
       <c r="F31">
-        <v>209.931</v>
+        <v>217.17</v>
       </c>
       <c r="G31">
         <v>5</v>
@@ -3817,28 +3817,28 @@
         <v>30.7</v>
       </c>
       <c r="M31">
-        <v>18.89379</v>
+        <v>19.5453</v>
       </c>
       <c r="N31">
-        <v>11.80621</v>
+        <v>11.1547</v>
       </c>
       <c r="O31">
-        <v>2.7154283</v>
+        <v>2.565581</v>
       </c>
       <c r="P31">
-        <v>9.090781700000001</v>
+        <v>8.589119000000002</v>
       </c>
       <c r="Q31">
-        <v>18.8907817</v>
+        <v>18.389119</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1065972162631598</v>
+        <v>0.1073137804749832</v>
       </c>
       <c r="T31">
-        <v>0.9405135997593008</v>
+        <v>0.9515986202214806</v>
       </c>
       <c r="U31">
         <v>0.09</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.624872511020817</v>
+        <v>1.57071009398679</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09590964633248825</v>
+        <v>0.09603826911813301</v>
       </c>
       <c r="C32">
-        <v>449.8978992143293</v>
+        <v>440.9638364866967</v>
       </c>
       <c r="D32">
-        <v>662.0678992143293</v>
+        <v>660.3728364866967</v>
       </c>
       <c r="E32">
-        <v>172.57</v>
+        <v>179.809</v>
       </c>
       <c r="F32">
-        <v>217.17</v>
+        <v>224.409</v>
       </c>
       <c r="G32">
         <v>5</v>
@@ -3899,28 +3899,28 @@
         <v>30.7</v>
       </c>
       <c r="M32">
-        <v>19.5453</v>
+        <v>20.19681</v>
       </c>
       <c r="N32">
-        <v>11.1547</v>
+        <v>10.50319</v>
       </c>
       <c r="O32">
-        <v>2.565581</v>
+        <v>2.4157337</v>
       </c>
       <c r="P32">
-        <v>8.589119000000002</v>
+        <v>8.087456299999999</v>
       </c>
       <c r="Q32">
-        <v>18.389119</v>
+        <v>17.8874563</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1073137804749832</v>
+        <v>0.1080511146639609</v>
       </c>
       <c r="T32">
-        <v>0.9515986202214806</v>
+        <v>0.9630049456245929</v>
       </c>
       <c r="U32">
         <v>0.09</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.57071009398679</v>
+        <v>1.520042026438829</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09603826911813301</v>
+        <v>0.111543712999334</v>
       </c>
       <c r="C33">
-        <v>440.9638364866967</v>
+        <v>277.9780207125748</v>
       </c>
       <c r="D33">
-        <v>660.3728364866967</v>
+        <v>504.6260207125748</v>
       </c>
       <c r="E33">
-        <v>179.809</v>
+        <v>187.048</v>
       </c>
       <c r="F33">
-        <v>224.409</v>
+        <v>231.648</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -3981,45 +3981,45 @@
         <v>30.7</v>
       </c>
       <c r="M33">
-        <v>20.19681</v>
+        <v>34.0059264</v>
       </c>
       <c r="N33">
-        <v>10.50319</v>
+        <v>-3.305926400000001</v>
       </c>
       <c r="O33">
-        <v>2.4157337</v>
+        <v>-0.7603630720000002</v>
       </c>
       <c r="P33">
-        <v>8.087456299999999</v>
+        <v>-2.545563328000001</v>
       </c>
       <c r="Q33">
-        <v>17.8874563</v>
+        <v>7.254436672000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1080511146639609</v>
+        <v>0.1092967980632235</v>
       </c>
       <c r="T33">
-        <v>0.9630049456245929</v>
+        <v>0.9822752716363916</v>
       </c>
       <c r="U33">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.23</v>
+        <v>0.2076402776664246</v>
       </c>
       <c r="W33">
-        <v>0.0693</v>
+        <v>0.1163184072385689</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y33">
-        <v>1.520042026438829</v>
+        <v>0.9027838159409767</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.111543712999334</v>
+        <v>0.112553712999334</v>
       </c>
       <c r="C34">
-        <v>277.9780207125748</v>
+        <v>263.1039056302904</v>
       </c>
       <c r="D34">
-        <v>504.6260207125748</v>
+        <v>496.9909056302904</v>
       </c>
       <c r="E34">
-        <v>187.048</v>
+        <v>194.287</v>
       </c>
       <c r="F34">
-        <v>231.648</v>
+        <v>238.887</v>
       </c>
       <c r="G34">
         <v>5</v>
@@ -4063,37 +4063,37 @@
         <v>30.7</v>
       </c>
       <c r="M34">
-        <v>34.0059264</v>
+        <v>35.0686116</v>
       </c>
       <c r="N34">
-        <v>-3.305926400000001</v>
+        <v>-4.368611600000005</v>
       </c>
       <c r="O34">
-        <v>-0.7603630720000002</v>
+        <v>-1.004780668000001</v>
       </c>
       <c r="P34">
-        <v>-2.545563328000001</v>
+        <v>-3.363830932000003</v>
       </c>
       <c r="Q34">
-        <v>7.254436672000001</v>
+        <v>6.436169067999997</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1092967980632235</v>
+        <v>0.1102445114671523</v>
       </c>
       <c r="T34">
-        <v>0.9822752716363916</v>
+        <v>0.9969360965861885</v>
       </c>
       <c r="U34">
         <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.2076402776664246</v>
+        <v>0.2013481480401693</v>
       </c>
       <c r="W34">
-        <v>0.1163184072385689</v>
+        <v>0.1172420918677032</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.9027838159409767</v>
+        <v>0.8754267306094318</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.112553712999334</v>
+        <v>0.113563712999334</v>
       </c>
       <c r="C35">
-        <v>263.1039056302904</v>
+        <v>248.457389240338</v>
       </c>
       <c r="D35">
-        <v>496.9909056302904</v>
+        <v>489.583389240338</v>
       </c>
       <c r="E35">
-        <v>194.287</v>
+        <v>201.526</v>
       </c>
       <c r="F35">
-        <v>238.887</v>
+        <v>246.126</v>
       </c>
       <c r="G35">
         <v>5</v>
@@ -4145,37 +4145,37 @@
         <v>30.7</v>
       </c>
       <c r="M35">
-        <v>35.0686116</v>
+        <v>36.1312968</v>
       </c>
       <c r="N35">
-        <v>-4.368611600000005</v>
+        <v>-5.431296800000002</v>
       </c>
       <c r="O35">
-        <v>-1.004780668000001</v>
+        <v>-1.249198264000001</v>
       </c>
       <c r="P35">
-        <v>-3.363830932000003</v>
+        <v>-4.182098536000002</v>
       </c>
       <c r="Q35">
-        <v>6.436169067999997</v>
+        <v>5.617901463999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1102445114671523</v>
+        <v>0.1112209434590788</v>
       </c>
       <c r="T35">
-        <v>0.9969360965861885</v>
+        <v>1.012041188958706</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.2013481480401693</v>
+        <v>0.1954261436860467</v>
       </c>
       <c r="W35">
-        <v>0.1172420918677032</v>
+        <v>0.1181114421068884</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8754267306094318</v>
+        <v>0.8496788855915074</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.113563712999334</v>
+        <v>0.114573712999334</v>
       </c>
       <c r="C36">
-        <v>248.457389240338</v>
+        <v>234.02844410625</v>
       </c>
       <c r="D36">
-        <v>489.583389240338</v>
+        <v>482.39344410625</v>
       </c>
       <c r="E36">
-        <v>201.526</v>
+        <v>208.765</v>
       </c>
       <c r="F36">
-        <v>246.126</v>
+        <v>253.365</v>
       </c>
       <c r="G36">
         <v>5</v>
@@ -4227,37 +4227,37 @@
         <v>30.7</v>
       </c>
       <c r="M36">
-        <v>36.1312968</v>
+        <v>37.19398200000001</v>
       </c>
       <c r="N36">
-        <v>-5.431296800000002</v>
+        <v>-6.493982000000006</v>
       </c>
       <c r="O36">
-        <v>-1.249198264000001</v>
+        <v>-1.493615860000002</v>
       </c>
       <c r="P36">
-        <v>-4.182098536000002</v>
+        <v>-5.000366140000004</v>
       </c>
       <c r="Q36">
-        <v>5.617901463999999</v>
+        <v>4.799633859999997</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1112209434590788</v>
+        <v>0.1122274195122954</v>
       </c>
       <c r="T36">
-        <v>1.012041188958706</v>
+        <v>1.027611053404225</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.1954261436860467</v>
+        <v>0.1898425395807311</v>
       </c>
       <c r="W36">
-        <v>0.1181114421068884</v>
+        <v>0.1189311151895487</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8496788855915074</v>
+        <v>0.8254023460031785</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.114573712999334</v>
+        <v>0.1155837129993341</v>
       </c>
       <c r="C37">
-        <v>234.02844410625</v>
+        <v>219.8076233115901</v>
       </c>
       <c r="D37">
-        <v>482.39344410625</v>
+        <v>475.4116233115902</v>
       </c>
       <c r="E37">
-        <v>208.765</v>
+        <v>216.004</v>
       </c>
       <c r="F37">
-        <v>253.365</v>
+        <v>260.604</v>
       </c>
       <c r="G37">
         <v>5</v>
@@ -4309,37 +4309,37 @@
         <v>30.7</v>
       </c>
       <c r="M37">
-        <v>37.19398200000001</v>
+        <v>38.25666720000001</v>
       </c>
       <c r="N37">
-        <v>-6.493982000000006</v>
+        <v>-7.55666720000001</v>
       </c>
       <c r="O37">
-        <v>-1.493615860000002</v>
+        <v>-1.738033456000002</v>
       </c>
       <c r="P37">
-        <v>-5.000366140000004</v>
+        <v>-5.818633744000008</v>
       </c>
       <c r="Q37">
-        <v>4.799633859999997</v>
+        <v>3.981366255999992</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1122274195122954</v>
+        <v>0.113265347942175</v>
       </c>
       <c r="T37">
-        <v>1.027611053404225</v>
+        <v>1.043667476113666</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.1898425395807311</v>
+        <v>0.1845691357034885</v>
       </c>
       <c r="W37">
-        <v>0.1189311151895487</v>
+        <v>0.1197052508787279</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8254023460031785</v>
+        <v>0.8024745030586458</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1155837129993341</v>
+        <v>0.1374001550527617</v>
       </c>
       <c r="C38">
-        <v>219.80762331159</v>
+        <v>99.3396650687888</v>
       </c>
       <c r="D38">
-        <v>475.41162331159</v>
+        <v>362.1826650687888</v>
       </c>
       <c r="E38">
-        <v>216.004</v>
+        <v>223.243</v>
       </c>
       <c r="F38">
-        <v>260.604</v>
+        <v>267.843</v>
       </c>
       <c r="G38">
         <v>5</v>
@@ -4391,45 +4391,45 @@
         <v>30.7</v>
       </c>
       <c r="M38">
-        <v>38.2566672</v>
+        <v>53.7828744</v>
       </c>
       <c r="N38">
-        <v>-7.556667200000003</v>
+        <v>-23.0828744</v>
       </c>
       <c r="O38">
-        <v>-1.738033456000001</v>
+        <v>-5.309061111999999</v>
       </c>
       <c r="P38">
-        <v>-5.818633744000002</v>
+        <v>-17.773813288</v>
       </c>
       <c r="Q38">
-        <v>3.981366255999998</v>
+        <v>-7.973813287999999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.113265347942175</v>
+        <v>0.1156480392641582</v>
       </c>
       <c r="T38">
-        <v>1.043667476113666</v>
+        <v>1.080526953078101</v>
       </c>
       <c r="U38">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1845691357034886</v>
+        <v>0.1312871444446264</v>
       </c>
       <c r="W38">
-        <v>0.1197052508787279</v>
+        <v>0.174437541395519</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.8024745030586459</v>
+        <v>0.5708136714983757</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1374001550527617</v>
+        <v>0.1389501550527617</v>
       </c>
       <c r="C39">
-        <v>99.3396650687888</v>
+        <v>86.07401776435171</v>
       </c>
       <c r="D39">
-        <v>362.1826650687888</v>
+        <v>356.1560177643517</v>
       </c>
       <c r="E39">
-        <v>223.243</v>
+        <v>230.482</v>
       </c>
       <c r="F39">
-        <v>267.843</v>
+        <v>275.082</v>
       </c>
       <c r="G39">
         <v>5</v>
@@ -4473,37 +4473,37 @@
         <v>30.7</v>
       </c>
       <c r="M39">
-        <v>53.7828744</v>
+        <v>55.2364656</v>
       </c>
       <c r="N39">
-        <v>-23.0828744</v>
+        <v>-24.5364656</v>
       </c>
       <c r="O39">
-        <v>-5.309061111999999</v>
+        <v>-5.643387088000001</v>
       </c>
       <c r="P39">
-        <v>-17.773813288</v>
+        <v>-18.893078512</v>
       </c>
       <c r="Q39">
-        <v>-7.973813287999999</v>
+        <v>-9.093078512000002</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1156480392641582</v>
+        <v>0.1167746205426124</v>
       </c>
       <c r="T39">
-        <v>1.080526953078101</v>
+        <v>1.097954807160005</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1312871444446264</v>
+        <v>0.1278322195908204</v>
       </c>
       <c r="W39">
-        <v>0.174437541395519</v>
+        <v>0.1751312903061633</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5708136714983757</v>
+        <v>0.5557922590905237</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1389501550527617</v>
+        <v>0.1405001550527617</v>
       </c>
       <c r="C40">
-        <v>86.07401776435171</v>
+        <v>73.00565215003792</v>
       </c>
       <c r="D40">
-        <v>356.1560177643517</v>
+        <v>350.3266521500379</v>
       </c>
       <c r="E40">
-        <v>230.482</v>
+        <v>237.721</v>
       </c>
       <c r="F40">
-        <v>275.082</v>
+        <v>282.321</v>
       </c>
       <c r="G40">
         <v>5</v>
@@ -4555,37 +4555,37 @@
         <v>30.7</v>
       </c>
       <c r="M40">
-        <v>55.2364656</v>
+        <v>56.69005680000001</v>
       </c>
       <c r="N40">
-        <v>-24.5364656</v>
+        <v>-25.99005680000001</v>
       </c>
       <c r="O40">
-        <v>-5.643387088000001</v>
+        <v>-5.977713064000002</v>
       </c>
       <c r="P40">
-        <v>-18.893078512</v>
+        <v>-20.01234373600001</v>
       </c>
       <c r="Q40">
-        <v>-9.093078512000002</v>
+        <v>-10.212343736</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1167746205426124</v>
+        <v>0.1179381389121634</v>
       </c>
       <c r="T40">
-        <v>1.097954807160005</v>
+        <v>1.115954066293776</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1278322195908204</v>
+        <v>0.124554470370543</v>
       </c>
       <c r="W40">
-        <v>0.1751312903061633</v>
+        <v>0.175789462349595</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5557922590905237</v>
+        <v>0.5415411755241</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1405001550527617</v>
+        <v>0.1420501550527617</v>
       </c>
       <c r="C41">
-        <v>73.00565215003792</v>
+        <v>60.12503722967858</v>
       </c>
       <c r="D41">
-        <v>350.3266521500379</v>
+        <v>344.6850372296786</v>
       </c>
       <c r="E41">
-        <v>237.721</v>
+        <v>244.96</v>
       </c>
       <c r="F41">
-        <v>282.321</v>
+        <v>289.56</v>
       </c>
       <c r="G41">
         <v>5</v>
@@ -4637,37 +4637,37 @@
         <v>30.7</v>
       </c>
       <c r="M41">
-        <v>56.69005680000001</v>
+        <v>58.143648</v>
       </c>
       <c r="N41">
-        <v>-25.99005680000001</v>
+        <v>-27.443648</v>
       </c>
       <c r="O41">
-        <v>-5.977713064000002</v>
+        <v>-6.31203904</v>
       </c>
       <c r="P41">
-        <v>-20.01234373600001</v>
+        <v>-21.13160896</v>
       </c>
       <c r="Q41">
-        <v>-10.212343736</v>
+        <v>-11.33160896</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1179381389121634</v>
+        <v>0.1191404412273661</v>
       </c>
       <c r="T41">
-        <v>1.115954066293776</v>
+        <v>1.134553300732006</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.124554470370543</v>
+        <v>0.1214406086112794</v>
       </c>
       <c r="W41">
-        <v>0.175789462349595</v>
+        <v>0.1764147257908551</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5415411755241</v>
+        <v>0.5280026461359975</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1420501550527617</v>
+        <v>0.1436001550527617</v>
       </c>
       <c r="C42">
-        <v>60.12503722967858</v>
+        <v>47.42324622062785</v>
       </c>
       <c r="D42">
-        <v>344.6850372296786</v>
+        <v>339.2222462206279</v>
       </c>
       <c r="E42">
-        <v>244.96</v>
+        <v>252.199</v>
       </c>
       <c r="F42">
-        <v>289.56</v>
+        <v>296.799</v>
       </c>
       <c r="G42">
         <v>5</v>
@@ -4719,37 +4719,37 @@
         <v>30.7</v>
       </c>
       <c r="M42">
-        <v>58.143648</v>
+        <v>59.59723920000001</v>
       </c>
       <c r="N42">
-        <v>-27.443648</v>
+        <v>-28.89723920000001</v>
       </c>
       <c r="O42">
-        <v>-6.31203904</v>
+        <v>-6.646365016000003</v>
       </c>
       <c r="P42">
-        <v>-21.13160896</v>
+        <v>-22.25087418400001</v>
       </c>
       <c r="Q42">
-        <v>-11.33160896</v>
+        <v>-12.45087418400001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1191404412273661</v>
+        <v>0.1203834995532537</v>
       </c>
       <c r="T42">
-        <v>1.134553300732006</v>
+        <v>1.153783017693565</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1214406086112794</v>
+        <v>0.1184786425475897</v>
       </c>
       <c r="W42">
-        <v>0.1764147257908551</v>
+        <v>0.177009488576444</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5280026461359975</v>
+        <v>0.5151245328156072</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1436001550527617</v>
+        <v>0.1451501550527617</v>
       </c>
       <c r="C43">
-        <v>47.42324622062785</v>
+        <v>34.89190942092449</v>
       </c>
       <c r="D43">
-        <v>339.2222462206279</v>
+        <v>333.9299094209245</v>
       </c>
       <c r="E43">
-        <v>252.199</v>
+        <v>259.438</v>
       </c>
       <c r="F43">
-        <v>296.799</v>
+        <v>304.038</v>
       </c>
       <c r="G43">
         <v>5</v>
@@ -4801,37 +4801,37 @@
         <v>30.7</v>
       </c>
       <c r="M43">
-        <v>59.59723920000001</v>
+        <v>61.0508304</v>
       </c>
       <c r="N43">
-        <v>-28.89723920000001</v>
+        <v>-30.3508304</v>
       </c>
       <c r="O43">
-        <v>-6.646365016000003</v>
+        <v>-6.980690992000001</v>
       </c>
       <c r="P43">
-        <v>-22.25087418400001</v>
+        <v>-23.370139408</v>
       </c>
       <c r="Q43">
-        <v>-12.45087418400001</v>
+        <v>-13.570139408</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1203834995532537</v>
+        <v>0.1216694219593443</v>
       </c>
       <c r="T43">
-        <v>1.153783017693565</v>
+        <v>1.173675828343454</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1184786425475897</v>
+        <v>0.1156577224869328</v>
       </c>
       <c r="W43">
-        <v>0.177009488576444</v>
+        <v>0.1775759293246239</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5151245328156072</v>
+        <v>0.5028596629866643</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1451501550527617</v>
+        <v>0.1620836344036328</v>
       </c>
       <c r="C44">
-        <v>34.89190942092455</v>
+        <v>-20.97470060190795</v>
       </c>
       <c r="D44">
-        <v>333.9299094209245</v>
+        <v>285.302299398092</v>
       </c>
       <c r="E44">
-        <v>259.4379999999999</v>
+        <v>266.677</v>
       </c>
       <c r="F44">
-        <v>304.038</v>
+        <v>311.277</v>
       </c>
       <c r="G44">
         <v>5</v>
@@ -4883,45 +4883,45 @@
         <v>30.7</v>
       </c>
       <c r="M44">
-        <v>61.0508304</v>
+        <v>73.3991166</v>
       </c>
       <c r="N44">
-        <v>-30.3508304</v>
+        <v>-42.6991166</v>
       </c>
       <c r="O44">
-        <v>-6.980690992</v>
+        <v>-9.820796818</v>
       </c>
       <c r="P44">
-        <v>-23.370139408</v>
+        <v>-32.878319782</v>
       </c>
       <c r="Q44">
-        <v>-13.570139408</v>
+        <v>-23.078319782</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1216694219593443</v>
+        <v>0.1235855159426153</v>
       </c>
       <c r="T44">
-        <v>1.173675828343454</v>
+        <v>1.203317192873747</v>
       </c>
       <c r="U44">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.1156577224869328</v>
+        <v>0.09620006789019038</v>
       </c>
       <c r="W44">
-        <v>0.1775759293246239</v>
+        <v>0.2131160239914931</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y44">
-        <v>0.5028596629866644</v>
+        <v>0.4182611647399582</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1620836344036328</v>
+        <v>0.1639836344036328</v>
       </c>
       <c r="C45">
-        <v>-20.97470060190795</v>
+        <v>-32.80041323425968</v>
       </c>
       <c r="D45">
-        <v>285.302299398092</v>
+        <v>280.7155867657403</v>
       </c>
       <c r="E45">
-        <v>266.677</v>
+        <v>273.916</v>
       </c>
       <c r="F45">
-        <v>311.277</v>
+        <v>318.516</v>
       </c>
       <c r="G45">
         <v>5</v>
@@ -4965,37 +4965,37 @@
         <v>30.7</v>
       </c>
       <c r="M45">
-        <v>73.3991166</v>
+        <v>75.10607280000001</v>
       </c>
       <c r="N45">
-        <v>-42.6991166</v>
+        <v>-44.4060728</v>
       </c>
       <c r="O45">
-        <v>-9.820796818</v>
+        <v>-10.213396744</v>
       </c>
       <c r="P45">
-        <v>-32.878319782</v>
+        <v>-34.192676056</v>
       </c>
       <c r="Q45">
-        <v>-23.078319782</v>
+        <v>-24.392676056</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1235855159426153</v>
+        <v>0.1249745430130192</v>
       </c>
       <c r="T45">
-        <v>1.203317192873747</v>
+        <v>1.22480499988935</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.09620006789019038</v>
+        <v>0.09401370271086787</v>
       </c>
       <c r="W45">
-        <v>0.2131160239914931</v>
+        <v>0.2136315689007774</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4182611647399582</v>
+        <v>0.4087552291776864</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1639836344036328</v>
+        <v>0.1658836344036328</v>
       </c>
       <c r="C46">
-        <v>-32.80041323425968</v>
+        <v>-44.48098112570233</v>
       </c>
       <c r="D46">
-        <v>280.7155867657403</v>
+        <v>276.2740188742977</v>
       </c>
       <c r="E46">
-        <v>273.916</v>
+        <v>281.155</v>
       </c>
       <c r="F46">
-        <v>318.516</v>
+        <v>325.755</v>
       </c>
       <c r="G46">
         <v>5</v>
@@ -5047,37 +5047,37 @@
         <v>30.7</v>
       </c>
       <c r="M46">
-        <v>75.10607280000001</v>
+        <v>76.813029</v>
       </c>
       <c r="N46">
-        <v>-44.4060728</v>
+        <v>-46.113029</v>
       </c>
       <c r="O46">
-        <v>-10.213396744</v>
+        <v>-10.60599667</v>
       </c>
       <c r="P46">
-        <v>-34.192676056</v>
+        <v>-35.50703233</v>
       </c>
       <c r="Q46">
-        <v>-24.392676056</v>
+        <v>-25.70703233</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1249745430130192</v>
+        <v>0.1264140801587104</v>
       </c>
       <c r="T46">
-        <v>1.22480499988935</v>
+        <v>1.24707418170552</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.09401370271086787</v>
+        <v>0.09192450931729303</v>
       </c>
       <c r="W46">
-        <v>0.2136315689007774</v>
+        <v>0.2141242007029823</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4087552291776864</v>
+        <v>0.3996717796404046</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1658836344036328</v>
+        <v>0.1677836344036328</v>
       </c>
       <c r="C47">
-        <v>-44.48098112570233</v>
+        <v>-56.02318653868622</v>
       </c>
       <c r="D47">
-        <v>276.2740188742977</v>
+        <v>271.9708134613138</v>
       </c>
       <c r="E47">
-        <v>281.155</v>
+        <v>288.394</v>
       </c>
       <c r="F47">
-        <v>325.755</v>
+        <v>332.994</v>
       </c>
       <c r="G47">
         <v>5</v>
@@ -5129,37 +5129,37 @@
         <v>30.7</v>
       </c>
       <c r="M47">
-        <v>76.813029</v>
+        <v>78.51998520000001</v>
       </c>
       <c r="N47">
-        <v>-46.113029</v>
+        <v>-47.8199852</v>
       </c>
       <c r="O47">
-        <v>-10.60599667</v>
+        <v>-10.998596596</v>
       </c>
       <c r="P47">
-        <v>-35.50703233</v>
+        <v>-36.82138860400001</v>
       </c>
       <c r="Q47">
-        <v>-25.70703233</v>
+        <v>-27.02138860400001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1264140801587104</v>
+        <v>0.1279069334949828</v>
       </c>
       <c r="T47">
-        <v>1.24707418170552</v>
+        <v>1.2701681480334</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.09192450931729303</v>
+        <v>0.08992615041909101</v>
       </c>
       <c r="W47">
-        <v>0.2141242007029823</v>
+        <v>0.2145954137311784</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3996717796404046</v>
+        <v>0.3909832626917</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1677836344036328</v>
+        <v>0.1696836344036328</v>
       </c>
       <c r="C48">
-        <v>-56.02318653868622</v>
+        <v>-67.4333956581479</v>
       </c>
       <c r="D48">
-        <v>271.9708134613138</v>
+        <v>267.7996043418521</v>
       </c>
       <c r="E48">
-        <v>288.394</v>
+        <v>295.633</v>
       </c>
       <c r="F48">
-        <v>332.994</v>
+        <v>340.233</v>
       </c>
       <c r="G48">
         <v>5</v>
@@ -5211,37 +5211,37 @@
         <v>30.7</v>
       </c>
       <c r="M48">
-        <v>78.51998520000001</v>
+        <v>80.2269414</v>
       </c>
       <c r="N48">
-        <v>-47.8199852</v>
+        <v>-49.5269414</v>
       </c>
       <c r="O48">
-        <v>-10.998596596</v>
+        <v>-11.391196522</v>
       </c>
       <c r="P48">
-        <v>-36.82138860400001</v>
+        <v>-38.135744878</v>
       </c>
       <c r="Q48">
-        <v>-27.02138860400001</v>
+        <v>-28.335744878</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1279069334949828</v>
+        <v>0.1294561209194165</v>
       </c>
       <c r="T48">
-        <v>1.2701681480334</v>
+        <v>1.294133584788747</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.08992615041909101</v>
+        <v>0.08801282806974865</v>
       </c>
       <c r="W48">
-        <v>0.2145954137311784</v>
+        <v>0.2150465751411533</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3909832626917</v>
+        <v>0.3826644698684725</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1696836344036328</v>
+        <v>0.1715836344036328</v>
       </c>
       <c r="C49">
-        <v>-67.4333956581479</v>
+        <v>-78.71759001639606</v>
       </c>
       <c r="D49">
-        <v>267.7996043418521</v>
+        <v>263.754409983604</v>
       </c>
       <c r="E49">
-        <v>295.633</v>
+        <v>302.872</v>
       </c>
       <c r="F49">
-        <v>340.233</v>
+        <v>347.472</v>
       </c>
       <c r="G49">
         <v>5</v>
@@ -5293,37 +5293,37 @@
         <v>30.7</v>
       </c>
       <c r="M49">
-        <v>80.2269414</v>
+        <v>81.93389760000001</v>
       </c>
       <c r="N49">
-        <v>-49.5269414</v>
+        <v>-51.23389760000001</v>
       </c>
       <c r="O49">
-        <v>-11.391196522</v>
+        <v>-11.783796448</v>
       </c>
       <c r="P49">
-        <v>-38.135744878</v>
+        <v>-39.450101152</v>
       </c>
       <c r="Q49">
-        <v>-28.335744878</v>
+        <v>-29.650101152</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1294561209194165</v>
+        <v>0.1310648924755591</v>
       </c>
       <c r="T49">
-        <v>1.294133584788747</v>
+        <v>1.319020769111608</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.08801282806974865</v>
+        <v>0.08617922748496222</v>
       </c>
       <c r="W49">
-        <v>0.2150465751411533</v>
+        <v>0.2154789381590459</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3826644698684725</v>
+        <v>0.3746922934128792</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1715836344036328</v>
+        <v>0.1734836344036328</v>
       </c>
       <c r="C50">
-        <v>-78.717590016396</v>
+        <v>-89.88139511228371</v>
       </c>
       <c r="D50">
-        <v>263.754409983604</v>
+        <v>259.8296048877162</v>
       </c>
       <c r="E50">
-        <v>302.872</v>
+        <v>310.1109999999999</v>
       </c>
       <c r="F50">
-        <v>347.472</v>
+        <v>354.711</v>
       </c>
       <c r="G50">
         <v>5</v>
@@ -5375,37 +5375,37 @@
         <v>30.7</v>
       </c>
       <c r="M50">
-        <v>81.93389759999999</v>
+        <v>83.64085379999999</v>
       </c>
       <c r="N50">
-        <v>-51.23389759999999</v>
+        <v>-52.94085379999999</v>
       </c>
       <c r="O50">
-        <v>-11.783796448</v>
+        <v>-12.176396374</v>
       </c>
       <c r="P50">
-        <v>-39.45010115199999</v>
+        <v>-40.76445742599999</v>
       </c>
       <c r="Q50">
-        <v>-29.65010115199999</v>
+        <v>-30.96445742599998</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1310648924755591</v>
+        <v>0.1327367531123348</v>
       </c>
       <c r="T50">
-        <v>1.319020769111608</v>
+        <v>1.344883921447129</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.08617922748496223</v>
+        <v>0.08442046774037117</v>
       </c>
       <c r="W50">
-        <v>0.2154789381590459</v>
+        <v>0.2158936537068205</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3746922934128792</v>
+        <v>0.3670455119146573</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1734836344036328</v>
+        <v>0.1753836344036328</v>
       </c>
       <c r="C51">
-        <v>-89.88139511228371</v>
+        <v>-100.9301065126365</v>
       </c>
       <c r="D51">
-        <v>259.8296048877162</v>
+        <v>256.0198934873634</v>
       </c>
       <c r="E51">
-        <v>310.1109999999999</v>
+        <v>317.35</v>
       </c>
       <c r="F51">
-        <v>354.711</v>
+        <v>361.95</v>
       </c>
       <c r="G51">
         <v>5</v>
@@ -5457,37 +5457,37 @@
         <v>30.7</v>
       </c>
       <c r="M51">
-        <v>83.64085379999999</v>
+        <v>85.34781</v>
       </c>
       <c r="N51">
-        <v>-52.94085379999999</v>
+        <v>-54.64780999999999</v>
       </c>
       <c r="O51">
-        <v>-12.176396374</v>
+        <v>-12.5689963</v>
       </c>
       <c r="P51">
-        <v>-40.76445742599999</v>
+        <v>-42.0788137</v>
       </c>
       <c r="Q51">
-        <v>-30.96445742599998</v>
+        <v>-32.2788137</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1327367531123348</v>
+        <v>0.1344754881745815</v>
       </c>
       <c r="T51">
-        <v>1.344883921447129</v>
+        <v>1.371781599876072</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.08442046774037117</v>
+        <v>0.08273205838556373</v>
       </c>
       <c r="W51">
-        <v>0.2158936537068205</v>
+        <v>0.2162917806326841</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3670455119146573</v>
+        <v>0.3597046016763641</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1753836344036328</v>
+        <v>0.1772836344036328</v>
       </c>
       <c r="C52">
-        <v>-100.9301065126365</v>
+        <v>-111.8687136906121</v>
       </c>
       <c r="D52">
-        <v>256.0198934873634</v>
+        <v>252.3202863093879</v>
       </c>
       <c r="E52">
-        <v>317.35</v>
+        <v>324.589</v>
       </c>
       <c r="F52">
-        <v>361.95</v>
+        <v>369.189</v>
       </c>
       <c r="G52">
         <v>5</v>
@@ -5539,37 +5539,37 @@
         <v>30.7</v>
       </c>
       <c r="M52">
-        <v>85.34781</v>
+        <v>87.0547662</v>
       </c>
       <c r="N52">
-        <v>-54.64780999999999</v>
+        <v>-56.3547662</v>
       </c>
       <c r="O52">
-        <v>-12.5689963</v>
+        <v>-12.961596226</v>
       </c>
       <c r="P52">
-        <v>-42.0788137</v>
+        <v>-43.393169974</v>
       </c>
       <c r="Q52">
-        <v>-32.2788137</v>
+        <v>-33.59316997400001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1344754881745815</v>
+        <v>0.1362851920148791</v>
       </c>
       <c r="T52">
-        <v>1.371781599876072</v>
+        <v>1.399777142730686</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.08273205838556373</v>
+        <v>0.08110986116231739</v>
       </c>
       <c r="W52">
-        <v>0.2162917806326841</v>
+        <v>0.2166742947379256</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3597046016763641</v>
+        <v>0.3526515702709452</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1772836344036328</v>
+        <v>0.1791836344036328</v>
       </c>
       <c r="C53">
-        <v>-111.8687136906121</v>
+        <v>-122.7019218266499</v>
       </c>
       <c r="D53">
-        <v>252.3202863093879</v>
+        <v>248.7260781733501</v>
       </c>
       <c r="E53">
-        <v>324.589</v>
+        <v>331.828</v>
       </c>
       <c r="F53">
-        <v>369.189</v>
+        <v>376.428</v>
       </c>
       <c r="G53">
         <v>5</v>
@@ -5621,37 +5621,37 @@
         <v>30.7</v>
       </c>
       <c r="M53">
-        <v>87.0547662</v>
+        <v>88.7617224</v>
       </c>
       <c r="N53">
-        <v>-56.3547662</v>
+        <v>-58.06172239999999</v>
       </c>
       <c r="O53">
-        <v>-12.961596226</v>
+        <v>-13.354196152</v>
       </c>
       <c r="P53">
-        <v>-43.393169974</v>
+        <v>-44.70752624799999</v>
       </c>
       <c r="Q53">
-        <v>-33.59316997400001</v>
+        <v>-34.907526248</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1362851920148791</v>
+        <v>0.1381703001818557</v>
       </c>
       <c r="T53">
-        <v>1.399777142730686</v>
+        <v>1.428939166537575</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.08110986116231739</v>
+        <v>0.07955005613996513</v>
       </c>
       <c r="W53">
-        <v>0.2166742947379256</v>
+        <v>0.2170420967621962</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3526515702709452</v>
+        <v>0.3458698093041962</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1791836344036328</v>
+        <v>0.1810836344036328</v>
       </c>
       <c r="C54">
-        <v>-122.7019218266499</v>
+        <v>-133.4341717723114</v>
       </c>
       <c r="D54">
-        <v>248.7260781733501</v>
+        <v>245.2328282276886</v>
       </c>
       <c r="E54">
-        <v>331.828</v>
+        <v>339.067</v>
       </c>
       <c r="F54">
-        <v>376.428</v>
+        <v>383.667</v>
       </c>
       <c r="G54">
         <v>5</v>
@@ -5703,37 +5703,37 @@
         <v>30.7</v>
       </c>
       <c r="M54">
-        <v>88.7617224</v>
+        <v>90.4686786</v>
       </c>
       <c r="N54">
-        <v>-58.06172239999999</v>
+        <v>-59.7686786</v>
       </c>
       <c r="O54">
-        <v>-13.354196152</v>
+        <v>-13.746796078</v>
       </c>
       <c r="P54">
-        <v>-44.70752624799999</v>
+        <v>-46.021882522</v>
       </c>
       <c r="Q54">
-        <v>-34.907526248</v>
+        <v>-36.221882522</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1381703001818557</v>
+        <v>0.1401356257176399</v>
       </c>
       <c r="T54">
-        <v>1.428939166537575</v>
+        <v>1.459342127527736</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.07955005613996513</v>
+        <v>0.07804911168449408</v>
       </c>
       <c r="W54">
-        <v>0.2170420967621962</v>
+        <v>0.2173960194647963</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3458698093041962</v>
+        <v>0.3393439638456265</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1810836344036328</v>
+        <v>0.1829836344036328</v>
       </c>
       <c r="C55">
-        <v>-133.4341717723114</v>
+        <v>-144.0696583551181</v>
       </c>
       <c r="D55">
-        <v>245.2328282276886</v>
+        <v>241.8363416448819</v>
       </c>
       <c r="E55">
-        <v>339.067</v>
+        <v>346.306</v>
       </c>
       <c r="F55">
-        <v>383.667</v>
+        <v>390.906</v>
       </c>
       <c r="G55">
         <v>5</v>
@@ -5785,37 +5785,37 @@
         <v>30.7</v>
       </c>
       <c r="M55">
-        <v>90.4686786</v>
+        <v>92.17563480000001</v>
       </c>
       <c r="N55">
-        <v>-59.7686786</v>
+        <v>-61.47563480000001</v>
       </c>
       <c r="O55">
-        <v>-13.746796078</v>
+        <v>-14.139396004</v>
       </c>
       <c r="P55">
-        <v>-46.021882522</v>
+        <v>-47.336238796</v>
       </c>
       <c r="Q55">
-        <v>-36.221882522</v>
+        <v>-37.53623879600001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1401356257176399</v>
+        <v>0.1421864001897625</v>
       </c>
       <c r="T55">
-        <v>1.459342127527736</v>
+        <v>1.491066956387035</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.07804911168449408</v>
+        <v>0.07660375776441086</v>
       </c>
       <c r="W55">
-        <v>0.2173960194647963</v>
+        <v>0.2177368339191519</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3393439638456265</v>
+        <v>0.3330598163670038</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1829836344036328</v>
+        <v>0.1848836344036328</v>
       </c>
       <c r="C56">
-        <v>-144.0696583551181</v>
+        <v>-154.6123471830344</v>
       </c>
       <c r="D56">
-        <v>241.8363416448819</v>
+        <v>238.5326528169656</v>
       </c>
       <c r="E56">
-        <v>346.306</v>
+        <v>353.545</v>
       </c>
       <c r="F56">
-        <v>390.906</v>
+        <v>398.145</v>
       </c>
       <c r="G56">
         <v>5</v>
@@ -5867,37 +5867,37 @@
         <v>30.7</v>
       </c>
       <c r="M56">
-        <v>92.17563480000001</v>
+        <v>93.88259100000002</v>
       </c>
       <c r="N56">
-        <v>-61.47563480000001</v>
+        <v>-63.18259100000002</v>
       </c>
       <c r="O56">
-        <v>-14.139396004</v>
+        <v>-14.53199593</v>
       </c>
       <c r="P56">
-        <v>-47.336238796</v>
+        <v>-48.65059507000001</v>
       </c>
       <c r="Q56">
-        <v>-37.53623879600001</v>
+        <v>-38.85059507000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1421864001897625</v>
+        <v>0.1443283201939794</v>
       </c>
       <c r="T56">
-        <v>1.491066956387035</v>
+        <v>1.52420177764008</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.07660375776441086</v>
+        <v>0.07521096216869429</v>
       </c>
       <c r="W56">
-        <v>0.2177368339191519</v>
+        <v>0.2180652551206219</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3330598163670038</v>
+        <v>0.3270041833421491</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1848836344036328</v>
+        <v>0.1867836344036328</v>
       </c>
       <c r="C57">
-        <v>-154.6123471830344</v>
+        <v>-165.0659900901303</v>
       </c>
       <c r="D57">
-        <v>238.5326528169656</v>
+        <v>235.3180099098697</v>
       </c>
       <c r="E57">
-        <v>353.545</v>
+        <v>360.784</v>
       </c>
       <c r="F57">
-        <v>398.145</v>
+        <v>405.384</v>
       </c>
       <c r="G57">
         <v>5</v>
@@ -5949,37 +5949,37 @@
         <v>30.7</v>
       </c>
       <c r="M57">
-        <v>93.88259100000002</v>
+        <v>95.58954720000001</v>
       </c>
       <c r="N57">
-        <v>-63.18259100000002</v>
+        <v>-64.88954720000001</v>
       </c>
       <c r="O57">
-        <v>-14.53199593</v>
+        <v>-14.924595856</v>
       </c>
       <c r="P57">
-        <v>-48.65059507000001</v>
+        <v>-49.96495134400001</v>
       </c>
       <c r="Q57">
-        <v>-38.85059507000001</v>
+        <v>-40.164951344</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1443283201939794</v>
+        <v>0.146567600198388</v>
       </c>
       <c r="T57">
-        <v>1.52420177764008</v>
+        <v>1.5588427271319</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.07521096216869429</v>
+        <v>0.07386790927282476</v>
       </c>
       <c r="W57">
-        <v>0.2180652551206219</v>
+        <v>0.2183819469934679</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3270041833421491</v>
+        <v>0.321164822925325</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1867836344036328</v>
+        <v>0.1886836344036328</v>
       </c>
       <c r="C58">
-        <v>-165.0659900901303</v>
+        <v>-175.43413934991</v>
       </c>
       <c r="D58">
-        <v>235.3180099098697</v>
+        <v>232.1888606500901</v>
       </c>
       <c r="E58">
-        <v>360.784</v>
+        <v>368.023</v>
       </c>
       <c r="F58">
-        <v>405.384</v>
+        <v>412.623</v>
       </c>
       <c r="G58">
         <v>5</v>
@@ -6031,37 +6031,37 @@
         <v>30.7</v>
       </c>
       <c r="M58">
-        <v>95.58954720000001</v>
+        <v>97.29650340000002</v>
       </c>
       <c r="N58">
-        <v>-64.88954720000001</v>
+        <v>-66.59650340000002</v>
       </c>
       <c r="O58">
-        <v>-14.924595856</v>
+        <v>-15.317195782</v>
       </c>
       <c r="P58">
-        <v>-49.96495134400001</v>
+        <v>-51.27930761800001</v>
       </c>
       <c r="Q58">
-        <v>-40.164951344</v>
+        <v>-41.47930761800001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.146567600198388</v>
+        <v>0.1489110327611413</v>
       </c>
       <c r="T58">
-        <v>1.5588427271319</v>
+        <v>1.595094883576828</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.07386790927282476</v>
+        <v>0.07257198103996816</v>
       </c>
       <c r="W58">
-        <v>0.2183819469934679</v>
+        <v>0.2186875268707755</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.321164822925325</v>
+        <v>0.3155303523476877</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1886836344036328</v>
+        <v>0.1905836344036328</v>
       </c>
       <c r="C59">
-        <v>-175.43413934991</v>
+        <v>-185.7201607695083</v>
       </c>
       <c r="D59">
-        <v>232.1888606500901</v>
+        <v>229.1418392304918</v>
       </c>
       <c r="E59">
-        <v>368.023</v>
+        <v>375.262</v>
       </c>
       <c r="F59">
-        <v>412.623</v>
+        <v>419.862</v>
       </c>
       <c r="G59">
         <v>5</v>
@@ -6113,37 +6113,37 @@
         <v>30.7</v>
       </c>
       <c r="M59">
-        <v>97.29650340000002</v>
+        <v>99.00345960000001</v>
       </c>
       <c r="N59">
-        <v>-66.59650340000002</v>
+        <v>-68.30345960000001</v>
       </c>
       <c r="O59">
-        <v>-15.317195782</v>
+        <v>-15.709795708</v>
       </c>
       <c r="P59">
-        <v>-51.27930761800001</v>
+        <v>-52.59366389200001</v>
       </c>
       <c r="Q59">
-        <v>-41.47930761800001</v>
+        <v>-42.79366389200001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1489110327611413</v>
+        <v>0.1513660573506922</v>
       </c>
       <c r="T59">
-        <v>1.595094883576828</v>
+        <v>1.6330733331858</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.07257198103996816</v>
+        <v>0.07132073998755492</v>
       </c>
       <c r="W59">
-        <v>0.2186875268707755</v>
+        <v>0.2189825695109346</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3155303523476877</v>
+        <v>0.3100901738589346</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1905836344036328</v>
+        <v>0.1924836344036328</v>
       </c>
       <c r="C60">
-        <v>-185.7201607695083</v>
+        <v>-195.9272457662292</v>
       </c>
       <c r="D60">
-        <v>229.1418392304917</v>
+        <v>226.1737542337707</v>
       </c>
       <c r="E60">
-        <v>375.2619999999999</v>
+        <v>382.5009999999999</v>
       </c>
       <c r="F60">
-        <v>419.862</v>
+        <v>427.1009999999999</v>
       </c>
       <c r="G60">
         <v>5</v>
@@ -6195,37 +6195,37 @@
         <v>30.7</v>
       </c>
       <c r="M60">
-        <v>99.0034596</v>
+        <v>100.7104158</v>
       </c>
       <c r="N60">
-        <v>-68.3034596</v>
+        <v>-70.01041579999999</v>
       </c>
       <c r="O60">
-        <v>-15.709795708</v>
+        <v>-16.102395634</v>
       </c>
       <c r="P60">
-        <v>-52.593663892</v>
+        <v>-53.90802016599999</v>
       </c>
       <c r="Q60">
-        <v>-42.793663892</v>
+        <v>-44.10802016599999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1513660573506922</v>
+        <v>0.1539408392372945</v>
       </c>
       <c r="T60">
-        <v>1.6330733331858</v>
+        <v>1.67290439009277</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.07132073998755493</v>
+        <v>0.07011191388607096</v>
       </c>
       <c r="W60">
-        <v>0.2189825695109346</v>
+        <v>0.2192676107056645</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3100901738589346</v>
+        <v>0.3048344082003086</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1924836344036328</v>
+        <v>0.1943836344036328</v>
       </c>
       <c r="C61">
-        <v>-195.9272457662292</v>
+        <v>-206.058422517518</v>
       </c>
       <c r="D61">
-        <v>226.1737542337707</v>
+        <v>223.281577482482</v>
       </c>
       <c r="E61">
-        <v>382.5009999999999</v>
+        <v>389.74</v>
       </c>
       <c r="F61">
-        <v>427.1009999999999</v>
+        <v>434.34</v>
       </c>
       <c r="G61">
         <v>5</v>
@@ -6277,37 +6277,37 @@
         <v>30.7</v>
       </c>
       <c r="M61">
-        <v>100.7104158</v>
+        <v>102.417372</v>
       </c>
       <c r="N61">
-        <v>-70.01041579999999</v>
+        <v>-71.717372</v>
       </c>
       <c r="O61">
-        <v>-16.102395634</v>
+        <v>-16.49499556</v>
       </c>
       <c r="P61">
-        <v>-53.90802016599999</v>
+        <v>-55.22237644</v>
       </c>
       <c r="Q61">
-        <v>-44.10802016599999</v>
+        <v>-45.42237643999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1539408392372945</v>
+        <v>0.1566443602182268</v>
       </c>
       <c r="T61">
-        <v>1.67290439009277</v>
+        <v>1.71472699984509</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.07011191388607096</v>
+        <v>0.06894338198796977</v>
       </c>
       <c r="W61">
-        <v>0.2192676107056645</v>
+        <v>0.2195431505272367</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3048344082003086</v>
+        <v>0.2997538347303034</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1943836344036328</v>
+        <v>0.1962836344036328</v>
       </c>
       <c r="C62">
-        <v>-206.058422517518</v>
+        <v>-216.1165662662582</v>
       </c>
       <c r="D62">
-        <v>223.281577482482</v>
+        <v>220.4624337337418</v>
       </c>
       <c r="E62">
-        <v>389.74</v>
+        <v>396.9789999999999</v>
       </c>
       <c r="F62">
-        <v>434.34</v>
+        <v>441.579</v>
       </c>
       <c r="G62">
         <v>5</v>
@@ -6359,37 +6359,37 @@
         <v>30.7</v>
       </c>
       <c r="M62">
-        <v>102.417372</v>
+        <v>104.1243282</v>
       </c>
       <c r="N62">
-        <v>-71.717372</v>
+        <v>-73.42432819999999</v>
       </c>
       <c r="O62">
-        <v>-16.49499556</v>
+        <v>-16.887595486</v>
       </c>
       <c r="P62">
-        <v>-55.22237644</v>
+        <v>-56.536732714</v>
       </c>
       <c r="Q62">
-        <v>-45.42237643999999</v>
+        <v>-46.736732714</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1566443602182268</v>
+        <v>0.1594865233007455</v>
       </c>
       <c r="T62">
-        <v>1.71472699984509</v>
+        <v>1.758694358815477</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.06894338198796977</v>
+        <v>0.06781316261111781</v>
       </c>
       <c r="W62">
-        <v>0.2195431505272367</v>
+        <v>0.2198096562562984</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2997538347303034</v>
+        <v>0.2948398374396427</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1962836344036328</v>
+        <v>0.1981836344036328</v>
       </c>
       <c r="C63">
-        <v>-216.1165662662582</v>
+        <v>-226.1044088551191</v>
       </c>
       <c r="D63">
-        <v>220.4624337337418</v>
+        <v>217.7135911448809</v>
       </c>
       <c r="E63">
-        <v>396.9789999999999</v>
+        <v>404.218</v>
       </c>
       <c r="F63">
-        <v>441.579</v>
+        <v>448.818</v>
       </c>
       <c r="G63">
         <v>5</v>
@@ -6441,37 +6441,37 @@
         <v>30.7</v>
       </c>
       <c r="M63">
-        <v>104.1243282</v>
+        <v>105.8312844</v>
       </c>
       <c r="N63">
-        <v>-73.42432819999999</v>
+        <v>-75.1312844</v>
       </c>
       <c r="O63">
-        <v>-16.887595486</v>
+        <v>-17.280195412</v>
       </c>
       <c r="P63">
-        <v>-56.536732714</v>
+        <v>-57.851088988</v>
       </c>
       <c r="Q63">
-        <v>-46.736732714</v>
+        <v>-48.051088988</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1594865233007455</v>
+        <v>0.162478273913923</v>
       </c>
       <c r="T63">
-        <v>1.758694358815477</v>
+        <v>1.804975789310621</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.06781316261111781</v>
+        <v>0.06671940192384172</v>
       </c>
       <c r="W63">
-        <v>0.2198096562562984</v>
+        <v>0.2200675650263581</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2948398374396427</v>
+        <v>0.2900843561906162</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1981836344036328</v>
+        <v>0.2000836344036328</v>
       </c>
       <c r="C64">
-        <v>-226.1044088551191</v>
+        <v>-236.0245475564092</v>
       </c>
       <c r="D64">
-        <v>217.7135911448809</v>
+        <v>215.0324524435908</v>
       </c>
       <c r="E64">
-        <v>404.218</v>
+        <v>411.457</v>
       </c>
       <c r="F64">
-        <v>448.818</v>
+        <v>456.057</v>
       </c>
       <c r="G64">
         <v>5</v>
@@ -6523,37 +6523,37 @@
         <v>30.7</v>
       </c>
       <c r="M64">
-        <v>105.8312844</v>
+        <v>107.5382406</v>
       </c>
       <c r="N64">
-        <v>-75.1312844</v>
+        <v>-76.83824060000001</v>
       </c>
       <c r="O64">
-        <v>-17.280195412</v>
+        <v>-17.672795338</v>
       </c>
       <c r="P64">
-        <v>-57.851088988</v>
+        <v>-59.16544526200001</v>
       </c>
       <c r="Q64">
-        <v>-48.051088988</v>
+        <v>-49.36544526200001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.162478273913923</v>
+        <v>0.1656317407764615</v>
       </c>
       <c r="T64">
-        <v>1.804975789310621</v>
+        <v>1.853758918751448</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.06671940192384172</v>
+        <v>0.06566036379806646</v>
       </c>
       <c r="W64">
-        <v>0.2200675650263581</v>
+        <v>0.2203172862164159</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2900843561906162</v>
+        <v>0.2854798426002889</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2000836344036328</v>
+        <v>0.2019836344036328</v>
       </c>
       <c r="C65">
-        <v>-236.0245475564092</v>
+        <v>-245.8794532574314</v>
       </c>
       <c r="D65">
-        <v>215.0324524435908</v>
+        <v>212.4165467425686</v>
       </c>
       <c r="E65">
-        <v>411.457</v>
+        <v>418.696</v>
       </c>
       <c r="F65">
-        <v>456.057</v>
+        <v>463.296</v>
       </c>
       <c r="G65">
         <v>5</v>
@@ -6605,37 +6605,37 @@
         <v>30.7</v>
       </c>
       <c r="M65">
-        <v>107.5382406</v>
+        <v>109.2451968</v>
       </c>
       <c r="N65">
-        <v>-76.83824060000001</v>
+        <v>-78.5451968</v>
       </c>
       <c r="O65">
-        <v>-17.672795338</v>
+        <v>-18.065395264</v>
       </c>
       <c r="P65">
-        <v>-59.16544526200001</v>
+        <v>-60.479801536</v>
       </c>
       <c r="Q65">
-        <v>-49.36544526200001</v>
+        <v>-50.679801536</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1656317407764615</v>
+        <v>0.1689604002424742</v>
       </c>
       <c r="T65">
-        <v>1.853758918751448</v>
+        <v>1.9052522220501</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06566036379806646</v>
+        <v>0.06463442061372167</v>
       </c>
       <c r="W65">
-        <v>0.2203172862164159</v>
+        <v>0.2205592036192844</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2854798426002889</v>
+        <v>0.2810192200596594</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2019836344036328</v>
+        <v>0.2038836344036328</v>
       </c>
       <c r="C66">
-        <v>-245.8794532574314</v>
+        <v>-255.6714780555607</v>
       </c>
       <c r="D66">
-        <v>212.4165467425686</v>
+        <v>209.8635219444393</v>
       </c>
       <c r="E66">
-        <v>418.696</v>
+        <v>425.935</v>
       </c>
       <c r="F66">
-        <v>463.296</v>
+        <v>470.535</v>
       </c>
       <c r="G66">
         <v>5</v>
@@ -6687,37 +6687,37 @@
         <v>30.7</v>
       </c>
       <c r="M66">
-        <v>109.2451968</v>
+        <v>110.952153</v>
       </c>
       <c r="N66">
-        <v>-78.5451968</v>
+        <v>-80.25215300000001</v>
       </c>
       <c r="O66">
-        <v>-18.065395264</v>
+        <v>-18.45799519</v>
       </c>
       <c r="P66">
-        <v>-60.479801536</v>
+        <v>-61.79415781</v>
       </c>
       <c r="Q66">
-        <v>-50.679801536</v>
+        <v>-51.99415781</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1689604002424742</v>
+        <v>0.1724792688208307</v>
       </c>
       <c r="T66">
-        <v>1.9052522220501</v>
+        <v>1.95968799982296</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.06463442061372167</v>
+        <v>0.06364004491197209</v>
       </c>
       <c r="W66">
-        <v>0.2205592036192844</v>
+        <v>0.220793677409757</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2810192200596594</v>
+        <v>0.276695847443357</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2038836344036328</v>
+        <v>0.2057836344036328</v>
       </c>
       <c r="C67">
-        <v>-255.6714780555607</v>
+        <v>-265.402862312118</v>
       </c>
       <c r="D67">
-        <v>209.8635219444393</v>
+        <v>207.371137687882</v>
       </c>
       <c r="E67">
-        <v>425.935</v>
+        <v>433.174</v>
       </c>
       <c r="F67">
-        <v>470.535</v>
+        <v>477.774</v>
       </c>
       <c r="G67">
         <v>5</v>
@@ -6769,37 +6769,37 @@
         <v>30.7</v>
       </c>
       <c r="M67">
-        <v>110.952153</v>
+        <v>112.6591092</v>
       </c>
       <c r="N67">
-        <v>-80.25215300000001</v>
+        <v>-81.9591092</v>
       </c>
       <c r="O67">
-        <v>-18.45799519</v>
+        <v>-18.850595116</v>
       </c>
       <c r="P67">
-        <v>-61.79415781</v>
+        <v>-63.108514084</v>
       </c>
       <c r="Q67">
-        <v>-51.99415781</v>
+        <v>-53.308514084</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1724792688208307</v>
+        <v>0.1762051296685022</v>
       </c>
       <c r="T67">
-        <v>1.95968799982296</v>
+        <v>2.017325882170694</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.06364004491197209</v>
+        <v>0.06267580180724525</v>
       </c>
       <c r="W67">
-        <v>0.220793677409757</v>
+        <v>0.2210210459338516</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.276695847443357</v>
+        <v>0.2725034861184576</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2057836344036328</v>
+        <v>0.2076836344036328</v>
       </c>
       <c r="C68">
-        <v>-265.402862312118</v>
+        <v>-275.0757412095029</v>
       </c>
       <c r="D68">
-        <v>207.371137687882</v>
+        <v>204.9372587904971</v>
       </c>
       <c r="E68">
-        <v>433.174</v>
+        <v>440.413</v>
       </c>
       <c r="F68">
-        <v>477.774</v>
+        <v>485.013</v>
       </c>
       <c r="G68">
         <v>5</v>
@@ -6851,37 +6851,37 @@
         <v>30.7</v>
       </c>
       <c r="M68">
-        <v>112.6591092</v>
+        <v>114.3660654</v>
       </c>
       <c r="N68">
-        <v>-81.9591092</v>
+        <v>-83.66606540000001</v>
       </c>
       <c r="O68">
-        <v>-18.850595116</v>
+        <v>-19.243195042</v>
       </c>
       <c r="P68">
-        <v>-63.108514084</v>
+        <v>-64.42287035800001</v>
       </c>
       <c r="Q68">
-        <v>-53.308514084</v>
+        <v>-54.62287035800001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1762051296685022</v>
+        <v>0.1801568002645174</v>
       </c>
       <c r="T68">
-        <v>2.017325882170694</v>
+        <v>2.0784569695092</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.06267580180724525</v>
+        <v>0.0617403420787789</v>
       </c>
       <c r="W68">
-        <v>0.2210210459338516</v>
+        <v>0.221241627337824</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2725034861184576</v>
+        <v>0.2684362699077344</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2076836344036328</v>
+        <v>0.2095836344036328</v>
       </c>
       <c r="C69">
-        <v>-275.0757412095029</v>
+        <v>-284.6921508519239</v>
       </c>
       <c r="D69">
-        <v>204.9372587904971</v>
+        <v>202.5598491480761</v>
       </c>
       <c r="E69">
-        <v>440.413</v>
+        <v>447.652</v>
       </c>
       <c r="F69">
-        <v>485.013</v>
+        <v>492.252</v>
       </c>
       <c r="G69">
         <v>5</v>
@@ -6933,37 +6933,37 @@
         <v>30.7</v>
       </c>
       <c r="M69">
-        <v>114.3660654</v>
+        <v>116.0730216</v>
       </c>
       <c r="N69">
-        <v>-83.66606540000001</v>
+        <v>-85.3730216</v>
       </c>
       <c r="O69">
-        <v>-19.243195042</v>
+        <v>-19.635794968</v>
       </c>
       <c r="P69">
-        <v>-64.42287035800001</v>
+        <v>-65.737226632</v>
       </c>
       <c r="Q69">
-        <v>-54.62287035800001</v>
+        <v>-55.93722663200001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1801568002645174</v>
+        <v>0.1843554502727836</v>
       </c>
       <c r="T69">
-        <v>2.0784569695092</v>
+        <v>2.143408749806363</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0617403420787789</v>
+        <v>0.06083239587173803</v>
       </c>
       <c r="W69">
-        <v>0.221241627337824</v>
+        <v>0.2214557210534442</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2684362699077344</v>
+        <v>0.2644886777032088</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2095836344036328</v>
+        <v>0.2114836344036328</v>
       </c>
       <c r="C70">
-        <v>-284.6921508519239</v>
+        <v>-294.2540339463625</v>
       </c>
       <c r="D70">
-        <v>202.5598491480761</v>
+        <v>200.2369660536376</v>
       </c>
       <c r="E70">
-        <v>447.652</v>
+        <v>454.891</v>
       </c>
       <c r="F70">
-        <v>492.252</v>
+        <v>499.491</v>
       </c>
       <c r="G70">
         <v>5</v>
@@ -7015,37 +7015,37 @@
         <v>30.7</v>
       </c>
       <c r="M70">
-        <v>116.0730216</v>
+        <v>117.7799778</v>
       </c>
       <c r="N70">
-        <v>-85.3730216</v>
+        <v>-87.07997780000001</v>
       </c>
       <c r="O70">
-        <v>-19.635794968</v>
+        <v>-20.028394894</v>
       </c>
       <c r="P70">
-        <v>-65.737226632</v>
+        <v>-67.05158290600001</v>
       </c>
       <c r="Q70">
-        <v>-55.93722663200001</v>
+        <v>-57.25158290600001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1843554502727836</v>
+        <v>0.1888249809267444</v>
       </c>
       <c r="T70">
-        <v>2.143408749806363</v>
+        <v>2.212550967542052</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.06083239587173803</v>
+        <v>0.05995076694606067</v>
       </c>
       <c r="W70">
-        <v>0.2214557210534442</v>
+        <v>0.2216636091541189</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2644886777032088</v>
+        <v>0.2606555084611334</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2114836344036328</v>
+        <v>0.2133836344036328</v>
       </c>
       <c r="C71">
-        <v>-294.2540339463625</v>
+        <v>-303.763245097086</v>
       </c>
       <c r="D71">
-        <v>200.2369660536376</v>
+        <v>197.966754902914</v>
       </c>
       <c r="E71">
-        <v>454.891</v>
+        <v>462.13</v>
       </c>
       <c r="F71">
-        <v>499.491</v>
+        <v>506.73</v>
       </c>
       <c r="G71">
         <v>5</v>
@@ -7097,37 +7097,37 @@
         <v>30.7</v>
       </c>
       <c r="M71">
-        <v>117.7799778</v>
+        <v>119.486934</v>
       </c>
       <c r="N71">
-        <v>-87.07997780000001</v>
+        <v>-88.786934</v>
       </c>
       <c r="O71">
-        <v>-20.028394894</v>
+        <v>-20.42099482</v>
       </c>
       <c r="P71">
-        <v>-67.05158290600001</v>
+        <v>-68.36593918</v>
       </c>
       <c r="Q71">
-        <v>-57.25158290600001</v>
+        <v>-58.56593918</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1888249809267444</v>
+        <v>0.1935924802909691</v>
       </c>
       <c r="T71">
-        <v>2.212550967542052</v>
+        <v>2.28630266646012</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05995076694606067</v>
+        <v>0.0590943274182598</v>
       </c>
       <c r="W71">
-        <v>0.2216636091541189</v>
+        <v>0.2218655575947743</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2606555084611334</v>
+        <v>0.25693185834026</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2133836344036328</v>
+        <v>0.2152836344036328</v>
       </c>
       <c r="C72">
-        <v>-303.763245097086</v>
+        <v>-313.2215557440347</v>
       </c>
       <c r="D72">
-        <v>197.966754902914</v>
+        <v>195.7474442559653</v>
       </c>
       <c r="E72">
-        <v>462.13</v>
+        <v>469.369</v>
       </c>
       <c r="F72">
-        <v>506.73</v>
+        <v>513.9690000000001</v>
       </c>
       <c r="G72">
         <v>5</v>
@@ -7179,37 +7179,37 @@
         <v>30.7</v>
       </c>
       <c r="M72">
-        <v>119.486934</v>
+        <v>121.1938902</v>
       </c>
       <c r="N72">
-        <v>-88.786934</v>
+        <v>-90.49389020000001</v>
       </c>
       <c r="O72">
-        <v>-20.42099482</v>
+        <v>-20.813594746</v>
       </c>
       <c r="P72">
-        <v>-68.36593918</v>
+        <v>-69.680295454</v>
       </c>
       <c r="Q72">
-        <v>-58.56593918</v>
+        <v>-59.88029545400001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1935924802909691</v>
+        <v>0.1986887727147957</v>
       </c>
       <c r="T72">
-        <v>2.28630266646012</v>
+        <v>2.365140689441504</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.0590943274182598</v>
+        <v>0.05826201294758009</v>
       </c>
       <c r="W72">
-        <v>0.2218655575947743</v>
+        <v>0.2220618173469606</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.25693185834026</v>
+        <v>0.2533130997720874</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2152836344036328</v>
+        <v>0.2171836344036328</v>
       </c>
       <c r="C73">
-        <v>-313.2215557440346</v>
+        <v>-322.6306587727195</v>
       </c>
       <c r="D73">
-        <v>195.7474442559653</v>
+        <v>193.5773412272805</v>
       </c>
       <c r="E73">
-        <v>469.3689999999999</v>
+        <v>476.6079999999999</v>
       </c>
       <c r="F73">
-        <v>513.9689999999999</v>
+        <v>521.208</v>
       </c>
       <c r="G73">
         <v>5</v>
@@ -7261,37 +7261,37 @@
         <v>30.7</v>
       </c>
       <c r="M73">
-        <v>121.1938902</v>
+        <v>122.9008464</v>
       </c>
       <c r="N73">
-        <v>-90.49389019999998</v>
+        <v>-92.20084639999999</v>
       </c>
       <c r="O73">
-        <v>-20.813594746</v>
+        <v>-21.206194672</v>
       </c>
       <c r="P73">
-        <v>-69.68029545399999</v>
+        <v>-70.99465172799999</v>
       </c>
       <c r="Q73">
-        <v>-59.88029545399999</v>
+        <v>-61.194651728</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1986887727147956</v>
+        <v>0.2041490860260383</v>
       </c>
       <c r="T73">
-        <v>2.365140689441503</v>
+        <v>2.4496099997787</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.0582620129475801</v>
+        <v>0.05745281832330815</v>
       </c>
       <c r="W73">
-        <v>0.2220618173469606</v>
+        <v>0.2222526254393639</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2533130997720874</v>
+        <v>0.2497948622752528</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2171836344036328</v>
+        <v>0.2190836344036328</v>
       </c>
       <c r="C74">
-        <v>-322.6306587727195</v>
+        <v>-331.9921728208443</v>
       </c>
       <c r="D74">
-        <v>193.5773412272805</v>
+        <v>191.4548271791557</v>
       </c>
       <c r="E74">
-        <v>476.6079999999999</v>
+        <v>483.847</v>
       </c>
       <c r="F74">
-        <v>521.208</v>
+        <v>528.447</v>
       </c>
       <c r="G74">
         <v>5</v>
@@ -7343,37 +7343,37 @@
         <v>30.7</v>
       </c>
       <c r="M74">
-        <v>122.9008464</v>
+        <v>124.6078026</v>
       </c>
       <c r="N74">
-        <v>-92.20084639999999</v>
+        <v>-93.9078026</v>
       </c>
       <c r="O74">
-        <v>-21.206194672</v>
+        <v>-21.598794598</v>
       </c>
       <c r="P74">
-        <v>-70.99465172799999</v>
+        <v>-72.309008002</v>
       </c>
       <c r="Q74">
-        <v>-61.194651728</v>
+        <v>-62.509008002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2041490860260383</v>
+        <v>0.2100138669899657</v>
       </c>
       <c r="T74">
-        <v>2.4496099997787</v>
+        <v>2.540336296066799</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05745281832330815</v>
+        <v>0.05666579341476968</v>
       </c>
       <c r="W74">
-        <v>0.2222526254393639</v>
+        <v>0.2224382059127973</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2497948622752528</v>
+        <v>0.2463730148468247</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2190836344036328</v>
+        <v>0.2209836344036328</v>
       </c>
       <c r="C75">
-        <v>-331.9921728208443</v>
+        <v>-341.3076463046758</v>
       </c>
       <c r="D75">
-        <v>191.4548271791557</v>
+        <v>189.3783536953241</v>
       </c>
       <c r="E75">
-        <v>483.847</v>
+        <v>491.0859999999999</v>
       </c>
       <c r="F75">
-        <v>528.447</v>
+        <v>535.6859999999999</v>
       </c>
       <c r="G75">
         <v>5</v>
@@ -7425,37 +7425,37 @@
         <v>30.7</v>
       </c>
       <c r="M75">
-        <v>124.6078026</v>
+        <v>126.3147588</v>
       </c>
       <c r="N75">
-        <v>-93.9078026</v>
+        <v>-95.61475879999999</v>
       </c>
       <c r="O75">
-        <v>-21.598794598</v>
+        <v>-21.991394524</v>
       </c>
       <c r="P75">
-        <v>-72.309008002</v>
+        <v>-73.62336427599999</v>
       </c>
       <c r="Q75">
-        <v>-62.509008002</v>
+        <v>-63.82336427599999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2100138669899657</v>
+        <v>0.2163297849511182</v>
       </c>
       <c r="T75">
-        <v>2.540336296066799</v>
+        <v>2.638041538223215</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05666579341476968</v>
+        <v>0.05590003944970522</v>
       </c>
       <c r="W75">
-        <v>0.2224382059127973</v>
+        <v>0.2226187706977595</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2463730148468247</v>
+        <v>0.2430436497813271</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2209836344036328</v>
+        <v>0.2228836344036328</v>
       </c>
       <c r="C76">
-        <v>-341.3076463046758</v>
+        <v>-350.5785611862112</v>
       </c>
       <c r="D76">
-        <v>189.3783536953241</v>
+        <v>187.3464388137887</v>
       </c>
       <c r="E76">
-        <v>491.0859999999999</v>
+        <v>498.3249999999999</v>
       </c>
       <c r="F76">
-        <v>535.6859999999999</v>
+        <v>542.925</v>
       </c>
       <c r="G76">
         <v>5</v>
@@ -7507,37 +7507,37 @@
         <v>30.7</v>
       </c>
       <c r="M76">
-        <v>126.3147588</v>
+        <v>128.021715</v>
       </c>
       <c r="N76">
-        <v>-95.61475879999999</v>
+        <v>-97.321715</v>
       </c>
       <c r="O76">
-        <v>-21.991394524</v>
+        <v>-22.38399445</v>
       </c>
       <c r="P76">
-        <v>-73.62336427599999</v>
+        <v>-74.93772054999999</v>
       </c>
       <c r="Q76">
-        <v>-63.82336427599999</v>
+        <v>-65.13772055</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2163297849511182</v>
+        <v>0.2231509763491629</v>
       </c>
       <c r="T76">
-        <v>2.638041538223215</v>
+        <v>2.743563199752144</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05590003944970522</v>
+        <v>0.05515470559037582</v>
       </c>
       <c r="W76">
-        <v>0.2226187706977595</v>
+        <v>0.2227945204217894</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2430436497813271</v>
+        <v>0.2398030677842428</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2228836344036328</v>
+        <v>0.2247836344036328</v>
       </c>
       <c r="C77">
-        <v>-350.5785611862112</v>
+        <v>-359.8063365004027</v>
       </c>
       <c r="D77">
-        <v>187.3464388137887</v>
+        <v>185.3576634995973</v>
       </c>
       <c r="E77">
-        <v>498.3249999999999</v>
+        <v>505.564</v>
       </c>
       <c r="F77">
-        <v>542.925</v>
+        <v>550.164</v>
       </c>
       <c r="G77">
         <v>5</v>
@@ -7589,37 +7589,37 @@
         <v>30.7</v>
       </c>
       <c r="M77">
-        <v>128.021715</v>
+        <v>129.7286712</v>
       </c>
       <c r="N77">
-        <v>-97.321715</v>
+        <v>-99.02867120000001</v>
       </c>
       <c r="O77">
-        <v>-22.38399445</v>
+        <v>-22.776594376</v>
       </c>
       <c r="P77">
-        <v>-74.93772054999999</v>
+        <v>-76.252076824</v>
       </c>
       <c r="Q77">
-        <v>-65.13772055</v>
+        <v>-66.452076824</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2231509763491629</v>
+        <v>0.2305406003637114</v>
       </c>
       <c r="T77">
-        <v>2.743563199752144</v>
+        <v>2.85787833307515</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05515470559037582</v>
+        <v>0.05442898577997614</v>
       </c>
       <c r="W77">
-        <v>0.2227945204217894</v>
+        <v>0.2229656451530816</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2398030677842428</v>
+        <v>0.2366477642607658</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2247836344036328</v>
+        <v>0.2266836344036328</v>
       </c>
       <c r="C78">
-        <v>-359.8063365004027</v>
+        <v>-368.9923316600829</v>
       </c>
       <c r="D78">
-        <v>185.3576634995973</v>
+        <v>183.4106683399171</v>
       </c>
       <c r="E78">
-        <v>505.564</v>
+        <v>512.803</v>
       </c>
       <c r="F78">
-        <v>550.164</v>
+        <v>557.403</v>
       </c>
       <c r="G78">
         <v>5</v>
@@ -7671,37 +7671,37 @@
         <v>30.7</v>
       </c>
       <c r="M78">
-        <v>129.7286712</v>
+        <v>131.4356274</v>
       </c>
       <c r="N78">
-        <v>-99.02867120000001</v>
+        <v>-100.7356274</v>
       </c>
       <c r="O78">
-        <v>-22.776594376</v>
+        <v>-23.169194302</v>
       </c>
       <c r="P78">
-        <v>-76.252076824</v>
+        <v>-77.566433098</v>
       </c>
       <c r="Q78">
-        <v>-66.452076824</v>
+        <v>-67.76643309800001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2305406003637114</v>
+        <v>0.238572800379525</v>
       </c>
       <c r="T78">
-        <v>2.85787833307515</v>
+        <v>2.98213391277407</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05442898577997614</v>
+        <v>0.05372211583478164</v>
       </c>
       <c r="W78">
-        <v>0.2229656451530816</v>
+        <v>0.2231323250861585</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2366477642607658</v>
+        <v>0.2335744166729636</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2266836344036328</v>
+        <v>0.2285836344036328</v>
       </c>
       <c r="C79">
-        <v>-368.9923316600829</v>
+        <v>-378.1378495547666</v>
       </c>
       <c r="D79">
-        <v>183.4106683399171</v>
+        <v>181.5041504452334</v>
       </c>
       <c r="E79">
-        <v>512.803</v>
+        <v>520.042</v>
       </c>
       <c r="F79">
-        <v>557.403</v>
+        <v>564.6420000000001</v>
       </c>
       <c r="G79">
         <v>5</v>
@@ -7753,37 +7753,37 @@
         <v>30.7</v>
       </c>
       <c r="M79">
-        <v>131.4356274</v>
+        <v>133.1425836</v>
       </c>
       <c r="N79">
-        <v>-100.7356274</v>
+        <v>-102.4425836</v>
       </c>
       <c r="O79">
-        <v>-23.169194302</v>
+        <v>-23.56179422800001</v>
       </c>
       <c r="P79">
-        <v>-77.566433098</v>
+        <v>-78.88078937200001</v>
       </c>
       <c r="Q79">
-        <v>-67.76643309800001</v>
+        <v>-69.08078937200001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.238572800379525</v>
+        <v>0.2473352003967761</v>
       </c>
       <c r="T79">
-        <v>2.98213391277407</v>
+        <v>3.1176854542638</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05372211583478164</v>
+        <v>0.05303337075997674</v>
       </c>
       <c r="W79">
-        <v>0.2231323250861585</v>
+        <v>0.2232947311747975</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2335744166729636</v>
+        <v>0.2305798728694641</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2285836344036328</v>
+        <v>0.2304836344036328</v>
       </c>
       <c r="C80">
-        <v>-378.1378495547666</v>
+        <v>-387.244139458171</v>
       </c>
       <c r="D80">
-        <v>181.5041504452334</v>
+        <v>179.636860541829</v>
       </c>
       <c r="E80">
-        <v>520.042</v>
+        <v>527.2809999999999</v>
       </c>
       <c r="F80">
-        <v>564.6420000000001</v>
+        <v>571.881</v>
       </c>
       <c r="G80">
         <v>5</v>
@@ -7835,37 +7835,37 @@
         <v>30.7</v>
       </c>
       <c r="M80">
-        <v>133.1425836</v>
+        <v>134.8495398</v>
       </c>
       <c r="N80">
-        <v>-102.4425836</v>
+        <v>-104.1495398</v>
       </c>
       <c r="O80">
-        <v>-23.56179422800001</v>
+        <v>-23.954394154</v>
       </c>
       <c r="P80">
-        <v>-78.88078937200001</v>
+        <v>-80.195145646</v>
       </c>
       <c r="Q80">
-        <v>-69.08078937200001</v>
+        <v>-70.395145646</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2473352003967761</v>
+        <v>0.2569321147013844</v>
       </c>
       <c r="T80">
-        <v>3.1176854542638</v>
+        <v>3.2661466663716</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05303337075997674</v>
+        <v>0.05236206226934414</v>
       </c>
       <c r="W80">
-        <v>0.2232947311747975</v>
+        <v>0.2234530257168887</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2305798728694641</v>
+        <v>0.2276611403014962</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2304836344036328</v>
+        <v>0.2323836344036328</v>
       </c>
       <c r="C81">
-        <v>-387.244139458171</v>
+        <v>-396.3123997580917</v>
       </c>
       <c r="D81">
-        <v>179.636860541829</v>
+        <v>177.8076002419083</v>
       </c>
       <c r="E81">
-        <v>527.2809999999999</v>
+        <v>534.52</v>
       </c>
       <c r="F81">
-        <v>571.881</v>
+        <v>579.12</v>
       </c>
       <c r="G81">
         <v>5</v>
@@ -7917,37 +7917,37 @@
         <v>30.7</v>
       </c>
       <c r="M81">
-        <v>134.8495398</v>
+        <v>136.556496</v>
       </c>
       <c r="N81">
-        <v>-104.1495398</v>
+        <v>-105.856496</v>
       </c>
       <c r="O81">
-        <v>-23.954394154</v>
+        <v>-24.34699408</v>
       </c>
       <c r="P81">
-        <v>-80.195145646</v>
+        <v>-81.50950192000001</v>
       </c>
       <c r="Q81">
-        <v>-70.395145646</v>
+        <v>-71.70950192000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2569321147013844</v>
+        <v>0.2674887204364537</v>
       </c>
       <c r="T81">
-        <v>3.2661466663716</v>
+        <v>3.42945399969018</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05236206226934414</v>
+        <v>0.05170753649097733</v>
       </c>
       <c r="W81">
-        <v>0.2234530257168887</v>
+        <v>0.2236073628954275</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2276611403014962</v>
+        <v>0.2248153760477275</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2323836344036328</v>
+        <v>0.2342836344036328</v>
       </c>
       <c r="C82">
-        <v>-396.3123997580917</v>
+        <v>-405.3437805211672</v>
       </c>
       <c r="D82">
-        <v>177.8076002419083</v>
+        <v>176.0152194788328</v>
       </c>
       <c r="E82">
-        <v>534.52</v>
+        <v>541.759</v>
       </c>
       <c r="F82">
-        <v>579.12</v>
+        <v>586.359</v>
       </c>
       <c r="G82">
         <v>5</v>
@@ -7999,37 +7999,37 @@
         <v>30.7</v>
       </c>
       <c r="M82">
-        <v>136.556496</v>
+        <v>138.2634522</v>
       </c>
       <c r="N82">
-        <v>-105.856496</v>
+        <v>-107.5634522</v>
       </c>
       <c r="O82">
-        <v>-24.34699408</v>
+        <v>-24.739594006</v>
       </c>
       <c r="P82">
-        <v>-81.50950192000001</v>
+        <v>-82.82385819400001</v>
       </c>
       <c r="Q82">
-        <v>-71.70950192000001</v>
+        <v>-73.02385819400001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2674887204364537</v>
+        <v>0.279156547827846</v>
       </c>
       <c r="T82">
-        <v>3.42945399969018</v>
+        <v>3.609951578621243</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05170753649097733</v>
+        <v>0.05106917184294057</v>
       </c>
       <c r="W82">
-        <v>0.2236073628954275</v>
+        <v>0.2237578892794346</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2248153760477275</v>
+        <v>0.2220398775780025</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2342836344036328</v>
+        <v>0.2361836344036328</v>
       </c>
       <c r="C83">
-        <v>-405.3437805211672</v>
+        <v>-414.3393859040688</v>
       </c>
       <c r="D83">
-        <v>176.0152194788328</v>
+        <v>174.2586140959313</v>
       </c>
       <c r="E83">
-        <v>541.759</v>
+        <v>548.998</v>
       </c>
       <c r="F83">
-        <v>586.359</v>
+        <v>593.5980000000001</v>
       </c>
       <c r="G83">
         <v>5</v>
@@ -8081,37 +8081,37 @@
         <v>30.7</v>
       </c>
       <c r="M83">
-        <v>138.2634522</v>
+        <v>139.9704084</v>
       </c>
       <c r="N83">
-        <v>-107.5634522</v>
+        <v>-109.2704084</v>
       </c>
       <c r="O83">
-        <v>-24.739594006</v>
+        <v>-25.13219393200001</v>
       </c>
       <c r="P83">
-        <v>-82.82385819400001</v>
+        <v>-84.13821446800002</v>
       </c>
       <c r="Q83">
-        <v>-73.02385819400001</v>
+        <v>-74.33821446800002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.279156547827846</v>
+        <v>0.2921208004849486</v>
       </c>
       <c r="T83">
-        <v>3.609951578621243</v>
+        <v>3.810504444100201</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05106917184294057</v>
+        <v>0.05044637706436812</v>
       </c>
       <c r="W83">
-        <v>0.2237578892794346</v>
+        <v>0.223904744288222</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2220398775780025</v>
+        <v>0.2193320741929049</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2361836344036328</v>
+        <v>0.2380836344036328</v>
       </c>
       <c r="C84">
-        <v>-414.3393859040688</v>
+        <v>-423.3002764217363</v>
       </c>
       <c r="D84">
-        <v>174.2586140959313</v>
+        <v>172.5367235782637</v>
       </c>
       <c r="E84">
-        <v>548.998</v>
+        <v>556.237</v>
       </c>
       <c r="F84">
-        <v>593.5980000000001</v>
+        <v>600.837</v>
       </c>
       <c r="G84">
         <v>5</v>
@@ -8163,37 +8163,37 @@
         <v>30.7</v>
       </c>
       <c r="M84">
-        <v>139.9704084</v>
+        <v>141.6773646</v>
       </c>
       <c r="N84">
-        <v>-109.2704084</v>
+        <v>-110.9773646</v>
       </c>
       <c r="O84">
-        <v>-25.13219393200001</v>
+        <v>-25.524793858</v>
       </c>
       <c r="P84">
-        <v>-84.13821446800002</v>
+        <v>-85.45257074200001</v>
       </c>
       <c r="Q84">
-        <v>-74.33821446800002</v>
+        <v>-75.65257074200001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2921208004849486</v>
+        <v>0.3066102593370044</v>
       </c>
       <c r="T84">
-        <v>3.810504444100201</v>
+        <v>4.03465176434139</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05044637706436812</v>
+        <v>0.04983858938889382</v>
       </c>
       <c r="W84">
-        <v>0.223904744288222</v>
+        <v>0.2240480606220988</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2193320741929049</v>
+        <v>0.2166895190821471</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2380836344036328</v>
+        <v>0.2399836344036328</v>
       </c>
       <c r="C85">
-        <v>-423.3002764217363</v>
+        <v>-432.2274710824527</v>
       </c>
       <c r="D85">
-        <v>172.5367235782637</v>
+        <v>170.8485289175474</v>
       </c>
       <c r="E85">
-        <v>556.237</v>
+        <v>563.476</v>
       </c>
       <c r="F85">
-        <v>600.837</v>
+        <v>608.076</v>
       </c>
       <c r="G85">
         <v>5</v>
@@ -8245,37 +8245,37 @@
         <v>30.7</v>
       </c>
       <c r="M85">
-        <v>141.6773646</v>
+        <v>143.3843208</v>
       </c>
       <c r="N85">
-        <v>-110.9773646</v>
+        <v>-112.6843208</v>
       </c>
       <c r="O85">
-        <v>-25.524793858</v>
+        <v>-25.917393784</v>
       </c>
       <c r="P85">
-        <v>-85.45257074200001</v>
+        <v>-86.76692701600001</v>
       </c>
       <c r="Q85">
-        <v>-75.65257074200001</v>
+        <v>-76.96692701600001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3066102593370044</v>
+        <v>0.3229109005455673</v>
       </c>
       <c r="T85">
-        <v>4.03465176434139</v>
+        <v>4.286817499612727</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04983858938889382</v>
+        <v>0.04924527284854983</v>
       </c>
       <c r="W85">
-        <v>0.2240480606220988</v>
+        <v>0.2241879646623119</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2166895190821471</v>
+        <v>0.2141098819502167</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2399836344036328</v>
+        <v>0.2418836344036328</v>
       </c>
       <c r="C86">
-        <v>-432.2274710824524</v>
+        <v>-441.1219493987874</v>
       </c>
       <c r="D86">
-        <v>170.8485289175475</v>
+        <v>169.1930506012126</v>
       </c>
       <c r="E86">
-        <v>563.4759999999999</v>
+        <v>570.7149999999999</v>
       </c>
       <c r="F86">
-        <v>608.0759999999999</v>
+        <v>615.3149999999999</v>
       </c>
       <c r="G86">
         <v>5</v>
@@ -8327,37 +8327,37 @@
         <v>30.7</v>
       </c>
       <c r="M86">
-        <v>143.3843208</v>
+        <v>145.091277</v>
       </c>
       <c r="N86">
-        <v>-112.6843208</v>
+        <v>-114.391277</v>
       </c>
       <c r="O86">
-        <v>-25.917393784</v>
+        <v>-26.30999371</v>
       </c>
       <c r="P86">
-        <v>-86.76692701599998</v>
+        <v>-88.08128328999999</v>
       </c>
       <c r="Q86">
-        <v>-76.96692701599999</v>
+        <v>-78.28128328999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.322910900545567</v>
+        <v>0.3413849605819382</v>
       </c>
       <c r="T86">
-        <v>4.286817499612724</v>
+        <v>4.572605332920239</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04924527284854985</v>
+        <v>0.04866591669739043</v>
       </c>
       <c r="W86">
-        <v>0.2241879646623119</v>
+        <v>0.2243245768427554</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2141098819502167</v>
+        <v>0.2115909421625671</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2418836344036328</v>
+        <v>0.2437836344036328</v>
       </c>
       <c r="C87">
-        <v>-441.1219493987874</v>
+        <v>-449.9846532827504</v>
       </c>
       <c r="D87">
-        <v>169.1930506012126</v>
+        <v>167.5693467172495</v>
       </c>
       <c r="E87">
-        <v>570.7149999999999</v>
+        <v>577.954</v>
       </c>
       <c r="F87">
-        <v>615.3149999999999</v>
+        <v>622.554</v>
       </c>
       <c r="G87">
         <v>5</v>
@@ -8409,37 +8409,37 @@
         <v>30.7</v>
       </c>
       <c r="M87">
-        <v>145.091277</v>
+        <v>146.7982332</v>
       </c>
       <c r="N87">
-        <v>-114.391277</v>
+        <v>-116.0982332</v>
       </c>
       <c r="O87">
-        <v>-26.30999371</v>
+        <v>-26.702593636</v>
       </c>
       <c r="P87">
-        <v>-88.08128328999999</v>
+        <v>-89.39563956399999</v>
       </c>
       <c r="Q87">
-        <v>-78.28128328999999</v>
+        <v>-79.595639564</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3413849605819382</v>
+        <v>0.3624981720520766</v>
       </c>
       <c r="T87">
-        <v>4.572605332920239</v>
+        <v>4.899219999557399</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04866591669739043</v>
+        <v>0.04810003394509519</v>
       </c>
       <c r="W87">
-        <v>0.2243245768427554</v>
+        <v>0.2244580119957466</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2115909421625671</v>
+        <v>0.2091305823699792</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2437836344036328</v>
+        <v>0.2456836344036328</v>
       </c>
       <c r="C88">
-        <v>-449.9846532827504</v>
+        <v>-458.8164888328579</v>
       </c>
       <c r="D88">
-        <v>167.5693467172495</v>
+        <v>165.9765111671421</v>
       </c>
       <c r="E88">
-        <v>577.954</v>
+        <v>585.193</v>
       </c>
       <c r="F88">
-        <v>622.554</v>
+        <v>629.793</v>
       </c>
       <c r="G88">
         <v>5</v>
@@ -8491,37 +8491,37 @@
         <v>30.7</v>
       </c>
       <c r="M88">
-        <v>146.7982332</v>
+        <v>148.5051894</v>
       </c>
       <c r="N88">
-        <v>-116.0982332</v>
+        <v>-117.8051894</v>
       </c>
       <c r="O88">
-        <v>-26.702593636</v>
+        <v>-27.095193562</v>
       </c>
       <c r="P88">
-        <v>-89.39563956399999</v>
+        <v>-90.709995838</v>
       </c>
       <c r="Q88">
-        <v>-79.595639564</v>
+        <v>-80.909995838</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3624981720520766</v>
+        <v>0.3868595699022364</v>
       </c>
       <c r="T88">
-        <v>4.899219999557399</v>
+        <v>5.276083076446429</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04810003394509519</v>
+        <v>0.04754715999170329</v>
       </c>
       <c r="W88">
-        <v>0.2244580119957466</v>
+        <v>0.2245883796739564</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2091305823699792</v>
+        <v>0.206726782572623</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2456836344036328</v>
+        <v>0.2475836344036328</v>
       </c>
       <c r="C89">
-        <v>-458.8164888328579</v>
+        <v>-467.6183280202359</v>
       </c>
       <c r="D89">
-        <v>165.9765111671421</v>
+        <v>164.4136719797641</v>
       </c>
       <c r="E89">
-        <v>585.193</v>
+        <v>592.432</v>
       </c>
       <c r="F89">
-        <v>629.793</v>
+        <v>637.032</v>
       </c>
       <c r="G89">
         <v>5</v>
@@ -8573,37 +8573,37 @@
         <v>30.7</v>
       </c>
       <c r="M89">
-        <v>148.5051894</v>
+        <v>150.2121456</v>
       </c>
       <c r="N89">
-        <v>-117.8051894</v>
+        <v>-119.5121456</v>
       </c>
       <c r="O89">
-        <v>-27.095193562</v>
+        <v>-27.487793488</v>
       </c>
       <c r="P89">
-        <v>-90.709995838</v>
+        <v>-92.024352112</v>
       </c>
       <c r="Q89">
-        <v>-80.909995838</v>
+        <v>-82.22435211200001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3868595699022364</v>
+        <v>0.4152812007274228</v>
       </c>
       <c r="T89">
-        <v>5.276083076446429</v>
+        <v>5.7157566661503</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04754715999170329</v>
+        <v>0.04700685135543393</v>
       </c>
       <c r="W89">
-        <v>0.2245883796739564</v>
+        <v>0.2247157844503887</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.206726782572623</v>
+        <v>0.2043776145888432</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2475836344036328</v>
+        <v>0.2494836344036328</v>
       </c>
       <c r="C90">
-        <v>-467.6183280202359</v>
+        <v>-476.3910102803556</v>
       </c>
       <c r="D90">
-        <v>164.4136719797641</v>
+        <v>162.8799897196444</v>
       </c>
       <c r="E90">
-        <v>592.432</v>
+        <v>599.6709999999999</v>
       </c>
       <c r="F90">
-        <v>637.032</v>
+        <v>644.271</v>
       </c>
       <c r="G90">
         <v>5</v>
@@ -8655,37 +8655,37 @@
         <v>30.7</v>
       </c>
       <c r="M90">
-        <v>150.2121456</v>
+        <v>151.9191018</v>
       </c>
       <c r="N90">
-        <v>-119.5121456</v>
+        <v>-121.2191018</v>
       </c>
       <c r="O90">
-        <v>-27.487793488</v>
+        <v>-27.880393414</v>
       </c>
       <c r="P90">
-        <v>-92.024352112</v>
+        <v>-93.33870838599999</v>
       </c>
       <c r="Q90">
-        <v>-82.22435211200001</v>
+        <v>-83.538708386</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4152812007274228</v>
+        <v>0.4488704007935521</v>
       </c>
       <c r="T90">
-        <v>5.7157566661503</v>
+        <v>6.235370908527599</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04700685135543393</v>
+        <v>0.04647868448627177</v>
       </c>
       <c r="W90">
-        <v>0.2247157844503887</v>
+        <v>0.2248403261981371</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2043776145888432</v>
+        <v>0.2020812368968338</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2494836344036328</v>
+        <v>0.2513836344036328</v>
       </c>
       <c r="C91">
-        <v>-476.3910102803556</v>
+        <v>-485.1353440165018</v>
       </c>
       <c r="D91">
-        <v>162.8799897196444</v>
+        <v>161.3746559834982</v>
       </c>
       <c r="E91">
-        <v>599.6709999999999</v>
+        <v>606.91</v>
       </c>
       <c r="F91">
-        <v>644.271</v>
+        <v>651.51</v>
       </c>
       <c r="G91">
         <v>5</v>
@@ -8737,37 +8737,37 @@
         <v>30.7</v>
       </c>
       <c r="M91">
-        <v>151.9191018</v>
+        <v>153.626058</v>
       </c>
       <c r="N91">
-        <v>-121.2191018</v>
+        <v>-122.926058</v>
       </c>
       <c r="O91">
-        <v>-27.880393414</v>
+        <v>-28.27299334</v>
       </c>
       <c r="P91">
-        <v>-93.33870838599999</v>
+        <v>-94.65306466</v>
       </c>
       <c r="Q91">
-        <v>-83.538708386</v>
+        <v>-84.85306466</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4488704007935521</v>
+        <v>0.4891774408729074</v>
       </c>
       <c r="T91">
-        <v>6.235370908527599</v>
+        <v>6.85890799938036</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04647868448627177</v>
+        <v>0.04596225465864651</v>
       </c>
       <c r="W91">
-        <v>0.2248403261981371</v>
+        <v>0.2249621003514911</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2020812368968338</v>
+        <v>0.1998358898202023</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2513836344036328</v>
+        <v>0.2532836344036328</v>
       </c>
       <c r="C92">
-        <v>-485.1353440165018</v>
+        <v>-493.8521080206361</v>
       </c>
       <c r="D92">
-        <v>161.3746559834982</v>
+        <v>159.8968919793639</v>
       </c>
       <c r="E92">
-        <v>606.91</v>
+        <v>614.149</v>
       </c>
       <c r="F92">
-        <v>651.51</v>
+        <v>658.749</v>
       </c>
       <c r="G92">
         <v>5</v>
@@ -8819,37 +8819,37 @@
         <v>30.7</v>
       </c>
       <c r="M92">
-        <v>153.626058</v>
+        <v>155.3330142</v>
       </c>
       <c r="N92">
-        <v>-122.926058</v>
+        <v>-124.6330142</v>
       </c>
       <c r="O92">
-        <v>-28.27299334</v>
+        <v>-28.665593266</v>
       </c>
       <c r="P92">
-        <v>-94.65306466</v>
+        <v>-95.967420934</v>
       </c>
       <c r="Q92">
-        <v>-84.85306466</v>
+        <v>-86.16742093400001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4891774408729074</v>
+        <v>0.5384416009698972</v>
       </c>
       <c r="T92">
-        <v>6.85890799938036</v>
+        <v>7.621008888200402</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04596225465864651</v>
+        <v>0.04545717493712292</v>
       </c>
       <c r="W92">
-        <v>0.2249621003514911</v>
+        <v>0.2250811981498264</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1998358898202023</v>
+        <v>0.1976398910309692</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2532836344036328</v>
+        <v>0.2551836344036328</v>
       </c>
       <c r="C93">
-        <v>-493.8521080206361</v>
+        <v>-502.5420528169001</v>
       </c>
       <c r="D93">
-        <v>159.8968919793639</v>
+        <v>158.4459471831</v>
       </c>
       <c r="E93">
-        <v>614.149</v>
+        <v>621.388</v>
       </c>
       <c r="F93">
-        <v>658.749</v>
+        <v>665.9880000000001</v>
       </c>
       <c r="G93">
         <v>5</v>
@@ -8901,37 +8901,37 @@
         <v>30.7</v>
       </c>
       <c r="M93">
-        <v>155.3330142</v>
+        <v>157.0399704</v>
       </c>
       <c r="N93">
-        <v>-124.6330142</v>
+        <v>-126.3399704</v>
       </c>
       <c r="O93">
-        <v>-28.665593266</v>
+        <v>-29.058193192</v>
       </c>
       <c r="P93">
-        <v>-95.967420934</v>
+        <v>-97.28177720800001</v>
       </c>
       <c r="Q93">
-        <v>-86.16742093400001</v>
+        <v>-87.48177720800001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5384416009698972</v>
+        <v>0.6000218010911345</v>
       </c>
       <c r="T93">
-        <v>7.621008888200402</v>
+        <v>8.573634999225455</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04545717493712292</v>
+        <v>0.0449630752095455</v>
       </c>
       <c r="W93">
-        <v>0.2250811981498264</v>
+        <v>0.2251977068655892</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1976398910309692</v>
+        <v>0.19549163134585</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2551836344036328</v>
+        <v>0.2570836344036328</v>
       </c>
       <c r="C94">
-        <v>-502.5420528169001</v>
+        <v>-511.2059019326284</v>
       </c>
       <c r="D94">
-        <v>158.4459471831</v>
+        <v>157.0210980673716</v>
       </c>
       <c r="E94">
-        <v>621.388</v>
+        <v>628.627</v>
       </c>
       <c r="F94">
-        <v>665.9880000000001</v>
+        <v>673.227</v>
       </c>
       <c r="G94">
         <v>5</v>
@@ -8983,37 +8983,37 @@
         <v>30.7</v>
       </c>
       <c r="M94">
-        <v>157.0399704</v>
+        <v>158.7469266</v>
       </c>
       <c r="N94">
-        <v>-126.3399704</v>
+        <v>-128.0469266</v>
       </c>
       <c r="O94">
-        <v>-29.058193192</v>
+        <v>-29.450793118</v>
       </c>
       <c r="P94">
-        <v>-97.28177720800001</v>
+        <v>-98.596133482</v>
       </c>
       <c r="Q94">
-        <v>-87.48177720800001</v>
+        <v>-88.796133482</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6000218010911345</v>
+        <v>0.6791963441041537</v>
       </c>
       <c r="T94">
-        <v>8.573634999225455</v>
+        <v>9.798439999114807</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0449630752095455</v>
+        <v>0.04447960128256115</v>
       </c>
       <c r="W94">
-        <v>0.2251977068655892</v>
+        <v>0.2253117100175721</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.19549163134585</v>
+        <v>0.1933895707937441</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2570836344036328</v>
+        <v>0.2589836344036328</v>
       </c>
       <c r="C95">
-        <v>-511.2059019326284</v>
+        <v>-519.8443531013947</v>
       </c>
       <c r="D95">
-        <v>157.0210980673716</v>
+        <v>155.6216468986053</v>
       </c>
       <c r="E95">
-        <v>628.627</v>
+        <v>635.866</v>
       </c>
       <c r="F95">
-        <v>673.227</v>
+        <v>680.466</v>
       </c>
       <c r="G95">
         <v>5</v>
@@ -9065,37 +9065,37 @@
         <v>30.7</v>
       </c>
       <c r="M95">
-        <v>158.7469266</v>
+        <v>160.4538828</v>
       </c>
       <c r="N95">
-        <v>-128.0469266</v>
+        <v>-129.7538828</v>
       </c>
       <c r="O95">
-        <v>-29.450793118</v>
+        <v>-29.84339304400001</v>
       </c>
       <c r="P95">
-        <v>-98.596133482</v>
+        <v>-99.910489756</v>
       </c>
       <c r="Q95">
-        <v>-88.796133482</v>
+        <v>-90.11048975600001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6791963441041537</v>
+        <v>0.7847624014548462</v>
       </c>
       <c r="T95">
-        <v>9.798439999114807</v>
+        <v>11.43151333230061</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04447960128256115</v>
+        <v>0.04400641403487433</v>
       </c>
       <c r="W95">
-        <v>0.2253117100175721</v>
+        <v>0.2254232875705766</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1933895707937441</v>
+        <v>0.1913322349342361</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2589836344036328</v>
+        <v>0.2608836344036328</v>
       </c>
       <c r="C96">
-        <v>-519.8443531013947</v>
+        <v>-528.4580794022925</v>
       </c>
       <c r="D96">
-        <v>155.6216468986053</v>
+        <v>154.2469205977075</v>
       </c>
       <c r="E96">
-        <v>635.866</v>
+        <v>643.105</v>
       </c>
       <c r="F96">
-        <v>680.466</v>
+        <v>687.705</v>
       </c>
       <c r="G96">
         <v>5</v>
@@ -9147,37 +9147,37 @@
         <v>30.7</v>
       </c>
       <c r="M96">
-        <v>160.4538828</v>
+        <v>162.160839</v>
       </c>
       <c r="N96">
-        <v>-129.7538828</v>
+        <v>-131.460839</v>
       </c>
       <c r="O96">
-        <v>-29.84339304400001</v>
+        <v>-30.23599297000001</v>
       </c>
       <c r="P96">
-        <v>-99.910489756</v>
+        <v>-101.22484603</v>
       </c>
       <c r="Q96">
-        <v>-90.11048975600001</v>
+        <v>-91.42484603000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7847624014548462</v>
+        <v>0.9325548817458159</v>
       </c>
       <c r="T96">
-        <v>11.43151333230061</v>
+        <v>13.71781599876074</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04400641403487433</v>
+        <v>0.04354318862398091</v>
       </c>
       <c r="W96">
-        <v>0.2254232875705766</v>
+        <v>0.2255325161224653</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1913322349342361</v>
+        <v>0.1893182114086126</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2608836344036328</v>
+        <v>0.2627836344036328</v>
       </c>
       <c r="C97">
-        <v>-528.4580794022925</v>
+        <v>-537.0477303393603</v>
       </c>
       <c r="D97">
-        <v>154.2469205977075</v>
+        <v>152.8962696606397</v>
       </c>
       <c r="E97">
-        <v>643.105</v>
+        <v>650.3440000000001</v>
       </c>
       <c r="F97">
-        <v>687.705</v>
+        <v>694.9440000000001</v>
       </c>
       <c r="G97">
         <v>5</v>
@@ -9229,37 +9229,37 @@
         <v>30.7</v>
       </c>
       <c r="M97">
-        <v>162.160839</v>
+        <v>163.8677952</v>
       </c>
       <c r="N97">
-        <v>-131.460839</v>
+        <v>-133.1677952</v>
       </c>
       <c r="O97">
-        <v>-30.23599297000001</v>
+        <v>-30.62859289600001</v>
       </c>
       <c r="P97">
-        <v>-101.22484603</v>
+        <v>-102.539202304</v>
       </c>
       <c r="Q97">
-        <v>-91.42484603000001</v>
+        <v>-92.73920230400002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9325548817458159</v>
+        <v>1.15424360218227</v>
       </c>
       <c r="T97">
-        <v>13.71781599876074</v>
+        <v>17.14726999845093</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04354318862398091</v>
+        <v>0.04308961374248111</v>
       </c>
       <c r="W97">
-        <v>0.2255325161224653</v>
+        <v>0.225639469079523</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1893182114086126</v>
+        <v>0.1873461467064396</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2627836344036328</v>
+        <v>0.2646836344036328</v>
       </c>
       <c r="C98">
-        <v>-537.0477303393602</v>
+        <v>-545.6139328647876</v>
       </c>
       <c r="D98">
-        <v>152.8962696606397</v>
+        <v>151.5690671352124</v>
       </c>
       <c r="E98">
-        <v>650.3439999999999</v>
+        <v>657.583</v>
       </c>
       <c r="F98">
-        <v>694.944</v>
+        <v>702.183</v>
       </c>
       <c r="G98">
         <v>5</v>
@@ -9311,37 +9311,37 @@
         <v>30.7</v>
       </c>
       <c r="M98">
-        <v>163.8677952</v>
+        <v>165.5747514</v>
       </c>
       <c r="N98">
-        <v>-133.1677952</v>
+        <v>-134.8747514</v>
       </c>
       <c r="O98">
-        <v>-30.628592896</v>
+        <v>-31.021192822</v>
       </c>
       <c r="P98">
-        <v>-102.539202304</v>
+        <v>-103.853558578</v>
       </c>
       <c r="Q98">
-        <v>-92.739202304</v>
+        <v>-94.05355857800001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.154243602182268</v>
+        <v>1.52372480290969</v>
       </c>
       <c r="T98">
-        <v>17.14726999845088</v>
+        <v>22.86302666460118</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04308961374248112</v>
+        <v>0.04264539092039368</v>
       </c>
       <c r="W98">
-        <v>0.225639469079523</v>
+        <v>0.2257442168209712</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1873461467064396</v>
+        <v>0.1854147431321463</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2646836344036328</v>
+        <v>0.2665836344036328</v>
       </c>
       <c r="C99">
-        <v>-545.6139328647876</v>
+        <v>-554.1572923492881</v>
       </c>
       <c r="D99">
-        <v>151.5690671352124</v>
+        <v>150.2647076507118</v>
       </c>
       <c r="E99">
-        <v>657.583</v>
+        <v>664.8219999999999</v>
       </c>
       <c r="F99">
-        <v>702.183</v>
+        <v>709.4219999999999</v>
       </c>
       <c r="G99">
         <v>5</v>
@@ -9393,37 +9393,37 @@
         <v>30.7</v>
       </c>
       <c r="M99">
-        <v>165.5747514</v>
+        <v>167.2817076</v>
       </c>
       <c r="N99">
-        <v>-134.8747514</v>
+        <v>-136.5817076</v>
       </c>
       <c r="O99">
-        <v>-31.021192822</v>
+        <v>-31.413792748</v>
       </c>
       <c r="P99">
-        <v>-103.853558578</v>
+        <v>-105.167914852</v>
       </c>
       <c r="Q99">
-        <v>-94.05355857800001</v>
+        <v>-95.367914852</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.52372480290969</v>
+        <v>2.262687204364535</v>
       </c>
       <c r="T99">
-        <v>22.86302666460118</v>
+        <v>34.29453999690177</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04264539092039368</v>
+        <v>0.04221023387018558</v>
       </c>
       <c r="W99">
-        <v>0.2257442168209712</v>
+        <v>0.2258468268534102</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1854147431321463</v>
+        <v>0.1835227559573286</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2665836344036328</v>
+        <v>0.2684836344036328</v>
       </c>
       <c r="C100">
-        <v>-554.1572923492881</v>
+        <v>-562.6783935027967</v>
       </c>
       <c r="D100">
-        <v>150.2647076507118</v>
+        <v>148.9826064972033</v>
       </c>
       <c r="E100">
-        <v>664.8219999999999</v>
+        <v>672.0609999999999</v>
       </c>
       <c r="F100">
-        <v>709.4219999999999</v>
+        <v>716.6609999999999</v>
       </c>
       <c r="G100">
         <v>5</v>
@@ -9475,37 +9475,37 @@
         <v>30.7</v>
       </c>
       <c r="M100">
-        <v>167.2817076</v>
+        <v>168.9886638</v>
       </c>
       <c r="N100">
-        <v>-136.5817076</v>
+        <v>-138.2886638</v>
       </c>
       <c r="O100">
-        <v>-31.413792748</v>
+        <v>-31.806392674</v>
       </c>
       <c r="P100">
-        <v>-105.167914852</v>
+        <v>-106.482271126</v>
       </c>
       <c r="Q100">
-        <v>-95.367914852</v>
+        <v>-96.682271126</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.262687204364535</v>
+        <v>4.47957440872907</v>
       </c>
       <c r="T100">
-        <v>34.29453999690177</v>
+        <v>68.58907999380354</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04221023387018558</v>
+        <v>0.04178386787149684</v>
       </c>
       <c r="W100">
-        <v>0.2258468268534102</v>
+        <v>0.2259473639559011</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1835227559573286</v>
+        <v>0.1816689907456384</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2684836344036328</v>
-      </c>
-      <c r="C101">
-        <v>-562.6783935027967</v>
-      </c>
-      <c r="D101">
-        <v>148.9826064972033</v>
-      </c>
-      <c r="E101">
-        <v>672.0609999999999</v>
-      </c>
-      <c r="F101">
-        <v>716.6609999999999</v>
-      </c>
-      <c r="G101">
-        <v>5</v>
-      </c>
-      <c r="H101">
-        <v>679.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>40.5</v>
-      </c>
-      <c r="K101">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="L101">
-        <v>30.7</v>
-      </c>
-      <c r="M101">
-        <v>168.9886638</v>
-      </c>
-      <c r="N101">
-        <v>-138.2886638</v>
-      </c>
-      <c r="O101">
-        <v>-31.806392674</v>
-      </c>
-      <c r="P101">
-        <v>-106.482271126</v>
-      </c>
-      <c r="Q101">
-        <v>-96.682271126</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.47957440872907</v>
-      </c>
-      <c r="T101">
-        <v>68.58907999380354</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04178386787149684</v>
-      </c>
-      <c r="W101">
-        <v>0.2259473639559011</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1816689907456384</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
